--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -2285,7 +2285,11 @@
           <t>Reheat Beef Stroganoff (Sun Dinner)</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G10" s="7" t="inlineStr"/>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -2359,7 +2363,11 @@
           <t>Reheat Vegan Mushroom Stroganoff (Sun Dinner — Veg)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -2521,7 +2529,11 @@
           <t>HOT Beef Stroganoff → Dinner</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr"/>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G13" s="15" t="inlineStr"/>
       <c r="H13" s="15" t="inlineStr">
         <is>
@@ -2595,7 +2607,11 @@
           <t>HOT Falafels → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -2669,7 +2685,11 @@
           <t>Heat Falafel (frozen → oven) (Mon Lunch — Veg)</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>40 pcs</t>
+        </is>
+      </c>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="7" t="inlineStr">
         <is>
@@ -3172,7 +3192,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr"/>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G21" s="15" t="inlineStr"/>
       <c r="H21" s="15" t="inlineStr">
         <is>
@@ -3234,7 +3258,11 @@
           <t>HOT Jerk Chicken → Dinner</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>1.5 hotels</t>
+        </is>
+      </c>
       <c r="G22" s="15" t="inlineStr"/>
       <c r="H22" s="15" t="inlineStr">
         <is>
@@ -3394,7 +3422,11 @@
           <t>HOT Beef Nacho Mix → Lunch</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -3468,7 +3500,11 @@
           <t>HOT Vegan Nacho Mix → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -3624,7 +3660,11 @@
           <t>Reheat Vegan Nacho Mix (Tue Lunch)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="7" t="inlineStr">
         <is>
@@ -4308,10 +4348,8 @@
           <t>Pork braise</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="K35" s="7" t="n">
+        <v>60</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
@@ -4392,10 +4430,8 @@
           <t>Pork braise</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="K36" s="7" t="n">
+        <v>60</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
@@ -4535,7 +4571,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr"/>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G38" s="15" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr">
         <is>
@@ -4597,7 +4637,11 @@
           <t>HOT Pork/Chicken/Halal Carnitas → Dinner</t>
         </is>
       </c>
-      <c r="F39" s="15" t="inlineStr"/>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
           <t>5 oz</t>
@@ -4765,7 +4809,11 @@
           <t>HOT Crispy Chicken Tenders → Lunch</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr">
         <is>
@@ -4839,7 +4887,11 @@
           <t>HOT Vegan Tenders → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="G42" s="3" t="inlineStr"/>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -4913,7 +4965,11 @@
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -4989,7 +5045,11 @@
           <t>Heat Crispy Chicken + Vegan Tenders (Wed Lunch)</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>4.5 hotels</t>
+        </is>
+      </c>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -5063,7 +5123,11 @@
           <t>Cook Adobo Pork/Chicken</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr"/>
+      <c r="F45" s="13" t="inlineStr">
+        <is>
+          <t>40 lbs/32 lbs cooked</t>
+        </is>
+      </c>
       <c r="G45" s="13" t="inlineStr"/>
       <c r="H45" s="13" t="inlineStr">
         <is>
@@ -5642,7 +5706,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G52" s="15" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr">
         <is>
@@ -6195,10 +6263,8 @@
         </is>
       </c>
       <c r="J59" s="14" t="inlineStr"/>
-      <c r="K59" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="K59" s="13" t="n">
+        <v>240</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
@@ -6681,7 +6747,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F65" s="15" t="inlineStr"/>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G65" s="15" t="inlineStr"/>
       <c r="H65" s="15" t="inlineStr">
         <is>
@@ -7344,7 +7414,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F73" s="15" t="inlineStr"/>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G73" s="15" t="inlineStr"/>
       <c r="H73" s="15" t="inlineStr">
         <is>
@@ -7564,7 +7638,7 @@
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr"/>
@@ -7600,10 +7674,8 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P76" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="P76" s="15" t="n">
+        <v>3</v>
       </c>
       <c r="Q76" s="15" t="inlineStr">
         <is>
@@ -7728,7 +7800,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>0.5 hotel</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr"/>
@@ -7768,10 +7840,8 @@
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P78" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="P78" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
@@ -7810,7 +7880,11 @@
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr"/>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>80 lbs + 15 lbs</t>
+        </is>
+      </c>
       <c r="G79" s="7" t="inlineStr"/>
       <c r="H79" s="7" t="inlineStr">
         <is>
@@ -8469,7 +8543,11 @@
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F87" s="13" t="inlineStr"/>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G87" s="13" t="inlineStr"/>
       <c r="H87" s="13" t="inlineStr"/>
       <c r="I87" s="13" t="inlineStr">
@@ -8627,7 +8705,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F89" s="15" t="inlineStr"/>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G89" s="15" t="inlineStr"/>
       <c r="H89" s="15" t="inlineStr">
         <is>
@@ -8863,7 +8945,11 @@
           <t>HOT Carrot Cabbage Fry → Dinner side</t>
         </is>
       </c>
-      <c r="F92" s="15" t="inlineStr"/>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="G92" s="15" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr">
         <is>
@@ -8943,7 +9029,11 @@
           <t>HOT Rice → Dinner</t>
         </is>
       </c>
-      <c r="F93" s="15" t="inlineStr"/>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G93" s="15" t="inlineStr"/>
       <c r="H93" s="15" t="inlineStr"/>
       <c r="I93" s="15" t="inlineStr">
@@ -8977,10 +9067,8 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P93" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="P93" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="Q93" s="15" t="inlineStr">
         <is>
@@ -10061,7 +10149,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G12" s="15" t="inlineStr"/>
       <c r="H12" s="15" t="inlineStr">
         <is>
@@ -11404,7 +11496,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr"/>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G28" s="15" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr">
         <is>
@@ -11640,7 +11736,11 @@
           <t>HOT Rice → Dinner</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr"/>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G31" s="15" t="inlineStr"/>
       <c r="H31" s="15" t="inlineStr">
         <is>
@@ -11714,7 +11814,11 @@
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G32" s="15" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr">
         <is>
@@ -12532,7 +12636,11 @@
           <t>Steam Broccoli (Tue Dinner side)</t>
         </is>
       </c>
-      <c r="F42" s="13" t="inlineStr"/>
+      <c r="F42" s="13" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G42" s="13" t="inlineStr"/>
       <c r="H42" s="13" t="inlineStr">
         <is>
@@ -12684,7 +12792,11 @@
           <t>HOT Steamed Rice → Dinner</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G44" s="15" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr">
         <is>
@@ -12758,7 +12870,11 @@
           <t>HOT Broccoli → Dinner side</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr"/>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G45" s="15" t="inlineStr"/>
       <c r="H45" s="15" t="inlineStr">
         <is>
@@ -13849,7 +13965,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G58" s="15" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr">
         <is>
@@ -14087,7 +14207,11 @@
           <t>HOT Coconut Rice &amp; Peas → Dinner</t>
         </is>
       </c>
-      <c r="F61" s="15" t="inlineStr"/>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G61" s="15" t="inlineStr"/>
       <c r="H61" s="15" t="inlineStr">
         <is>
@@ -14161,7 +14285,11 @@
           <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
-      <c r="F62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="G62" s="15" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr">
         <is>
@@ -19138,7 +19266,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>50 pcs</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
@@ -19174,10 +19302,8 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="P17" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
@@ -19718,7 +19844,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G24" s="15" t="inlineStr"/>
       <c r="H24" s="15" t="inlineStr">
         <is>
@@ -21294,7 +21424,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr"/>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G43" s="15" t="inlineStr"/>
       <c r="H43" s="15" t="inlineStr">
         <is>
@@ -21704,7 +21838,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>155 pcs</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr"/>
@@ -21740,10 +21874,8 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P48" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="P48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
@@ -21864,7 +21996,11 @@
           <t>Cold Chiffonade Lettuce &amp; Sliced Peppers → Lunch (wraps)</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -22613,7 +22749,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F59" s="15" t="inlineStr"/>
+      <c r="F59" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G59" s="15" t="inlineStr"/>
       <c r="H59" s="15" t="inlineStr">
         <is>
@@ -23503,10 +23643,8 @@
           <t>Stove top</t>
         </is>
       </c>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
+      <c r="K70" s="13" t="n">
+        <v>240</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
@@ -23981,7 +24119,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F76" s="15" t="inlineStr"/>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G76" s="15" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr">
         <is>
@@ -24045,7 +24187,7 @@
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>2.5 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr">
@@ -24209,7 +24351,11 @@
           <t>HOT Chakalaka → Dinner side</t>
         </is>
       </c>
-      <c r="F79" s="15" t="inlineStr"/>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G79" s="15" t="inlineStr"/>
       <c r="H79" s="15" t="inlineStr">
         <is>
@@ -24369,7 +24515,11 @@
           <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
         </is>
       </c>
-      <c r="F81" s="13" t="inlineStr"/>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>100 lbs</t>
+        </is>
+      </c>
       <c r="G81" s="13" t="inlineStr"/>
       <c r="H81" s="13" t="inlineStr">
         <is>
@@ -24935,7 +25085,11 @@
           <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="F88" s="15" t="inlineStr"/>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="G88" s="15" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr"/>
       <c r="I88" s="15" t="inlineStr">
@@ -25011,7 +25165,11 @@
           <t>HOT Spring Rolls → Dinner side</t>
         </is>
       </c>
-      <c r="F89" s="15" t="inlineStr"/>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="G89" s="15" t="inlineStr"/>
       <c r="H89" s="15" t="inlineStr"/>
       <c r="I89" s="15" t="inlineStr">
@@ -26180,7 +26338,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F103" s="15" t="inlineStr"/>
+      <c r="F103" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G103" s="15" t="inlineStr"/>
       <c r="H103" s="15" t="inlineStr">
         <is>
@@ -26242,7 +26404,11 @@
           <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
-      <c r="F104" s="15" t="inlineStr"/>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G104" s="15" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr">
         <is>
@@ -26404,7 +26570,11 @@
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="F106" s="15" t="inlineStr"/>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G106" s="15" t="inlineStr">
         <is>
           <t>6 oz</t>
@@ -26849,10 +27019,8 @@
       </c>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="P4" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
@@ -27399,7 +27567,11 @@
           <t>Reheat White Chilli Chicken Pasta (Sun Dinner)</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr"/>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -27901,7 +28073,11 @@
           <t>HOT Pasta + Broccoli &amp; Carrot → Dinner</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>9 hotels</t>
+        </is>
+      </c>
       <c r="G17" s="15" t="inlineStr"/>
       <c r="H17" s="15" t="inlineStr">
         <is>
@@ -28166,10 +28342,8 @@
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr"/>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="K20" s="13" t="n">
+        <v>60</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
@@ -28968,7 +29142,11 @@
           <t>HOT Curry Fish → Dinner</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr"/>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G30" s="15" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr"/>
       <c r="I30" s="15" t="inlineStr">
@@ -29042,7 +29220,11 @@
           <t>HOT Curry Spiced Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr"/>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="G31" s="15" t="inlineStr"/>
       <c r="H31" s="15" t="inlineStr"/>
       <c r="I31" s="15" t="inlineStr">
@@ -29116,7 +29298,11 @@
           <t>HOT Green Curry Sauce → Dinner</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="G32" s="15" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr"/>
       <c r="I32" s="15" t="inlineStr">
@@ -29192,7 +29378,11 @@
           <t>HOT Rice + Green Beans → Dinner</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr"/>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>7 hotels</t>
+        </is>
+      </c>
       <c r="G33" s="15" t="inlineStr"/>
       <c r="H33" s="15" t="inlineStr">
         <is>
@@ -30831,7 +31021,11 @@
           <t>HOT BBQ Chicken Legs → Dinner</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr"/>
+      <c r="F53" s="15" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
       <c r="G53" s="15" t="inlineStr"/>
       <c r="H53" s="15" t="inlineStr"/>
       <c r="I53" s="15" t="inlineStr">
@@ -30907,7 +31101,11 @@
           <t>HOT BBQ Vegan Tenders → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="F54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="G54" s="15" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr"/>
       <c r="I54" s="15" t="inlineStr">
@@ -30983,7 +31181,11 @@
           <t>HOT Herb Garlic Potatoes → Dinner</t>
         </is>
       </c>
-      <c r="F55" s="15" t="inlineStr"/>
+      <c r="F55" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G55" s="15" t="inlineStr"/>
       <c r="H55" s="15" t="inlineStr"/>
       <c r="I55" s="15" t="inlineStr">
@@ -31059,7 +31261,11 @@
           <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
-      <c r="F56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G56" s="15" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr"/>
       <c r="I56" s="15" t="inlineStr">
@@ -32241,7 +32447,11 @@
           <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
-      <c r="F70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
       <c r="G70" s="15" t="inlineStr"/>
       <c r="H70" s="15" t="inlineStr">
         <is>
@@ -32315,7 +32525,11 @@
           <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
         </is>
       </c>
-      <c r="F71" s="15" t="inlineStr"/>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G71" s="15" t="inlineStr"/>
       <c r="H71" s="15" t="inlineStr"/>
       <c r="I71" s="15" t="inlineStr">
@@ -32463,7 +32677,11 @@
           <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
@@ -33591,7 +33809,11 @@
           <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
-      <c r="F87" s="15" t="inlineStr"/>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>8 hotels</t>
+        </is>
+      </c>
       <c r="G87" s="15" t="inlineStr"/>
       <c r="H87" s="15" t="inlineStr">
         <is>
@@ -33873,10 +34095,8 @@
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P90" s="15" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="P90" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="Q90" s="15" t="inlineStr">
         <is>
@@ -33917,7 +34137,7 @@
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>0.5 unit</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="G91" s="15" t="inlineStr"/>
@@ -33925,7 +34145,7 @@
       <c r="I91" s="15" t="inlineStr"/>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
         </is>
       </c>
       <c r="K91" s="15" t="inlineStr"/>
@@ -33946,7 +34166,7 @@
         </is>
       </c>
       <c r="P91" s="18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q91" s="15" t="inlineStr">
         <is>
@@ -34791,7 +35011,11 @@
           <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="F102" s="15" t="inlineStr"/>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="G102" s="15" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr"/>
       <c r="I102" s="15" t="inlineStr">
@@ -34865,7 +35089,11 @@
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F103" s="15" t="inlineStr"/>
+      <c r="F103" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
       <c r="G103" s="15" t="inlineStr"/>
       <c r="H103" s="15" t="inlineStr"/>
       <c r="I103" s="15" t="inlineStr"/>
@@ -35661,7 +35889,11 @@
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F113" s="13" t="inlineStr"/>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G113" s="13" t="inlineStr"/>
       <c r="H113" s="13" t="inlineStr">
         <is>
@@ -35737,7 +35969,11 @@
           <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
-      <c r="F114" s="15" t="inlineStr"/>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G114" s="15" t="inlineStr"/>
       <c r="H114" s="15" t="inlineStr"/>
       <c r="I114" s="15" t="inlineStr">
@@ -35811,7 +36047,11 @@
           <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="F115" s="15" t="inlineStr"/>
+      <c r="F115" s="15" t="inlineStr">
+        <is>
+          <t>0.5 hotels</t>
+        </is>
+      </c>
       <c r="G115" s="15" t="inlineStr"/>
       <c r="H115" s="15" t="inlineStr"/>
       <c r="I115" s="15" t="inlineStr">
@@ -35885,7 +36125,11 @@
           <t>HOT Rice → Dinner side</t>
         </is>
       </c>
-      <c r="F116" s="15" t="inlineStr"/>
+      <c r="F116" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="G116" s="15" t="inlineStr"/>
       <c r="H116" s="15" t="inlineStr">
         <is>
@@ -35959,7 +36203,11 @@
           <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
         </is>
       </c>
-      <c r="F117" s="15" t="inlineStr"/>
+      <c r="F117" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="G117" s="15" t="inlineStr"/>
       <c r="H117" s="15" t="inlineStr"/>
       <c r="I117" s="15" t="inlineStr">

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+          <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>No AM run — Tuna Rex + Chickpea Rex Salad pre-sent Fri PM</t>
+          <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -25224,7 +25224,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>No AM run — Bean Salad pre-sent Thu PM</t>
+          <t>Bean Salad at Rex — sent Thu PM</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -32396,7 +32396,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>No AM run — Coronation Chicken Salad pre-sent Tue PM</t>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -4375,7 +4375,7 @@
       <c r="Q35" s="7" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thu/Fri Production (prev. cycle)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thu/Fri Production (prev. cycle)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="R39" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thu/Fri Production (prev. cycle)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T124"/>
+  <dimension ref="A1:T126"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -34252,58 +34252,68 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
+          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="G83" s="9" t="inlineStr"/>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr"/>
-      <c r="J83" s="10" t="inlineStr"/>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
+        </is>
+      </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M83" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N83" s="9" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="O83" s="9" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P83" s="9" t="n">
-        <v>1</v>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P83" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="Q83" s="9" t="inlineStr"/>
       <c r="R83" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-      <c r="S83" s="12" t="n">
-        <v>5</v>
+          <t>Serves: Wk.4 Saturday Lunch</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -34329,12 +34339,12 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
+          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>1 cs</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr"/>
@@ -34345,48 +34355,50 @@
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="J84" s="10" t="inlineStr"/>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
+        </is>
+      </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M84" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N84" s="9" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="O84" s="9" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P84" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P84" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="Q84" s="9" t="inlineStr"/>
       <c r="R84" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-      <c r="S84" s="12" t="n">
-        <v>5</v>
+          <t>Serves: Wk.4 Saturday Lunch</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -34397,7 +34409,7 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
@@ -34412,12 +34424,12 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
+          <t>Prep Slaw (→ Fri Lunch)</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>1 cs</t>
+          <t>???</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr"/>
@@ -34426,454 +34438,441 @@
           <t>bus bin</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="J85" s="10" t="inlineStr"/>
+      <c r="I85" s="9" t="inlineStr"/>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>Shred; dress; chill; send Thu PM</t>
+        </is>
+      </c>
       <c r="K85" s="9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N85" s="9" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P85" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P85" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="Q85" s="9" t="inlineStr"/>
       <c r="R85" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-      <c r="S85" s="12" t="n">
-        <v>5</v>
+          <t>Serves: Wk.4 Friday Lunch</t>
+        </is>
+      </c>
+      <c r="S85" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C86" s="9" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr"/>
+      <c r="H86" s="13" t="inlineStr"/>
+      <c r="I86" s="13" t="inlineStr"/>
+      <c r="J86" s="14" t="inlineStr">
+        <is>
+          <t>Combi roast</t>
+        </is>
+      </c>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M86" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N86" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O86" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P86" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q86" s="13" t="inlineStr"/>
+      <c r="R86" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr"/>
+      <c r="H87" s="13" t="inlineStr"/>
+      <c r="I87" s="13" t="inlineStr"/>
+      <c r="J87" s="14" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M87" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N87" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O87" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P87" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q87" s="13" t="inlineStr"/>
+      <c r="R87" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>215 pcs</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr"/>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>hotel/vac</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K88" s="15" t="inlineStr"/>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N88" s="15" t="inlineStr"/>
+      <c r="O88" s="15" t="inlineStr"/>
+      <c r="P88" s="15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q88" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R88" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="inlineStr">
+        <is>
+          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>8 hotels</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr"/>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
+        <is>
+          <t>8 hotels</t>
+        </is>
+      </c>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K89" s="15" t="inlineStr"/>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M89" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N89" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O89" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P89" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Q89" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R89" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>Cold Beef Nacho Mix → Rex fridge</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr"/>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="J90" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
+        </is>
+      </c>
+      <c r="K90" s="15" t="inlineStr"/>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M90" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N90" s="15" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O90" s="15" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="F86" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="G86" s="9" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
-        </is>
-      </c>
-      <c r="K86" s="9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L86" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M86" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N86" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O86" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P86" s="9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q86" s="9" t="inlineStr"/>
-      <c r="R86" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Saturday Lunch</t>
-        </is>
-      </c>
-      <c r="S86" s="11" t="n">
+      <c r="P90" s="17" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="J87" s="10" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
-        </is>
-      </c>
-      <c r="K87" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L87" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M87" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N87" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O87" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P87" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q87" s="9" t="inlineStr"/>
-      <c r="R87" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Saturday Lunch</t>
-        </is>
-      </c>
-      <c r="S87" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>Prep Slaw (→ Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr"/>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="inlineStr"/>
-      <c r="J88" s="10" t="inlineStr">
-        <is>
-          <t>Shred; dress; chill; send Thu PM</t>
-        </is>
-      </c>
-      <c r="K88" s="9" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="L88" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M88" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N88" s="9" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O88" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P88" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q88" s="9" t="inlineStr"/>
-      <c r="R88" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Friday Lunch</t>
-        </is>
-      </c>
-      <c r="S88" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C89" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D89" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E89" s="14" t="inlineStr">
-        <is>
-          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="F89" s="13" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="G89" s="13" t="inlineStr"/>
-      <c r="H89" s="13" t="inlineStr"/>
-      <c r="I89" s="13" t="inlineStr"/>
-      <c r="J89" s="14" t="inlineStr">
-        <is>
-          <t>Combi roast</t>
-        </is>
-      </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L89" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M89" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N89" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O89" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P89" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q89" s="13" t="inlineStr"/>
-      <c r="R89" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C90" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D90" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E90" s="14" t="inlineStr">
-        <is>
-          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
-        </is>
-      </c>
-      <c r="F90" s="13" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="G90" s="13" t="inlineStr"/>
-      <c r="H90" s="13" t="inlineStr"/>
-      <c r="I90" s="13" t="inlineStr"/>
-      <c r="J90" s="14" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="K90" s="13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M90" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N90" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O90" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P90" s="13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q90" s="13" t="inlineStr"/>
-      <c r="R90" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Dinner</t>
+      <c r="Q90" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R90" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -34900,28 +34899,28 @@
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
+          <t>Cold Vegan Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>215 pcs</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="G91" s="15" t="inlineStr"/>
       <c r="H91" s="15" t="inlineStr">
         <is>
-          <t>hotel/vac</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
-          <t>6 hotels</t>
+          <t>0.5u</t>
         </is>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
         </is>
       </c>
       <c r="K91" s="15" t="inlineStr"/>
@@ -34935,12 +34934,18 @@
           <t>4</t>
         </is>
       </c>
-      <c r="N91" s="15" t="inlineStr"/>
-      <c r="O91" s="15" t="inlineStr"/>
-      <c r="P91" s="15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="N91" s="15" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O91" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P91" s="17" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q91" s="15" t="inlineStr">
         <is>
@@ -34949,7 +34954,7 @@
       </c>
       <c r="R91" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
+          <t>Produced: Wk. 4 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -34976,34 +34981,34 @@
       </c>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>bus bin</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
@@ -35011,20 +35016,14 @@
           <t>4</t>
         </is>
       </c>
-      <c r="N92" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
+      <c r="N92" s="15" t="inlineStr"/>
       <c r="O92" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P92" s="15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P92" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="Q92" s="15" t="inlineStr">
         <is>
@@ -35033,7 +35032,7 @@
       </c>
       <c r="R92" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk.4 Wed Production (LAN)</t>
         </is>
       </c>
     </row>
@@ -35060,534 +35059,532 @@
       </c>
       <c r="E93" s="16" t="inlineStr">
         <is>
-          <t>Cold Beef Nacho Mix → Rex fridge</t>
+          <t>Cold Slaw → Fri Lunch side</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="G93" s="15" t="inlineStr"/>
-      <c r="H93" s="15" t="inlineStr">
+      <c r="H93" s="15" t="inlineStr"/>
+      <c r="I93" s="15" t="inlineStr"/>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K93" s="15" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M93" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N93" s="15" t="inlineStr"/>
+      <c r="O93" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P93" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q93" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R93" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Wed Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>HOT Crispy Falafel → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>0.5 hotel</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr"/>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R94" s="4" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Fri Lunch (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>30 pcs</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr">
+        <is>
+          <t>Purchased frozen; heat day-of at Bloor</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O95" s="7" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P95" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q95" s="7" t="inlineStr"/>
+      <c r="R95" s="8" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Friday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>Vegan Carnitas</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="G96" s="13" t="inlineStr"/>
+      <c r="H96" s="13" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="J93" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
-      <c r="K93" s="15" t="inlineStr"/>
-      <c r="L93" s="5" t="inlineStr">
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>Stove</t>
+        </is>
+      </c>
+      <c r="K96" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M93" s="15" t="inlineStr">
+      <c r="M96" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N96" s="13" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O96" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P96" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q96" s="13" t="inlineStr"/>
+      <c r="R96" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S96" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N93" s="15" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="O93" s="15" t="inlineStr">
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P93" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q93" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R93" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="15" t="inlineStr">
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>Broccoli Prep (Saturday Lunch)</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="inlineStr"/>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="J97" s="10" t="inlineStr"/>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M97" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="inlineStr">
-        <is>
-          <t>Cold Vegan Nacho Mix → Rex fridge</t>
-        </is>
-      </c>
-      <c r="F94" s="15" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="G94" s="15" t="inlineStr"/>
-      <c r="H94" s="15" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="J94" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
-        </is>
-      </c>
-      <c r="K94" s="15" t="inlineStr"/>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="N97" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O97" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P97" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Q97" s="9" t="inlineStr"/>
+      <c r="R97" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Saturday Lunch</t>
+        </is>
+      </c>
+      <c r="S97" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>4 hotels veg</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="inlineStr"/>
+      <c r="H98" s="9" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr"/>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M94" s="15" t="inlineStr">
+      <c r="M98" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N94" s="15" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="O94" s="15" t="inlineStr">
+      <c r="N98" s="9" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O98" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P98" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q98" s="9" t="inlineStr"/>
+      <c r="R98" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P94" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q94" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R94" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E95" s="16" t="inlineStr">
-        <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
-        </is>
-      </c>
-      <c r="F95" s="15" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="G95" s="15" t="inlineStr"/>
-      <c r="H95" s="15" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="J95" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="K95" s="15" t="inlineStr"/>
-      <c r="L95" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M95" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N95" s="15" t="inlineStr"/>
-      <c r="O95" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P95" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q95" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R95" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk.4 Wed Production (LAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D96" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E96" s="16" t="inlineStr">
-        <is>
-          <t>Cold Slaw → Fri Lunch side</t>
-        </is>
-      </c>
-      <c r="F96" s="15" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="G96" s="15" t="inlineStr"/>
-      <c r="H96" s="15" t="inlineStr"/>
-      <c r="I96" s="15" t="inlineStr"/>
-      <c r="J96" s="16" t="inlineStr">
-        <is>
-          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
-        </is>
-      </c>
-      <c r="K96" s="15" t="inlineStr"/>
-      <c r="L96" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M96" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N96" s="15" t="inlineStr"/>
-      <c r="O96" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P96" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R96" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk.4 Wed Production (LAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>HOT Crispy Falafel → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr"/>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>0.5 hotel</t>
-        </is>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K97" s="3" t="inlineStr"/>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>Jerk Marinade</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>cambro/bag</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>1 bag/8 qt</t>
+        </is>
+      </c>
+      <c r="J99" s="10" t="inlineStr"/>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="Q97" s="3" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R97" s="4" t="inlineStr">
-        <is>
-          <t>Produced: Wk.4 Fri Lunch (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
-      <c r="J98" s="8" t="inlineStr">
-        <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
-        </is>
-      </c>
-      <c r="K98" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M98" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N98" s="7" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O98" s="7" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P98" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q98" s="7" t="inlineStr"/>
-      <c r="R98" s="8" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Friday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C99" s="13" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D99" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E99" s="14" t="inlineStr">
-        <is>
-          <t>Vegan Carnitas</t>
-        </is>
-      </c>
-      <c r="F99" s="13" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="G99" s="13" t="inlineStr"/>
-      <c r="H99" s="13" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>1/2 hotel</t>
-        </is>
-      </c>
-      <c r="J99" s="14" t="inlineStr">
-        <is>
-          <t>Stove</t>
-        </is>
-      </c>
-      <c r="K99" s="13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L99" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M99" s="13" t="inlineStr">
+      <c r="M99" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N99" s="13" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="O99" s="13" t="inlineStr">
+      <c r="N99" s="9" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="O99" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P99" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q99" s="13" t="inlineStr"/>
-      <c r="R99" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+      <c r="P99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q99" s="9" t="inlineStr"/>
+      <c r="R99" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Monday Dinner</t>
         </is>
       </c>
       <c r="S99" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -35613,12 +35610,12 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>Broccoli Prep (Saturday Lunch)</t>
+          <t>Jerk Cauliflower</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>15 pcs</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr"/>
@@ -35629,288 +35626,281 @@
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>1/2 hotel</t>
         </is>
       </c>
       <c r="J100" s="10" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L100" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M100" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N100" s="9" t="inlineStr">
         <is>
-          <t>SATURDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="O100" s="9" t="inlineStr">
         <is>
-          <t>LUNCH</t>
+          <t>DINNER</t>
         </is>
       </c>
       <c r="P100" s="9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q100" s="9" t="inlineStr"/>
       <c r="R100" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Saturday Lunch</t>
-        </is>
-      </c>
-      <c r="S100" s="11" t="n">
+          <t>Serves: Wk. 1 Monday Dinner</t>
+        </is>
+      </c>
+      <c r="S100" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr">
-        <is>
-          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="F101" s="9" t="inlineStr">
-        <is>
-          <t>4 hotels veg</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr"/>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="10" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M101" s="9" t="inlineStr">
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N101" s="9" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O101" s="9" t="inlineStr">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P101" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q101" s="9" t="inlineStr"/>
-      <c r="R101" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E102" s="10" t="inlineStr">
-        <is>
-          <t>Jerk Marinade</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr">
-        <is>
-          <t>cambro/bag</t>
-        </is>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>1 bag/8 qt</t>
-        </is>
-      </c>
-      <c r="J102" s="10" t="inlineStr"/>
-      <c r="K102" s="9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M102" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N102" s="9" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="O102" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q102" s="9" t="inlineStr"/>
-      <c r="R102" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
-        </is>
-      </c>
-      <c r="S102" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="inlineStr">
-        <is>
-          <t>Jerk Cauliflower</t>
-        </is>
-      </c>
-      <c r="F103" s="9" t="inlineStr">
-        <is>
-          <t>15 pcs</t>
-        </is>
-      </c>
-      <c r="G103" s="9" t="inlineStr"/>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>1/2 hotel</t>
-        </is>
-      </c>
-      <c r="J103" s="10" t="inlineStr"/>
-      <c r="K103" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L103" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M103" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N103" s="9" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="O103" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P103" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q103" s="9" t="inlineStr"/>
-      <c r="R103" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
-        </is>
-      </c>
-      <c r="S103" s="12" t="n">
-        <v>3</v>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -36907,484 +36897,508 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="A117" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Cook Carnitas Pork (→ NC Wk1 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S117" t="n">
+        <v>3</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Cook Carnitas Chicken (→ NC Wk1 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S118" t="n">
+        <v>3</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="E117" s="10" t="inlineStr">
+      <c r="E119" s="10" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr">
+      <c r="F119" s="9" t="inlineStr">
         <is>
           <t>3 pcs</t>
         </is>
       </c>
-      <c r="G117" s="9" t="inlineStr">
+      <c r="G119" s="9" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="H117" s="9" t="inlineStr">
+      <c r="H119" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I117" s="9" t="inlineStr"/>
-      <c r="J117" s="10" t="inlineStr">
+      <c r="I119" s="9" t="inlineStr"/>
+      <c r="J119" s="10" t="inlineStr">
         <is>
           <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
         </is>
       </c>
-      <c r="K117" s="9" t="inlineStr">
+      <c r="K119" s="9" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L117" s="6" t="inlineStr">
+      <c r="L119" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M117" s="9" t="inlineStr">
+      <c r="M119" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N117" s="9" t="inlineStr">
+      <c r="N119" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O117" s="9" t="inlineStr">
+      <c r="O119" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P117" s="9" t="n">
+      <c r="P119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" s="9" t="inlineStr"/>
-      <c r="R117" s="10" t="inlineStr">
+      <c r="Q119" s="9" t="inlineStr"/>
+      <c r="R119" s="10" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="7" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E118" s="8" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr">
+      <c r="F120" s="7" t="inlineStr">
         <is>
           <t>110 lbs</t>
         </is>
       </c>
-      <c r="G118" s="7" t="inlineStr"/>
-      <c r="H118" s="7" t="inlineStr">
+      <c r="G120" s="7" t="inlineStr"/>
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr">
+      <c r="I120" s="7" t="inlineStr">
         <is>
           <t>3u</t>
         </is>
       </c>
-      <c r="J118" s="8" t="inlineStr">
+      <c r="J120" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K118" s="7" t="inlineStr">
+      <c r="K120" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr">
+      <c r="L120" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M118" s="7" t="inlineStr">
+      <c r="M120" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N118" s="7" t="inlineStr">
+      <c r="N120" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O118" s="7" t="inlineStr">
+      <c r="O120" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P118" s="7" t="n">
+      <c r="P120" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" s="7" t="inlineStr"/>
-      <c r="R118" s="8" t="inlineStr">
+      <c r="Q120" s="7" t="inlineStr"/>
+      <c r="R120" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="7" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C121" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
         </is>
       </c>
-      <c r="F119" s="7" t="inlineStr">
+      <c r="F121" s="7" t="inlineStr">
         <is>
           <t>15 lbs</t>
         </is>
       </c>
-      <c r="G119" s="7" t="inlineStr"/>
-      <c r="H119" s="7" t="inlineStr">
+      <c r="G121" s="7" t="inlineStr"/>
+      <c r="H121" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I119" s="7" t="inlineStr">
+      <c r="I121" s="7" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="J119" s="8" t="inlineStr">
+      <c r="J121" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K119" s="7" t="inlineStr">
+      <c r="K121" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L119" s="5" t="inlineStr">
+      <c r="L121" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M119" s="7" t="inlineStr">
+      <c r="M121" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N119" s="7" t="inlineStr">
+      <c r="N121" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O119" s="7" t="inlineStr">
+      <c r="O121" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P119" s="7" t="n">
+      <c r="P121" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q119" s="7" t="inlineStr"/>
-      <c r="R119" s="8" t="inlineStr">
+      <c r="Q121" s="7" t="inlineStr"/>
+      <c r="R121" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="13" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B120" s="13" t="inlineStr">
+      <c r="B122" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C120" s="13" t="inlineStr">
+      <c r="C122" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D120" s="13" t="inlineStr">
+      <c r="D122" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E120" s="14" t="inlineStr">
+      <c r="E122" s="14" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F120" s="13" t="inlineStr">
+      <c r="F122" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G120" s="13" t="inlineStr"/>
-      <c r="H120" s="13" t="inlineStr">
+      <c r="G122" s="13" t="inlineStr"/>
+      <c r="H122" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I120" s="13" t="inlineStr">
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J120" s="14" t="inlineStr"/>
-      <c r="K120" s="13" t="inlineStr">
+      <c r="J122" s="14" t="inlineStr"/>
+      <c r="K122" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L120" s="5" t="inlineStr">
+      <c r="L122" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M120" s="13" t="inlineStr">
+      <c r="M122" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N120" s="13" t="inlineStr">
+      <c r="N122" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O120" s="13" t="inlineStr">
+      <c r="O122" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P120" s="13" t="inlineStr">
+      <c r="P122" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q120" s="13" t="inlineStr"/>
-      <c r="R120" s="14" t="inlineStr">
+      <c r="Q122" s="13" t="inlineStr"/>
+      <c r="R122" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D121" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E121" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef Massaman Curry → Dinner</t>
-        </is>
-      </c>
-      <c r="F121" s="15" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G121" s="15" t="inlineStr"/>
-      <c r="H121" s="15" t="inlineStr"/>
-      <c r="I121" s="15" t="inlineStr">
-        <is>
-          <t>3u</t>
-        </is>
-      </c>
-      <c r="J121" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K121" s="15" t="inlineStr"/>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M121" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N121" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O121" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P121" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q121" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R121" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E122" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="F122" s="15" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="G122" s="15" t="inlineStr"/>
-      <c r="H122" s="15" t="inlineStr"/>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="J122" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K122" s="15" t="inlineStr"/>
-      <c r="L122" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M122" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N122" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O122" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P122" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q122" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R122" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -37411,21 +37425,21 @@
       </c>
       <c r="E123" s="16" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner side</t>
+          <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
       <c r="F123" s="15" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G123" s="15" t="inlineStr"/>
-      <c r="H123" s="15" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I123" s="15" t="inlineStr"/>
+      <c r="H123" s="15" t="inlineStr"/>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>3u</t>
+        </is>
+      </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -37439,7 +37453,7 @@
       </c>
       <c r="M123" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N123" s="15" t="inlineStr">
@@ -37449,11 +37463,11 @@
       </c>
       <c r="O123" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P123" s="26" t="n">
-        <v>4</v>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P123" s="17" t="n">
+        <v>3</v>
       </c>
       <c r="Q123" s="15" t="inlineStr">
         <is>
@@ -37462,7 +37476,7 @@
       </c>
       <c r="R123" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -37489,24 +37503,24 @@
       </c>
       <c r="E124" s="16" t="inlineStr">
         <is>
-          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="G124" s="15" t="inlineStr"/>
       <c r="H124" s="15" t="inlineStr"/>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>0.5u</t>
         </is>
       </c>
       <c r="J124" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex fridge</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K124" s="15" t="inlineStr"/>
@@ -37517,30 +37531,186 @@
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N124" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O124" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P124" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q124" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R124" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N124" s="15" t="inlineStr">
+      <c r="B125" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O124" s="15" t="inlineStr">
+      <c r="C125" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E125" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="F125" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="G125" s="15" t="inlineStr"/>
+      <c r="H125" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I125" s="15" t="inlineStr"/>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K125" s="15" t="inlineStr"/>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M125" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N125" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O125" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P125" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q125" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R125" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+        </is>
+      </c>
+      <c r="F126" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G126" s="15" t="inlineStr"/>
+      <c r="H126" s="15" t="inlineStr"/>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex fridge</t>
+        </is>
+      </c>
+      <c r="K126" s="15" t="inlineStr"/>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M126" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N126" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O126" s="15" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P124" s="15" t="inlineStr">
+      <c r="P126" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q124" s="15" t="inlineStr">
+      <c r="Q126" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R124" s="16" t="inlineStr">
+      <c r="R126" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production</t>
         </is>

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -1457,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T96"/>
+  <dimension ref="A1:T101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7241,484 +7241,500 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Vindaloo Sauce (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>Reheat Pork/Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>60 lbs</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>10 oz</t>
         </is>
       </c>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>2 hotels + Vegan</t>
         </is>
       </c>
-      <c r="J72" s="8" t="inlineStr"/>
-      <c r="K72" s="7" t="inlineStr">
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M72" s="7" t="inlineStr">
+      <c r="M75" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N72" s="7" t="inlineStr">
+      <c r="N75" s="7" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O72" s="7" t="inlineStr">
+      <c r="O75" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P72" s="7" t="inlineStr">
+      <c r="P75" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q72" s="7" t="inlineStr"/>
-      <c r="R72" s="8" t="inlineStr">
+      <c r="Q75" s="7" t="inlineStr"/>
+      <c r="R75" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="13" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E73" s="14" t="inlineStr">
+      <c r="E76" s="14" t="inlineStr">
         <is>
           <t>Pineapple Rice (Fri Dinner)</t>
         </is>
       </c>
-      <c r="F73" s="13" t="inlineStr">
+      <c r="F76" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G73" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="H73" s="13" t="inlineStr">
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I73" s="13" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J73" s="14" t="inlineStr">
+      <c r="J76" s="14" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Oven rice</t>
         </is>
       </c>
-      <c r="K73" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L73" s="6" t="inlineStr">
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M73" s="13" t="inlineStr">
+      <c r="M76" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N73" s="13" t="inlineStr">
+      <c r="N76" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O73" s="13" t="inlineStr">
+      <c r="O76" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P73" s="13" t="inlineStr">
+      <c r="P76" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q73" s="13" t="inlineStr"/>
-      <c r="R73" s="14" t="inlineStr">
+      <c r="Q76" s="13" t="inlineStr"/>
+      <c r="R76" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C77" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E74" s="14" t="inlineStr">
+      <c r="E77" s="14" t="inlineStr">
         <is>
           <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="F74" s="13" t="inlineStr">
+      <c r="F77" s="13" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G77" s="13" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="H74" s="13" t="inlineStr">
+      <c r="H77" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I74" s="13" t="inlineStr">
+      <c r="I77" s="13" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J74" s="14" t="inlineStr">
+      <c r="J77" s="14" t="inlineStr">
         <is>
           <t>Frozen; steam at Bloor</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K77" s="13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="L77" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M74" s="13" t="inlineStr">
+      <c r="M77" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N74" s="13" t="inlineStr">
+      <c r="N77" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O74" s="13" t="inlineStr">
+      <c r="O77" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P74" s="13" t="inlineStr">
+      <c r="P77" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q74" s="13" t="inlineStr"/>
-      <c r="R74" s="14" t="inlineStr">
+      <c r="Q77" s="13" t="inlineStr"/>
+      <c r="R77" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B75" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C75" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E75" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr"/>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I75" s="15" t="inlineStr"/>
-      <c r="J75" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K75" s="15" t="inlineStr"/>
-      <c r="L75" s="19" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M75" s="15" t="inlineStr"/>
-      <c r="N75" s="15" t="inlineStr"/>
-      <c r="O75" s="15" t="inlineStr"/>
-      <c r="P75" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R75" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E76" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
-        </is>
-      </c>
-      <c r="F76" s="15" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G76" s="15" t="inlineStr"/>
-      <c r="H76" s="15" t="inlineStr"/>
-      <c r="I76" s="15" t="inlineStr"/>
-      <c r="J76" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M76" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N76" s="15" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="O76" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P76" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q76" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R76" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B77" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C77" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E77" s="16" t="inlineStr">
-        <is>
-          <t>HOT Pineapple Rice → Dinner side</t>
-        </is>
-      </c>
-      <c r="F77" s="15" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="G77" s="15" t="inlineStr"/>
-      <c r="H77" s="15" t="inlineStr"/>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="J77" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="K77" s="15" t="inlineStr"/>
-      <c r="L77" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M77" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N77" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O77" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P77" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q77" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R77" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -7745,546 +7761,523 @@
       </c>
       <c r="E78" s="16" t="inlineStr">
         <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr"/>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="19" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="M78" s="15" t="inlineStr"/>
+      <c r="N78" s="15" t="inlineStr"/>
+      <c r="O78" s="15" t="inlineStr"/>
+      <c r="P78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R78" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E79" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pork/Chicken/Halal + Veg Adobo → Dinner</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr"/>
+      <c r="H79" s="15" t="inlineStr"/>
+      <c r="I79" s="15" t="inlineStr"/>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K79" s="15" t="inlineStr"/>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N79" s="15" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O79" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P79" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q79" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R79" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>HOT Pineapple Rice → Dinner side</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr"/>
+      <c r="H80" s="15" t="inlineStr"/>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N80" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O80" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P80" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q80" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R80" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="inlineStr">
+        <is>
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F81" s="15" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G78" s="15" t="inlineStr"/>
-      <c r="H78" s="15" t="inlineStr"/>
-      <c r="I78" s="15" t="inlineStr">
+      <c r="G81" s="15" t="inlineStr"/>
+      <c r="H81" s="15" t="inlineStr"/>
+      <c r="I81" s="15" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J78" s="16" t="inlineStr">
+      <c r="J81" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="K81" s="15" t="inlineStr"/>
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M78" s="15" t="inlineStr">
+      <c r="M81" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N78" s="15" t="inlineStr">
+      <c r="N81" s="15" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O78" s="15" t="inlineStr">
+      <c r="O81" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P78" s="15" t="n">
+      <c r="P81" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" s="15" t="inlineStr">
+      <c r="Q81" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R78" s="16" t="inlineStr">
+      <c r="R81" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
+      <c r="I82" s="3" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr"/>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="K82" s="3" t="inlineStr"/>
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M79" s="3" t="inlineStr">
+      <c r="M82" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr">
+      <c r="N82" s="3" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O79" s="3" t="inlineStr">
+      <c r="O82" s="3" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P79" s="3" t="inlineStr">
+      <c r="P82" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q79" s="3" t="inlineStr">
+      <c r="Q82" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R79" s="4" t="inlineStr">
+      <c r="R82" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr"/>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I80" s="3" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K80" s="3" t="inlineStr"/>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M80" s="3" t="inlineStr">
+      <c r="M83" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N80" s="3" t="inlineStr">
+      <c r="N83" s="3" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O80" s="3" t="inlineStr">
+      <c r="O83" s="3" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P80" s="3" t="n">
+      <c r="P83" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q80" s="3" t="inlineStr">
+      <c r="Q83" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R80" s="4" t="inlineStr">
+      <c r="R83" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>80 lbs + 15 lbs</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="8" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K81" s="7" t="inlineStr">
+      <c r="K84" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="L84" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr">
+      <c r="M84" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N81" s="7" t="inlineStr">
+      <c r="N84" s="7" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O81" s="7" t="inlineStr">
+      <c r="O84" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P81" s="7" t="inlineStr"/>
-      <c r="Q81" s="7" t="inlineStr"/>
-      <c r="R81" s="8" t="inlineStr">
+      <c r="P84" s="7" t="inlineStr"/>
+      <c r="Q84" s="7" t="inlineStr"/>
+      <c r="R84" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>Griot Marinade</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr"/>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="I82" s="9" t="inlineStr"/>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
-        </is>
-      </c>
-      <c r="K82" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L82" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M82" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N82" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O82" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P82" s="9" t="inlineStr"/>
-      <c r="Q82" s="9" t="inlineStr"/>
-      <c r="R82" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S82" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>Cut/Marinate Pork Griot</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>30kg raw</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>1 bin/2 hotels</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr"/>
-      <c r="K83" s="9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M83" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N83" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O83" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P83" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q83" s="9" t="inlineStr"/>
-      <c r="R83" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S83" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Griot</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>25kg raw</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="J84" s="10" t="inlineStr"/>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M84" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N84" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O84" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P84" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="Q84" s="9" t="inlineStr"/>
-      <c r="R84" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S84" s="12" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -8310,68 +8303,60 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr"/>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr"/>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+          <t>For Griot Pork/Chicken/Tofu</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L85" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="9" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P85" s="9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P85" s="9" t="inlineStr"/>
       <c r="Q85" s="9" t="inlineStr"/>
       <c r="R85" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
-        </is>
-      </c>
-      <c r="S85" s="11" t="n">
-        <v>1</v>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+      <c r="S85" s="12" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="86">
@@ -8397,33 +8382,29 @@
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Cut/Marinate Pork Griot</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>30kg raw</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr"/>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>bus bin/hotel</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
+          <t>1 bin/2 hotels</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr"/>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L86" s="5" t="inlineStr">
@@ -8433,763 +8414,790 @@
       </c>
       <c r="M86" s="9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N86" s="9" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O86" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P86" s="9" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="N86" s="9" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O86" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P86" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Q86" s="9" t="inlineStr"/>
       <c r="R86" s="10" t="inlineStr">
         <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+      <c r="S86" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Griot</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>25kg raw</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr"/>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M87" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N87" s="9" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O87" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P87" s="9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Q87" s="9" t="inlineStr"/>
+      <c r="R87" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+      <c r="S87" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr"/>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M88" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N88" s="9" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O88" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P88" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Q88" s="9" t="inlineStr"/>
+      <c r="R88" s="10" t="inlineStr">
+        <is>
           <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
-      <c r="S86" s="11" t="n">
+      <c r="S88" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="13" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B87" s="13" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C87" s="13" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr"/>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M89" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N89" s="9" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O89" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P89" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q89" s="9" t="inlineStr"/>
+      <c r="R89" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S89" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Cook Pork Vindaloo (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D87" s="13" t="inlineStr">
+      <c r="P90" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S90" t="n">
+        <v>4</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E87" s="14" t="inlineStr">
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 2 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S91" t="n">
+        <v>4</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
         <is>
           <t>Carrot Cabbage Fry (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="F87" s="13" t="inlineStr">
+      <c r="F92" s="13" t="inlineStr">
         <is>
           <t>3 bins → 2 hotels</t>
         </is>
       </c>
-      <c r="G87" s="13" t="inlineStr"/>
-      <c r="H87" s="13" t="inlineStr">
+      <c r="G92" s="13" t="inlineStr"/>
+      <c r="H92" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I87" s="13" t="inlineStr">
+      <c r="I92" s="13" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J87" s="14" t="inlineStr">
+      <c r="J92" s="14" t="inlineStr">
         <is>
           <t>Stir-fry at LAN; send hot PM</t>
         </is>
       </c>
-      <c r="K87" s="13" t="inlineStr">
+      <c r="K92" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L87" s="6" t="inlineStr">
+      <c r="L92" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M87" s="13" t="inlineStr">
+      <c r="M92" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N87" s="13" t="inlineStr">
+      <c r="N92" s="13" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O87" s="13" t="inlineStr">
+      <c r="O92" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P87" s="13" t="inlineStr">
+      <c r="P92" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q87" s="13" t="inlineStr"/>
-      <c r="R87" s="14" t="inlineStr">
+      <c r="Q92" s="13" t="inlineStr"/>
+      <c r="R92" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="7" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J88" s="8" t="inlineStr">
+      <c r="J93" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr">
+      <c r="K93" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M88" s="7" t="inlineStr">
+      <c r="M93" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N88" s="7" t="inlineStr">
+      <c r="N93" s="7" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O88" s="7" t="inlineStr">
+      <c r="O93" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P88" s="7" t="inlineStr">
+      <c r="P93" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q88" s="7" t="inlineStr"/>
-      <c r="R88" s="8" t="inlineStr">
+      <c r="Q93" s="7" t="inlineStr"/>
+      <c r="R93" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="13" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B89" s="13" t="inlineStr">
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C89" s="13" t="inlineStr">
+      <c r="C94" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D89" s="13" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E89" s="14" t="inlineStr">
+      <c r="E94" s="14" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F89" s="13" t="inlineStr">
+      <c r="F94" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G89" s="13" t="inlineStr"/>
-      <c r="H89" s="13" t="inlineStr"/>
-      <c r="I89" s="13" t="inlineStr">
+      <c r="G94" s="13" t="inlineStr"/>
+      <c r="H94" s="13" t="inlineStr"/>
+      <c r="I94" s="13" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J89" s="14" t="inlineStr"/>
-      <c r="K89" s="13" t="inlineStr">
+      <c r="J94" s="14" t="inlineStr"/>
+      <c r="K94" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="L94" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M89" s="13" t="inlineStr">
+      <c r="M94" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N89" s="13" t="inlineStr">
+      <c r="N94" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O89" s="13" t="inlineStr">
+      <c r="O94" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P89" s="13" t="inlineStr">
+      <c r="P94" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q89" s="13" t="inlineStr"/>
-      <c r="R89" s="14" t="inlineStr">
+      <c r="Q94" s="13" t="inlineStr"/>
+      <c r="R94" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="9" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C90" s="9" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
+      <c r="D95" s="9" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F90" s="9" t="inlineStr">
+      <c r="F95" s="9" t="inlineStr">
         <is>
           <t>2 pcs</t>
         </is>
       </c>
-      <c r="G90" s="9" t="inlineStr">
+      <c r="G95" s="9" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="H90" s="9" t="inlineStr">
+      <c r="H95" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I90" s="9" t="inlineStr">
+      <c r="I95" s="9" t="inlineStr">
         <is>
           <t>4" hotel</t>
         </is>
       </c>
-      <c r="J90" s="10" t="inlineStr">
+      <c r="J95" s="10" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
       </c>
-      <c r="K90" s="9" t="inlineStr">
+      <c r="K95" s="9" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L90" s="6" t="inlineStr">
+      <c r="L95" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M90" s="9" t="inlineStr">
+      <c r="M95" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N90" s="9" t="inlineStr">
+      <c r="N95" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O90" s="9" t="inlineStr">
+      <c r="O95" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P90" s="9" t="n">
+      <c r="P95" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" s="9" t="inlineStr"/>
-      <c r="R90" s="10" t="inlineStr">
+      <c r="Q95" s="9" t="inlineStr"/>
+      <c r="R95" s="10" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E91" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F91" s="15" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G91" s="15" t="inlineStr"/>
-      <c r="H91" s="15" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I91" s="15" t="inlineStr"/>
-      <c r="J91" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K91" s="15" t="inlineStr"/>
-      <c r="L91" s="19" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M91" s="15" t="inlineStr"/>
-      <c r="N91" s="15" t="inlineStr"/>
-      <c r="O91" s="15" t="inlineStr"/>
-      <c r="P91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R91" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B92" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C92" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E92" s="16" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="F92" s="15" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G92" s="15" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="H92" s="15" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I92" s="15" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="J92" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M92" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N92" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O92" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P92" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q92" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R92" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E93" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="F93" s="15" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="G93" s="15" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="H93" s="15" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>1 × 4" hotel</t>
-        </is>
-      </c>
-      <c r="J93" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K93" s="15" t="inlineStr"/>
-      <c r="L93" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M93" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N93" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O93" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P93" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q93" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R93" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B94" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D94" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="inlineStr">
-        <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
-        </is>
-      </c>
-      <c r="F94" s="15" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="G94" s="15" t="inlineStr"/>
-      <c r="H94" s="15" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="J94" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="K94" s="15" t="inlineStr"/>
-      <c r="L94" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M94" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N94" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O94" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P94" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q94" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R94" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D95" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E95" s="16" t="inlineStr">
-        <is>
-          <t>HOT Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="F95" s="15" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="G95" s="15" t="inlineStr"/>
-      <c r="H95" s="15" t="inlineStr"/>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J95" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K95" s="15" t="inlineStr"/>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M95" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N95" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O95" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P95" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q95" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R95" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -9216,50 +9224,452 @@
       </c>
       <c r="E96" s="16" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="G96" s="15" t="inlineStr"/>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I96" s="15" t="inlineStr"/>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex fridge</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K96" s="15" t="inlineStr"/>
-      <c r="L96" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L96" s="19" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr"/>
       <c r="N96" s="15" t="inlineStr"/>
       <c r="O96" s="15" t="inlineStr"/>
-      <c r="P96" s="15" t="inlineStr">
+      <c r="P96" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R96" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G97" s="15" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J97" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K97" s="15" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M97" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N97" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O97" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P97" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q97" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R97" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B98" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>1 × 4" hotel</t>
+        </is>
+      </c>
+      <c r="J98" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="inlineStr"/>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M98" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N98" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O98" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P98" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q98" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R98" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E99" s="16" t="inlineStr">
+        <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr"/>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J99" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M99" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N99" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O99" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P99" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q99" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R99" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr"/>
+      <c r="H100" s="15" t="inlineStr"/>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J100" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="inlineStr"/>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M100" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N100" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O100" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P100" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q100" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R100" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr"/>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="J101" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="K101" s="15" t="inlineStr"/>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M101" s="15" t="inlineStr"/>
+      <c r="N101" s="15" t="inlineStr"/>
+      <c r="O101" s="15" t="inlineStr"/>
+      <c r="P101" s="15" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="Q96" s="15" t="inlineStr">
+      <c r="Q101" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R96" s="16" t="inlineStr">
+      <c r="R101" s="16" t="inlineStr">
         <is>
           <t>Produced: LAN day-before</t>
         </is>
@@ -12552,7 +12962,7 @@
       <c r="Q39" s="7" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Mon–Tue Production</t>
+          <t>Produced: Wk. 1 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -12638,7 +13048,7 @@
       <c r="Q40" s="7" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Tuesday Production</t>
+          <t>Produced: Wk. 1 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -12956,7 +13366,7 @@
       </c>
       <c r="R44" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Mon–Tue Production</t>
+          <t>Produced: Wk. 1 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -13749,7 +14159,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>Caribbean Stew</t>
+          <t>Caribbean Chicken + Chickpea Curry (→ Wk3 Tue Dinner)</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -18593,7 +19003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T108"/>
+  <dimension ref="A1:T113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -26713,744 +27123,1154 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="A100" t="n">
+        <v>3</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Vindaloo Sauce (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>recipe</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Stove; simmer; cool in cambro; use same day for marinade</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>1</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S100" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Marinate Pork in Vindaloo (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S101" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Coat in Vindaloo Sauce; cover; chill overnight</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S102" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="D103" s="9" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="E100" s="10" t="inlineStr">
+      <c r="E103" s="10" t="inlineStr">
         <is>
           <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
-      <c r="F100" s="9" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr"/>
-      <c r="H100" s="9" t="inlineStr">
+      <c r="G103" s="9" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr">
         <is>
           <t>bus bin/bag</t>
         </is>
       </c>
-      <c r="I100" s="9" t="inlineStr">
+      <c r="I103" s="9" t="inlineStr">
         <is>
           <t>4 items</t>
         </is>
       </c>
-      <c r="J100" s="10" t="inlineStr">
+      <c r="J103" s="10" t="inlineStr">
         <is>
           <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
-      <c r="K100" s="9" t="inlineStr">
+      <c r="K103" s="9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L100" s="6" t="inlineStr">
+      <c r="L103" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M100" s="9" t="inlineStr">
+      <c r="M103" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N100" s="9" t="inlineStr">
+      <c r="N103" s="9" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O100" s="9" t="inlineStr">
+      <c r="O103" s="9" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P100" s="9" t="inlineStr">
+      <c r="P103" s="9" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="Q100" s="9" t="inlineStr"/>
-      <c r="R100" s="10" t="inlineStr">
+      <c r="Q103" s="9" t="inlineStr"/>
+      <c r="R103" s="10" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
-      <c r="S100" s="11" t="n">
+      <c r="S103" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="9" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="E101" s="10" t="inlineStr">
+      <c r="E104" s="10" t="inlineStr">
         <is>
           <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
         </is>
       </c>
-      <c r="F101" s="9" t="inlineStr">
+      <c r="F104" s="9" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr"/>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
-      <c r="J101" s="10" t="inlineStr">
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr"/>
+      <c r="I104" s="9" t="inlineStr"/>
+      <c r="J104" s="10" t="inlineStr">
         <is>
           <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
         </is>
       </c>
-      <c r="K101" s="9" t="inlineStr">
+      <c r="K104" s="9" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L101" s="6" t="inlineStr">
+      <c r="L104" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M101" s="9" t="inlineStr">
+      <c r="M104" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N101" s="9" t="inlineStr">
+      <c r="N104" s="9" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O101" s="9" t="inlineStr">
+      <c r="O104" s="9" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P101" s="9" t="inlineStr">
+      <c r="P104" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q101" s="9" t="inlineStr"/>
-      <c r="R101" s="10" t="inlineStr">
+      <c r="Q104" s="9" t="inlineStr"/>
+      <c r="R104" s="10" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
-      <c r="S101" s="11" t="n">
+      <c r="S104" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D105" s="9" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="E102" s="10" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
+      <c r="F105" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="G102" s="9" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr">
+      <c r="G105" s="9" t="inlineStr"/>
+      <c r="H105" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
+      <c r="I105" s="9" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J102" s="10" t="inlineStr">
+      <c r="J105" s="10" t="inlineStr">
         <is>
           <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
         </is>
       </c>
-      <c r="K102" s="9" t="inlineStr">
+      <c r="K105" s="9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M102" s="9" t="inlineStr">
+      <c r="M105" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N102" s="9" t="inlineStr">
+      <c r="N105" s="9" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O102" s="9" t="inlineStr">
+      <c r="O105" s="9" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P102" s="9" t="inlineStr">
+      <c r="P105" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q102" s="9" t="inlineStr"/>
-      <c r="R102" s="10" t="inlineStr">
+      <c r="Q105" s="9" t="inlineStr"/>
+      <c r="R105" s="10" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Sunday Lunch</t>
         </is>
       </c>
-      <c r="S102" s="11" t="n">
+      <c r="S105" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="13" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B103" s="13" t="inlineStr">
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C103" s="13" t="inlineStr">
+      <c r="C106" s="13" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D103" s="13" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E103" s="14" t="inlineStr">
+      <c r="E106" s="14" t="inlineStr">
         <is>
           <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
         </is>
       </c>
-      <c r="F103" s="13" t="inlineStr">
+      <c r="F106" s="13" t="inlineStr">
         <is>
           <t>110lbs</t>
         </is>
       </c>
-      <c r="G103" s="13" t="inlineStr">
+      <c r="G106" s="13" t="inlineStr">
         <is>
           <t>12 oz</t>
         </is>
       </c>
-      <c r="H103" s="13" t="inlineStr">
+      <c r="H106" s="13" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J103" s="14" t="inlineStr">
+      <c r="J106" s="14" t="inlineStr">
         <is>
           <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
         </is>
       </c>
-      <c r="K103" s="13" t="inlineStr">
+      <c r="K106" s="13" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M103" s="13" t="inlineStr">
+      <c r="M106" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N103" s="13" t="inlineStr">
+      <c r="N106" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O103" s="13" t="inlineStr">
+      <c r="O106" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P103" s="13" t="inlineStr">
+      <c r="P106" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q103" s="13" t="inlineStr"/>
-      <c r="R103" s="14" t="inlineStr">
+      <c r="Q106" s="13" t="inlineStr"/>
+      <c r="R106" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
-      <c r="S103" s="12" t="n">
+      <c r="S106" s="12" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Cook Pork Vindaloo (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>40 lbs cooked</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S107" t="n">
+        <v>4</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Cook Chicken Vindaloo — Halal (→ Wk. 4 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S108" t="n">
+        <v>4</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B104" s="13" t="inlineStr">
+      <c r="B109" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C104" s="13" t="inlineStr">
+      <c r="C109" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D104" s="13" t="inlineStr">
+      <c r="D109" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E104" s="14" t="inlineStr">
+      <c r="E109" s="14" t="inlineStr">
         <is>
           <t>Potato Wedges (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="F104" s="13" t="inlineStr">
+      <c r="F109" s="13" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G104" s="13" t="inlineStr"/>
-      <c r="H104" s="13" t="inlineStr"/>
-      <c r="I104" s="13" t="inlineStr">
+      <c r="G109" s="13" t="inlineStr"/>
+      <c r="H109" s="13" t="inlineStr"/>
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J104" s="14" t="inlineStr">
+      <c r="J109" s="14" t="inlineStr">
         <is>
           <t>Purchased frozen; oven</t>
         </is>
       </c>
-      <c r="K104" s="13" t="inlineStr">
+      <c r="K109" s="13" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L104" s="5" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M104" s="13" t="inlineStr">
+      <c r="M109" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N104" s="13" t="inlineStr">
+      <c r="N109" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O104" s="13" t="inlineStr">
+      <c r="O109" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P104" s="13" t="inlineStr">
+      <c r="P109" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q104" s="13" t="inlineStr"/>
-      <c r="R104" s="14" t="inlineStr">
+      <c r="Q109" s="13" t="inlineStr"/>
+      <c r="R109" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="15" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B105" s="15" t="inlineStr">
+      <c r="B110" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C105" s="15" t="inlineStr">
+      <c r="C110" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D105" s="15" t="inlineStr">
+      <c r="D110" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E105" s="16" t="inlineStr">
+      <c r="E110" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F105" s="15" t="inlineStr">
+      <c r="F110" s="15" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="G105" s="15" t="inlineStr"/>
-      <c r="H105" s="15" t="inlineStr">
+      <c r="G110" s="15" t="inlineStr"/>
+      <c r="H110" s="15" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="I105" s="15" t="inlineStr"/>
-      <c r="J105" s="16" t="inlineStr">
+      <c r="I110" s="15" t="inlineStr"/>
+      <c r="J110" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="K105" s="15" t="inlineStr"/>
-      <c r="L105" s="19" t="inlineStr">
+      <c r="K110" s="15" t="inlineStr"/>
+      <c r="L110" s="19" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="M105" s="15" t="inlineStr"/>
-      <c r="N105" s="15" t="inlineStr"/>
-      <c r="O105" s="15" t="inlineStr"/>
-      <c r="P105" s="18" t="n">
+      <c r="M110" s="15" t="inlineStr"/>
+      <c r="N110" s="15" t="inlineStr"/>
+      <c r="O110" s="15" t="inlineStr"/>
+      <c r="P110" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" s="15" t="inlineStr">
+      <c r="Q110" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R105" s="16" t="inlineStr">
+      <c r="R110" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="15" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B106" s="15" t="inlineStr">
+      <c r="B111" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C106" s="15" t="inlineStr">
+      <c r="C111" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D106" s="15" t="inlineStr">
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E106" s="16" t="inlineStr">
+      <c r="E111" s="16" t="inlineStr">
         <is>
           <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
-      <c r="F106" s="15" t="inlineStr">
+      <c r="F111" s="15" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="G106" s="15" t="inlineStr"/>
-      <c r="H106" s="15" t="inlineStr">
+      <c r="G111" s="15" t="inlineStr"/>
+      <c r="H111" s="15" t="inlineStr">
         <is>
           <t>boxes</t>
         </is>
       </c>
-      <c r="I106" s="15" t="inlineStr">
+      <c r="I111" s="15" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="J106" s="16" t="inlineStr">
+      <c r="J111" s="16" t="inlineStr">
         <is>
           <t>Vendor → Rex | Driver collects ordered pizza</t>
         </is>
       </c>
-      <c r="K106" s="15" t="inlineStr"/>
-      <c r="L106" s="20" t="inlineStr">
+      <c r="K111" s="15" t="inlineStr"/>
+      <c r="L111" s="20" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="M106" s="15" t="inlineStr">
+      <c r="M111" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N106" s="15" t="inlineStr">
+      <c r="N111" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O106" s="15" t="inlineStr">
+      <c r="O111" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P106" s="18" t="n">
+      <c r="P111" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" s="15" t="inlineStr">
+      <c r="Q111" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R106" s="16" t="inlineStr">
+      <c r="R111" s="16" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B107" s="15" t="inlineStr">
+      <c r="B112" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C107" s="15" t="inlineStr">
+      <c r="C112" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D107" s="15" t="inlineStr">
+      <c r="D112" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E107" s="16" t="inlineStr">
+      <c r="E112" s="16" t="inlineStr">
         <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="F107" s="15" t="inlineStr">
+      <c r="F112" s="15" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="G107" s="15" t="inlineStr"/>
-      <c r="H107" s="15" t="inlineStr">
+      <c r="G112" s="15" t="inlineStr"/>
+      <c r="H112" s="15" t="inlineStr">
         <is>
           <t>bus bin/bag</t>
         </is>
       </c>
-      <c r="I107" s="15" t="inlineStr">
+      <c r="I112" s="15" t="inlineStr">
         <is>
           <t>4 items</t>
         </is>
       </c>
-      <c r="J107" s="16" t="inlineStr">
+      <c r="J112" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex fridge</t>
         </is>
       </c>
-      <c r="K107" s="15" t="inlineStr"/>
-      <c r="L107" s="6" t="inlineStr">
+      <c r="K112" s="15" t="inlineStr"/>
+      <c r="L112" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M107" s="15" t="inlineStr">
+      <c r="M112" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N107" s="15" t="inlineStr">
+      <c r="N112" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O107" s="15" t="inlineStr">
+      <c r="O112" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P107" s="15" t="inlineStr">
+      <c r="P112" s="15" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="Q107" s="15" t="inlineStr">
+      <c r="Q112" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R107" s="16" t="inlineStr">
+      <c r="R112" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="15" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B108" s="15" t="inlineStr">
+      <c r="B113" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C108" s="15" t="inlineStr">
+      <c r="C113" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D108" s="15" t="inlineStr">
+      <c r="D113" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E108" s="16" t="inlineStr">
+      <c r="E113" s="16" t="inlineStr">
         <is>
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="F108" s="15" t="inlineStr">
+      <c r="F113" s="15" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G108" s="15" t="inlineStr">
+      <c r="G113" s="15" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="H108" s="15" t="inlineStr">
+      <c r="H113" s="15" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I108" s="15" t="inlineStr">
+      <c r="I113" s="15" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J108" s="16" t="inlineStr">
+      <c r="J113" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K108" s="15" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="K113" s="15" t="inlineStr"/>
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M108" s="15" t="inlineStr">
+      <c r="M113" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N108" s="15" t="inlineStr">
+      <c r="N113" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O108" s="15" t="inlineStr">
+      <c r="O113" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P108" s="15" t="inlineStr">
+      <c r="P113" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q108" s="15" t="inlineStr">
+      <c r="Q113" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R108" s="16" t="inlineStr">
+      <c r="R113" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Dinner (same day)</t>
         </is>

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -1788,7 +1788,7 @@
       <c r="I4" s="9" t="inlineStr"/>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>PREP ONLY — no oven. Shape, bread, freeze in blast chiller all day.</t>
+          <t>Bread, shape, blast-chill; NO oven — all hands-on</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -19549,7 +19549,7 @@
       <c r="I5" s="9" t="inlineStr"/>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>PREP ONLY — no oven. Shape, bread, freeze; blast chiller</t>
+          <t>Bread, shape, blast-chill; NO oven — all hands-on</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
+          <t>DINNER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -2733,7 +2733,7 @@
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Monday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       <c r="Q30" s="7" t="inlineStr"/>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Tuesday Lunch</t>
+          <t>Produced: Wk. 4 Wednesday Production (cold chain via Rex; prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       <c r="Q50" s="7" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Wednesday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T113"/>
+  <dimension ref="A1:T114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16772,89 +16772,86 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Refried Beans (→ Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | ⚠ CONFIRM cook time</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E77" s="14" t="inlineStr">
-        <is>
-          <t>Beef Sausages (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="F77" s="13" t="inlineStr">
-        <is>
-          <t>100 pcs</t>
-        </is>
-      </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="H77" s="13" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="J77" s="14" t="inlineStr">
-        <is>
-          <t>Cook sausages for dinner service</t>
-        </is>
-      </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M77" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N77" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O77" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P77" s="13" t="n">
+      <c r="P77" t="n">
+        <v>3</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Friday Dinner</t>
+        </is>
+      </c>
+      <c r="S77" t="n">
         <v>2</v>
-      </c>
-      <c r="Q77" s="13" t="inlineStr"/>
-      <c r="R77" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Thursday Dinner</t>
-        </is>
       </c>
     </row>
     <row r="78">
@@ -16880,12 +16877,12 @@
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Halal Sausages (Thu Dinner)</t>
+          <t>Beef Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>60 pcs</t>
+          <t>100 pcs</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
@@ -16900,7 +16897,7 @@
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
@@ -16934,7 +16931,7 @@
         </is>
       </c>
       <c r="P78" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="13" t="inlineStr"/>
       <c r="R78" s="14" t="inlineStr">
@@ -16966,12 +16963,12 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>Vegan Sausages (Thu Dinner)</t>
+          <t>Halal Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>15 pcs</t>
+          <t>60 pcs</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
@@ -16986,7 +16983,7 @@
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
-          <t>0.5 hotel</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
@@ -17020,7 +17017,7 @@
         </is>
       </c>
       <c r="P79" s="13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q79" s="13" t="inlineStr"/>
       <c r="R79" s="14" t="inlineStr">
@@ -17052,17 +17049,17 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
+          <t>Vegan Sausages (Thu Dinner)</t>
         </is>
       </c>
       <c r="F80" s="13" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>15 pcs</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>1 pc</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -17072,17 +17069,17 @@
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>0.5 hotel</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>Combi</t>
+          <t>Cook sausages for dinner service</t>
         </is>
       </c>
       <c r="K80" s="13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L80" s="5" t="inlineStr">
@@ -17105,10 +17102,8 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P80" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="P80" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q80" s="13" t="inlineStr"/>
       <c r="R80" s="14" t="inlineStr">
@@ -17118,172 +17113,174 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>Combi</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M81" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N81" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O81" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P81" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q81" s="13" t="inlineStr"/>
+      <c r="R81" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Thursday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>Reheat Gravy (Thu Dinner + hold portion for Sat Dinner Meatloaf)</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>2 batches</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr">
+      <c r="J82" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged; portion ½ for Thu PM, hold ½ at Bloor for Sat</t>
         </is>
       </c>
-      <c r="K81" s="7" t="inlineStr">
+      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M81" s="7" t="inlineStr">
+      <c r="M82" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N81" s="7" t="inlineStr">
+      <c r="N82" s="7" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O81" s="7" t="inlineStr">
+      <c r="O82" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P81" s="7" t="inlineStr">
+      <c r="P82" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q81" s="7" t="inlineStr"/>
-      <c r="R81" s="8" t="inlineStr">
+      <c r="Q82" s="7" t="inlineStr"/>
+      <c r="R82" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Sunday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B82" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C82" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E82" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr">
-        <is>
-          <t>250 pcs</t>
-        </is>
-      </c>
-      <c r="G82" s="15" t="inlineStr">
-        <is>
-          <t>2 pcs</t>
-        </is>
-      </c>
-      <c r="H82" s="15" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I82" s="15" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="J82" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K82" s="15" t="inlineStr"/>
-      <c r="L82" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M82" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N82" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O82" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P82" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q82" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R82" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -17310,17 +17307,17 @@
       </c>
       <c r="E83" s="16" t="inlineStr">
         <is>
-          <t>HOT Mashed Potato → Dinner</t>
+          <t>HOT Beef/Halal/Vegan Sausages → Dinner</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>250 pcs</t>
         </is>
       </c>
       <c r="G83" s="15" t="inlineStr">
         <is>
-          <t>8 oz</t>
+          <t>2 pcs</t>
         </is>
       </c>
       <c r="H83" s="15" t="inlineStr">
@@ -17330,7 +17327,7 @@
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>6 hotels</t>
         </is>
       </c>
       <c r="J83" s="16" t="inlineStr">
@@ -17346,23 +17343,21 @@
       </c>
       <c r="M83" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" s="15" t="inlineStr">
         <is>
-          <t>SATURDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O83" s="15" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P83" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P83" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="Q83" s="15" t="inlineStr">
         <is>
@@ -17371,7 +17366,7 @@
       </c>
       <c r="R83" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Production (via LAN)</t>
+          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -17398,17 +17393,17 @@
       </c>
       <c r="E84" s="16" t="inlineStr">
         <is>
-          <t>HOT Peas &amp; Carrot → Dinner side</t>
+          <t>HOT Mashed Potato → Dinner</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>8 oz</t>
         </is>
       </c>
       <c r="H84" s="15" t="inlineStr">
@@ -17434,17 +17429,17 @@
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N84" s="15" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="O84" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P84" s="15" t="inlineStr">
@@ -17459,7 +17454,7 @@
       </c>
       <c r="R84" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
+          <t>Produced: Wk. 1 Saturday Production (via LAN)</t>
         </is>
       </c>
     </row>
@@ -17486,15 +17481,19 @@
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
-          <t>HOT Gravy → Dinner</t>
+          <t>HOT Peas &amp; Carrot → Dinner side</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>½ batch</t>
-        </is>
-      </c>
-      <c r="G85" s="15" t="inlineStr"/>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
       <c r="H85" s="15" t="inlineStr">
         <is>
           <t>hotel</t>
@@ -17502,7 +17501,7 @@
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="J85" s="16" t="inlineStr">
@@ -17533,7 +17532,7 @@
       </c>
       <c r="P85" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q85" s="15" t="inlineStr">
@@ -17570,34 +17569,34 @@
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>HOT Gravy → Dinner</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>½ batch</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr"/>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K86" s="15" t="inlineStr"/>
-      <c r="L86" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
@@ -17605,14 +17604,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="N86" s="15" t="inlineStr"/>
+      <c r="N86" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
       <c r="O86" s="15" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P86" s="15" t="n">
-        <v>4</v>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P86" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="Q86" s="15" t="inlineStr">
         <is>
@@ -17621,7 +17626,7 @@
       </c>
       <c r="R86" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk.2 Wed Production (LAN)</t>
+          <t>Produced: Wk. 2 Thursday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17653,7 @@
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
         </is>
       </c>
       <c r="F87" s="15" t="inlineStr">
@@ -17689,7 +17694,7 @@
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P87" s="18" t="n">
+      <c r="P87" s="15" t="n">
         <v>4</v>
       </c>
       <c r="Q87" s="15" t="inlineStr">
@@ -17704,242 +17709,231 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>Cold Slaw → Fri Lunch side</t>
+        </is>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr"/>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K88" s="15" t="inlineStr"/>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M88" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N88" s="15" t="inlineStr"/>
+      <c r="O88" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P88" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q88" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R88" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk.2 Wed Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>HOT Crispy Falafel → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K88" s="3" t="inlineStr"/>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M88" s="3" t="inlineStr">
+      <c r="M89" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N88" s="3" t="inlineStr"/>
-      <c r="O88" s="3" t="inlineStr">
+      <c r="N89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P88" s="3" t="inlineStr">
+      <c r="P89" s="3" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="Q88" s="3" t="inlineStr">
+      <c r="Q89" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R88" s="4" t="inlineStr">
+      <c r="R89" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk.2 Fri Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>30 pcs</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P89" t="n">
+      <c r="P90" t="n">
         <v>2</v>
       </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Friday Lunch</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C90" s="13" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D90" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E90" s="14" t="inlineStr">
-        <is>
-          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="F90" s="13" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G90" s="13" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="H90" s="13" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="J90" s="14" t="inlineStr">
-        <is>
-          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
-        </is>
-      </c>
-      <c r="K90" s="13" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M90" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N90" s="13" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O90" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P90" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q90" s="13" t="inlineStr"/>
-      <c r="R90" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Saturday Lunch</t>
-        </is>
-      </c>
-      <c r="S90" s="12" t="n">
-        <v>8</v>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Serves: same day (purchased frozen)</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -17965,17 +17959,17 @@
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>Vegan CONC Salad Mix (→ Wk3 Sat Lunch)</t>
+          <t>Beef CONC Salad Mix (→ Wk3 Sat Lunch)</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>6 oz</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -17985,7 +17979,7 @@
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="J91" s="14" t="inlineStr">
@@ -17995,7 +17989,7 @@
       </c>
       <c r="K91" s="13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="L91" s="5" t="inlineStr">
@@ -18019,7 +18013,7 @@
         </is>
       </c>
       <c r="P91" s="13" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="13" t="inlineStr"/>
       <c r="R91" s="14" t="inlineStr">
@@ -18032,90 +18026,92 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="A92" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C92" s="13" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t>Prep Butternut Squash (→ Sat Dinner side)</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="G92" s="9" t="inlineStr"/>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="J92" s="10" t="inlineStr">
-        <is>
-          <t>Peel/dice at LAN; chill overnight</t>
-        </is>
-      </c>
-      <c r="K92" s="9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L92" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M92" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N92" s="9" t="inlineStr">
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>Vegan CONC Salad Mix (→ Wk3 Sat Lunch)</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>Cook; send Rex Sat PM; pull Wk3 Fri AM</t>
+        </is>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M92" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N92" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O92" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P92" s="9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="Q92" s="9" t="inlineStr"/>
-      <c r="R92" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Saturday Dinner</t>
-        </is>
-      </c>
-      <c r="S92" s="11" t="n">
-        <v>1</v>
+      <c r="O92" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P92" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q92" s="13" t="inlineStr"/>
+      <c r="R92" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Saturday Lunch</t>
+        </is>
+      </c>
+      <c r="S92" s="12" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="93">
@@ -18141,32 +18137,38 @@
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
+          <t>Prep Butternut Squash (→ Sat Dinner side)</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>7 loaves</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="G93" s="9" t="inlineStr"/>
-      <c r="H93" s="9" t="inlineStr"/>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>7 trays</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="J93" s="10" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K93" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="L93" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>Peel/dice at LAN; chill overnight</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M93" s="9" t="inlineStr">
@@ -18184,8 +18186,10 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P93" s="9" t="n">
-        <v>4</v>
+      <c r="P93" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
       </c>
       <c r="Q93" s="9" t="inlineStr"/>
       <c r="R93" s="10" t="inlineStr">
@@ -18220,19 +18224,19 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
+          <t>Prep &amp; Tray Meatloaf (raw) — 7 Beef (→ Sat Dinner)</t>
         </is>
       </c>
       <c r="F94" s="9" t="inlineStr">
         <is>
-          <t>1 loaves</t>
+          <t>7 loaves</t>
         </is>
       </c>
       <c r="G94" s="9" t="inlineStr"/>
       <c r="H94" s="9" t="inlineStr"/>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>1 tray</t>
+          <t>7 trays</t>
         </is>
       </c>
       <c r="J94" s="10" t="inlineStr">
@@ -18241,7 +18245,7 @@
         </is>
       </c>
       <c r="K94" s="9" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
@@ -18264,7 +18268,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q94" s="9" t="inlineStr"/>
       <c r="R94" s="10" t="inlineStr">
@@ -18277,252 +18281,249 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>Prep &amp; Tray Vegan Meatloaf (raw) — (→ Sat Dinner)</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>1 loaves</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr"/>
+      <c r="H95" s="9" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>1 tray</t>
+        </is>
+      </c>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N95" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O95" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="P95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="9" t="inlineStr"/>
+      <c r="R95" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Saturday Dinner</t>
+        </is>
+      </c>
+      <c r="S95" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>Reheat Refried Beans (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J95" s="8" t="inlineStr">
+      <c r="J96" s="8" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE — Reheat bagged</t>
         </is>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="K96" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M95" s="7" t="inlineStr">
+      <c r="M96" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N95" s="7" t="inlineStr">
+      <c r="N96" s="7" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O95" s="7" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P95" s="7" t="inlineStr">
+      <c r="P96" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q95" s="7" t="inlineStr"/>
-      <c r="R95" s="8" t="inlineStr">
+      <c r="Q96" s="7" t="inlineStr"/>
+      <c r="R96" s="8" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>Arroz con Pollo</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>6 hotels</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="H97" s="13" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr"/>
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K97" s="13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M97" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N97" s="13" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O97" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P97" s="13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q97" s="13" t="inlineStr"/>
+      <c r="R97" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B96" s="13" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C96" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D96" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="inlineStr">
-        <is>
-          <t>Arroz con Pollo</t>
-        </is>
-      </c>
-      <c r="F96" s="13" t="inlineStr">
-        <is>
-          <t>6 hotels</t>
-        </is>
-      </c>
-      <c r="G96" s="13" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="H96" s="13" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I96" s="13" t="inlineStr"/>
-      <c r="J96" s="14" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K96" s="13" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="L96" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M96" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N96" s="13" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O96" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P96" s="13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q96" s="13" t="inlineStr"/>
-      <c r="R96" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B97" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E97" s="16" t="inlineStr">
-        <is>
-          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
-        </is>
-      </c>
-      <c r="F97" s="15" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="G97" s="15" t="inlineStr"/>
-      <c r="H97" s="15" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>2½ hotels</t>
-        </is>
-      </c>
-      <c r="J97" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K97" s="15" t="inlineStr"/>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M97" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N97" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O97" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P97" s="17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q97" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R97" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -18549,23 +18550,23 @@
       </c>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>HOT Refried Beans → Dinner side</t>
+          <t>HOT Arroz con Pollo + Vegan Arroz → Dinner</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>2½ hotels</t>
         </is>
       </c>
       <c r="J98" s="16" t="inlineStr">
@@ -18586,18 +18587,16 @@
       </c>
       <c r="N98" s="15" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="O98" s="15" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P98" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P98" s="17" t="n">
+        <v>2.5</v>
       </c>
       <c r="Q98" s="15" t="inlineStr">
         <is>
@@ -18606,7 +18605,7 @@
       </c>
       <c r="R98" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Wednesday Production</t>
+          <t>Produced: Wk. 2 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -18633,112 +18632,136 @@
       </c>
       <c r="E99" s="16" t="inlineStr">
         <is>
+          <t>HOT Refried Beans → Dinner side</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr"/>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J99" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="inlineStr"/>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M99" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N99" s="15" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O99" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P99" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q99" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R99" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Wednesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B100" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
           <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
         </is>
       </c>
-      <c r="F99" s="15" t="inlineStr">
+      <c r="F100" s="15" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="G99" s="15" t="inlineStr"/>
-      <c r="H99" s="15" t="inlineStr"/>
-      <c r="I99" s="15" t="inlineStr"/>
-      <c r="J99" s="16" t="inlineStr">
+      <c r="G100" s="15" t="inlineStr"/>
+      <c r="H100" s="15" t="inlineStr"/>
+      <c r="I100" s="15" t="inlineStr"/>
+      <c r="J100" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="K99" s="15" t="inlineStr"/>
-      <c r="L99" s="6" t="inlineStr">
+      <c r="K100" s="15" t="inlineStr"/>
+      <c r="L100" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M99" s="15" t="inlineStr">
+      <c r="M100" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N99" s="15" t="inlineStr"/>
-      <c r="O99" s="15" t="inlineStr">
+      <c r="N100" s="15" t="inlineStr"/>
+      <c r="O100" s="15" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P99" s="15" t="inlineStr">
+      <c r="P100" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q99" s="15" t="inlineStr">
+      <c r="Q100" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R99" s="16" t="inlineStr">
+      <c r="R100" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk.2 Thu Production (LAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>AM</t>
         </is>
       </c>
     </row>
@@ -18755,122 +18778,103 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Tuna Rex + Chickpea Rex Salad at Rex — sent Fri PM</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Tuna Rex + Chickpea Rex Salad (Sat Lunch)</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C102" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E102" s="10" t="inlineStr">
-        <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr"/>
-      <c r="I102" s="9" t="inlineStr"/>
-      <c r="J102" s="10" t="inlineStr">
-        <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
-        </is>
-      </c>
-      <c r="K102" s="9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L102" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M102" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N102" s="9" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O102" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P102" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q102" s="9" t="inlineStr"/>
-      <c r="R102" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
-        </is>
-      </c>
-      <c r="S102" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -18896,33 +18900,25 @@
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>Tuna Salad Mix (→ Wk3 Mon Lunch)</t>
+          <t>Prep Roasted Peppers &amp; Onions (→ Sun Lunch)</t>
         </is>
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G103" s="9" t="inlineStr"/>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
+      <c r="H103" s="9" t="inlineStr"/>
+      <c r="I103" s="9" t="inlineStr"/>
       <c r="J103" s="10" t="inlineStr">
         <is>
-          <t>Mix; chill; send Sun PM</t>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
         </is>
       </c>
       <c r="K103" s="9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
@@ -18937,7 +18933,7 @@
       </c>
       <c r="N103" s="9" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>SUNDAY</t>
         </is>
       </c>
       <c r="O103" s="9" t="inlineStr">
@@ -18947,170 +18943,179 @@
       </c>
       <c r="P103" s="9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q103" s="9" t="inlineStr"/>
       <c r="R103" s="10" t="inlineStr">
         <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S103" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>Tuna Salad Mix (→ Wk3 Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>Mix; chill; send Sun PM</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="O104" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P104" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q104" s="9" t="inlineStr"/>
+      <c r="R104" s="10" t="inlineStr">
+        <is>
           <t>Serves: Wk.3 Monday Lunch</t>
         </is>
       </c>
-      <c r="S103" s="11" t="n">
+      <c r="S104" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>Prep Broccoli Salad (→ Wk3 Sun Lunch)</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R105" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Sunday Lunch</t>
         </is>
       </c>
-      <c r="S104" t="n">
+      <c r="S105" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B105" s="13" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C105" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D105" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E105" s="14" t="inlineStr">
-        <is>
-          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="F105" s="13" t="inlineStr">
-        <is>
-          <t>7 trays</t>
-        </is>
-      </c>
-      <c r="G105" s="13" t="inlineStr"/>
-      <c r="H105" s="13" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I105" s="13" t="inlineStr"/>
-      <c r="J105" s="14" t="inlineStr">
-        <is>
-          <t>Bake meatloaf from tray</t>
-        </is>
-      </c>
-      <c r="K105" s="13" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L105" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M105" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N105" s="13" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O105" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P105" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q105" s="13" t="inlineStr"/>
-      <c r="R105" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 2 Saturday Dinner</t>
-        </is>
       </c>
     </row>
     <row r="106">
@@ -19136,12 +19141,12 @@
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
+          <t>Beef Meatloaf — Bake (Sat Dinner)</t>
         </is>
       </c>
       <c r="F106" s="13" t="inlineStr">
         <is>
-          <t>1 tray</t>
+          <t>7 trays</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr"/>
@@ -19151,7 +19156,11 @@
         </is>
       </c>
       <c r="I106" s="13" t="inlineStr"/>
-      <c r="J106" s="14" t="inlineStr"/>
+      <c r="J106" s="14" t="inlineStr">
+        <is>
+          <t>Bake meatloaf from tray</t>
+        </is>
+      </c>
       <c r="K106" s="13" t="inlineStr">
         <is>
           <t>90</t>
@@ -19178,7 +19187,7 @@
         </is>
       </c>
       <c r="P106" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q106" s="13" t="inlineStr"/>
       <c r="R106" s="14" t="inlineStr">
@@ -19210,30 +19219,22 @@
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>Roasted Potatoes (Sat Dinner)</t>
+          <t>Vegan Meatloaf — Bake (Sat Dinner)</t>
         </is>
       </c>
       <c r="F107" s="13" t="inlineStr">
         <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G107" s="13" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
+          <t>1 tray</t>
+        </is>
+      </c>
+      <c r="G107" s="13" t="inlineStr"/>
       <c r="H107" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
       <c r="I107" s="13" t="inlineStr"/>
-      <c r="J107" s="14" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
+      <c r="J107" s="14" t="inlineStr"/>
       <c r="K107" s="13" t="inlineStr">
         <is>
           <t>90</t>
@@ -19260,7 +19261,7 @@
         </is>
       </c>
       <c r="P107" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q107" s="13" t="inlineStr"/>
       <c r="R107" s="14" t="inlineStr">
@@ -19292,17 +19293,17 @@
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Roasted Butternut Squash (Sat Dinner side)</t>
+          <t>Roasted Potatoes (Sat Dinner)</t>
         </is>
       </c>
       <c r="F108" s="13" t="inlineStr">
         <is>
-          <t>3 bins → 3 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>6 oz</t>
         </is>
       </c>
       <c r="H108" s="13" t="inlineStr">
@@ -19310,24 +19311,20 @@
           <t>hotel</t>
         </is>
       </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+      <c r="I108" s="13" t="inlineStr"/>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>Roast at LAN day-of</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L108" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M108" s="13" t="inlineStr">
@@ -19345,10 +19342,8 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P108" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="P108" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="Q108" s="13" t="inlineStr"/>
       <c r="R108" s="14" t="inlineStr">
@@ -19358,86 +19353,90 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="15" t="inlineStr">
+      <c r="A109" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B109" s="15" t="inlineStr">
+      <c r="B109" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C109" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D109" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E109" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
-        </is>
-      </c>
-      <c r="F109" s="15" t="inlineStr">
-        <is>
-          <t>8 trays</t>
-        </is>
-      </c>
-      <c r="G109" s="15" t="inlineStr"/>
-      <c r="H109" s="15" t="inlineStr">
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E109" s="14" t="inlineStr">
+        <is>
+          <t>Roasted Butternut Squash (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>3 bins → 3 hotels</t>
+        </is>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="H109" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I109" s="15" t="inlineStr">
-        <is>
-          <t>8 hotels</t>
-        </is>
-      </c>
-      <c r="J109" s="16" t="inlineStr">
-        <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="K109" s="15" t="inlineStr"/>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J109" s="14" t="inlineStr">
+        <is>
+          <t>Roast at LAN day-of</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M109" s="15" t="inlineStr">
+      <c r="M109" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N109" s="15" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="O109" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P109" s="15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Q109" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R109" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Wednesday Production (LAN bake same day)</t>
+      <c r="N109" s="13" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O109" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P109" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q109" s="13" t="inlineStr"/>
+      <c r="R109" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Saturday Dinner</t>
         </is>
       </c>
     </row>
@@ -19464,19 +19463,15 @@
       </c>
       <c r="E110" s="16" t="inlineStr">
         <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
+          <t>HOT Beef + Vegan Meatloaf → Dinner</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="G110" s="15" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
+          <t>8 trays</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr">
         <is>
           <t>hotel</t>
@@ -19484,7 +19479,7 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="J110" s="16" t="inlineStr">
@@ -19505,17 +19500,17 @@
       </c>
       <c r="N110" s="15" t="inlineStr">
         <is>
-          <t>SATURDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="O110" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P110" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q110" s="15" t="inlineStr">
@@ -19525,7 +19520,7 @@
       </c>
       <c r="R110" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Saturday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 2 Wednesday Production (LAN bake same day)</t>
         </is>
       </c>
     </row>
@@ -19552,17 +19547,17 @@
       </c>
       <c r="E111" s="16" t="inlineStr">
         <is>
-          <t>HOT Butternut Squash → Dinner side</t>
+          <t>HOT Roasted Potatoes → Dinner</t>
         </is>
       </c>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="G111" s="15" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>6 oz</t>
         </is>
       </c>
       <c r="H111" s="15" t="inlineStr">
@@ -19572,7 +19567,7 @@
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="J111" s="16" t="inlineStr">
@@ -19603,7 +19598,7 @@
       </c>
       <c r="P111" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q111" s="15" t="inlineStr">
@@ -19640,139 +19635,227 @@
       </c>
       <c r="E112" s="16" t="inlineStr">
         <is>
+          <t>HOT Butternut Squash → Dinner side</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G112" s="15" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J112" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K112" s="15" t="inlineStr"/>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N112" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P112" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q112" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R112" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
           <t>HOT Gravy → Dinner (Meatloaf)</t>
         </is>
       </c>
-      <c r="F112" s="15" t="inlineStr">
+      <c r="F113" s="15" t="inlineStr">
         <is>
           <t>½ batch</t>
         </is>
       </c>
-      <c r="G112" s="15" t="inlineStr"/>
-      <c r="H112" s="15" t="inlineStr">
+      <c r="G113" s="15" t="inlineStr"/>
+      <c r="H113" s="15" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I112" s="15" t="inlineStr">
+      <c r="I113" s="15" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J112" s="16" t="inlineStr">
+      <c r="J113" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex | Held from Thu batch</t>
         </is>
       </c>
-      <c r="K112" s="15" t="inlineStr"/>
-      <c r="L112" s="5" t="inlineStr">
+      <c r="K113" s="15" t="inlineStr"/>
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M112" s="15" t="inlineStr">
+      <c r="M113" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N112" s="15" t="inlineStr">
+      <c r="N113" s="15" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="O112" s="15" t="inlineStr">
+      <c r="O113" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P112" s="15" t="inlineStr">
+      <c r="P113" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q112" s="15" t="inlineStr">
+      <c r="Q113" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R112" s="16" t="inlineStr">
+      <c r="R113" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Thursday Dinner (held at Bloor)</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>Cold Broccoli Salad → Wk3 Sun Lunch</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>Bloor → Rex fridge</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr">
+      <c r="N114" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
+      <c r="P114" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="R114" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Saturday Production</t>
         </is>
@@ -21323,7 +21406,7 @@
       <c r="Q18" s="7" t="inlineStr"/>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Monday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -22405,7 +22488,7 @@
       <c r="Q31" s="7" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Tuesday Lunch</t>
+          <t>Produced: Wk. 2 Wednesday Production (cold chain via Rex)</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22566,7 @@
       <c r="Q32" s="7" t="inlineStr"/>
       <c r="R32" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Tuesday Lunch</t>
+          <t>Produced: Wk. 2 Wednesday Production (cold chain via Rex)</t>
         </is>
       </c>
     </row>
@@ -24055,7 +24138,7 @@
       <c r="Q51" s="7" t="inlineStr"/>
       <c r="R51" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Wednesday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -26930,7 +27013,7 @@
       <c r="Q87" s="7" t="inlineStr"/>
       <c r="R87" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
@@ -27508,7 +27591,7 @@
       <c r="Q94" s="7" t="inlineStr"/>
       <c r="R94" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Saturday Lunch</t>
+          <t>Produced: Wk. 3 Sunday Production</t>
         </is>
       </c>
     </row>
@@ -36473,7 +36556,7 @@
       <c r="Q95" s="7" t="inlineStr"/>
       <c r="R95" s="8" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Friday Lunch</t>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -28788,7 +28788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T126"/>
+  <dimension ref="A1:T127"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -33681,55 +33681,75 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Shakshuka → Rex fridge (NC Wk1 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>LUNCH</t>
+          <t>DINNER</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Monday Production</t>
         </is>
       </c>
     </row>
@@ -33746,128 +33766,103 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Coronation Chicken Salad at Rex — sent Tue PM</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Coronation Chicken Salad (Wed Lunch)</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D62" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="inlineStr">
-        <is>
-          <t>Vegan Nacho Mix (→ Wk1 Tue Lunch)</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="G62" s="13" t="inlineStr"/>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="J62" s="14" t="inlineStr">
-        <is>
-          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
-        </is>
-      </c>
-      <c r="K62" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M62" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N62" s="13" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="O62" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P62" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q62" s="13" t="inlineStr"/>
-      <c r="R62" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Lunch (next cycle)</t>
-        </is>
-      </c>
-      <c r="S62" s="12" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -33893,12 +33888,12 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>Beef Nacho Mix (→ Wk1 Tue Lunch)</t>
+          <t>Vegan Nacho Mix (→ Wk1 Tue Lunch)</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr"/>
@@ -33909,7 +33904,7 @@
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>0.5u</t>
         </is>
       </c>
       <c r="J63" s="14" t="inlineStr">
@@ -33919,7 +33914,7 @@
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
@@ -33943,7 +33938,7 @@
         </is>
       </c>
       <c r="P63" s="13" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="Q63" s="13" t="inlineStr"/>
       <c r="R63" s="14" t="inlineStr">
@@ -33956,51 +33951,55 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C64" s="13" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>Marinade Five Spice Tofu</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>15 pcs</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Beef Nacho Mix (→ Wk1 Tue Lunch)</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr"/>
+      <c r="H64" s="13" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>1/2 hotel</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr"/>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr">
+        <is>
+          <t>Stove; cool; vac bag; send Thu PM cold → Rex</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
@@ -34008,34 +34007,32 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M64" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N64" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O64" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P64" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q64" s="9" t="inlineStr"/>
-      <c r="R64" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S64" s="11" t="n">
-        <v>1</v>
+      <c r="M64" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N64" s="13" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O64" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P64" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q64" s="13" t="inlineStr"/>
+      <c r="R64" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Lunch (next cycle)</t>
+        </is>
+      </c>
+      <c r="S64" s="12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="65">
@@ -34046,7 +34043,7 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
@@ -34061,38 +34058,34 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>Coleslaw (→ Thu Lunch side)</t>
+          <t>Marinade Five Spice Tofu</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>2 bins (?)</t>
+          <t>15 pcs</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr"/>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>2 bins (?)</t>
-        </is>
-      </c>
-      <c r="J65" s="10" t="inlineStr">
-        <is>
-          <t>Shred; dress; chill; send Wed PM</t>
-        </is>
-      </c>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr"/>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M65" s="9" t="inlineStr">
@@ -34112,7 +34105,7 @@
       </c>
       <c r="P65" s="9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q65" s="9" t="inlineStr"/>
@@ -34122,90 +34115,94 @@
         </is>
       </c>
       <c r="S65" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>Coleslaw (→ Thu Lunch side)</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>2 bins (?)</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>2 bins (?)</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>Shred; dress; chill; send Wed PM</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O66" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P66" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q66" s="9" t="inlineStr"/>
+      <c r="R66" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Dinner</t>
+        </is>
+      </c>
+      <c r="S66" s="11" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B66" s="13" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D66" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>Beef Stroganoff</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="G66" s="13" t="inlineStr"/>
-      <c r="H66" s="13" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="J66" s="14" t="inlineStr"/>
-      <c r="K66" s="13" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M66" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N66" s="13" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O66" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P66" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q66" s="13" t="inlineStr"/>
-      <c r="R66" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Sunday Dinner</t>
-        </is>
-      </c>
-      <c r="S66" s="12" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -34231,12 +34228,12 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>Vegan Mushroom Stroganoff</t>
+          <t>Beef Stroganoff</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr"/>
@@ -34247,13 +34244,13 @@
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>1/2 hotel</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="J67" s="14" t="inlineStr"/>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>180</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
@@ -34278,7 +34275,7 @@
       </c>
       <c r="P67" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q67" s="13" t="inlineStr"/>
@@ -34292,90 +34289,86 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>Prep Chickpea Salad (→ Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr"/>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>Dress; chill; send Wed PM</t>
-        </is>
-      </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="L68" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N68" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O68" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P68" s="9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q68" s="9" t="inlineStr"/>
-      <c r="R68" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Thursday Lunch</t>
-        </is>
-      </c>
-      <c r="S68" s="11" t="n">
-        <v>2</v>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>Vegan Mushroom Stroganoff</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr"/>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="inlineStr"/>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M68" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N68" s="13" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O68" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P68" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q68" s="13" t="inlineStr"/>
+      <c r="R68" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Sunday Dinner</t>
+        </is>
+      </c>
+      <c r="S68" s="12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -34386,7 +34379,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -34401,7 +34394,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>Chicken Ranch Salad Mix (→ Fri Lunch — make day before send)</t>
+          <t>Prep Chickpea Salad (→ Thu Lunch)</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
@@ -34422,12 +34415,12 @@
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>Mix; chill overnight; send Thu PM</t>
+          <t>Dress; chill; send Wed PM</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>???</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -34442,7 +34435,7 @@
       </c>
       <c r="N69" s="9" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O69" s="9" t="inlineStr">
@@ -34458,7 +34451,7 @@
       <c r="Q69" s="9" t="inlineStr"/>
       <c r="R69" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk.4 Friday Lunch</t>
+          <t>Serves: Wk.4 Thursday Lunch</t>
         </is>
       </c>
       <c r="S69" s="11" t="n">
@@ -34466,340 +34459,343 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="A70" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>Chicken Ranch Salad Mix (→ Fri Lunch — make day before send)</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr"/>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>Mix; chill overnight; send Thu PM</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N70" s="9" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P70" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q70" s="9" t="inlineStr"/>
+      <c r="R70" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk.4 Friday Lunch</t>
+        </is>
+      </c>
+      <c r="S70" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>Reheat Beef &amp; Vegetable Stew (Wed Dinner)</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>130 lbs</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J70" s="8" t="inlineStr">
+      <c r="J71" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="K71" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="L71" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M70" s="7" t="inlineStr">
+      <c r="M71" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N70" s="7" t="inlineStr">
+      <c r="N71" s="7" t="inlineStr">
         <is>
           <t>TUESDAY</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr">
+      <c r="O71" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P70" s="7" t="inlineStr">
+      <c r="P71" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q70" s="7" t="inlineStr"/>
-      <c r="R70" s="8" t="inlineStr">
+      <c r="Q71" s="7" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Tuesday Production</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="13" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B72" s="13" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C72" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D72" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E71" s="14" t="inlineStr">
+      <c r="E72" s="14" t="inlineStr">
         <is>
           <t>Roasted Potatoes (Wed Dinner)</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
+      <c r="F72" s="13" t="inlineStr">
         <is>
           <t>2 bins/4 hotels</t>
         </is>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="G72" s="13" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
+      <c r="H72" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I71" s="13" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J71" s="14" t="inlineStr">
+      <c r="J72" s="14" t="inlineStr">
         <is>
           <t>Steam/Roast</t>
         </is>
       </c>
-      <c r="K71" s="13" t="inlineStr">
+      <c r="K72" s="13" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="L72" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M71" s="13" t="inlineStr">
+      <c r="M72" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N71" s="13" t="inlineStr">
+      <c r="N72" s="13" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O71" s="13" t="inlineStr">
+      <c r="O72" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P71" s="13" t="inlineStr">
+      <c r="P72" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q71" s="13" t="inlineStr"/>
-      <c r="R71" s="14" t="inlineStr">
+      <c r="Q72" s="13" t="inlineStr"/>
+      <c r="R72" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>Reheat Eggplant/Cassava Stew (Wed Dinner)</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr">
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>2u</t>
         </is>
       </c>
-      <c r="J72" s="8" t="inlineStr">
+      <c r="J73" s="8" t="inlineStr">
         <is>
           <t>Reheat</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr">
+      <c r="K73" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L73" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M72" s="7" t="inlineStr">
+      <c r="M73" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N72" s="7" t="inlineStr">
+      <c r="N73" s="7" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O72" s="7" t="inlineStr">
+      <c r="O73" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P72" s="7" t="n">
+      <c r="P73" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" s="7" t="inlineStr"/>
-      <c r="R72" s="8" t="inlineStr">
+      <c r="Q73" s="7" t="inlineStr"/>
+      <c r="R73" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Friday Production</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E73" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="inlineStr">
-        <is>
-          <t>30 lbs</t>
-        </is>
-      </c>
-      <c r="G73" s="15" t="inlineStr"/>
-      <c r="H73" s="15" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J73" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K73" s="15" t="inlineStr"/>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M73" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N73" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O73" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P73" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q73" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R73" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Thursday Production</t>
         </is>
       </c>
     </row>
@@ -34826,27 +34822,23 @@
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>HOT Roasted Potatoes → Dinner</t>
+          <t>HOT Vegan Pot Pie + Veg Medley → Dinner (Veg)</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="G74" s="15" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
+          <t>30 lbs</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J74" s="16" t="inlineStr">
@@ -34862,22 +34854,22 @@
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="15" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O74" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P74" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q74" s="15" t="inlineStr">
@@ -34887,7 +34879,7 @@
       </c>
       <c r="R74" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Wednesday Dinner (same day)</t>
+          <t>Produced: Wk. 3 Thursday Production</t>
         </is>
       </c>
     </row>
@@ -34914,21 +34906,29 @@
       </c>
       <c r="E75" s="16" t="inlineStr">
         <is>
-          <t>HOT Eggplant/Cassava Stew → Dinner</t>
+          <t>HOT Roasted Potatoes → Dinner</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr"/>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I75" s="15" t="inlineStr"/>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -34942,21 +34942,23 @@
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N75" s="15" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>WEDNESDAY</t>
         </is>
       </c>
       <c r="O75" s="15" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P75" s="26" t="n">
-        <v>2</v>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P75" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Q75" s="15" t="inlineStr">
         <is>
@@ -34965,7 +34967,7 @@
       </c>
       <c r="R75" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Friday Production</t>
+          <t>Produced: Wk. 4 Wednesday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -34992,21 +34994,21 @@
       </c>
       <c r="E76" s="16" t="inlineStr">
         <is>
-          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
+          <t>HOT Eggplant/Cassava Stew → Dinner</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr"/>
-      <c r="H76" s="15" t="inlineStr"/>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr"/>
       <c r="J76" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -35025,7 +35027,7 @@
       </c>
       <c r="N76" s="15" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="O76" s="15" t="inlineStr">
@@ -35033,10 +35035,8 @@
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P76" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="P76" s="26" t="n">
+        <v>2</v>
       </c>
       <c r="Q76" s="15" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
       </c>
       <c r="R76" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Tuesday Production</t>
+          <t>Produced: Wk. 3 Friday Production</t>
         </is>
       </c>
     </row>
@@ -35072,130 +35072,132 @@
       </c>
       <c r="E77" s="16" t="inlineStr">
         <is>
-          <t>Cold Chickpea Salad → Thu Lunch</t>
+          <t>HOT Beef &amp; Vegetable Stew → Dinner</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr"/>
       <c r="H77" s="15" t="inlineStr"/>
-      <c r="I77" s="15" t="inlineStr"/>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K77" s="15" t="inlineStr"/>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M77" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N77" s="15" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O77" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P77" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q77" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R77" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Tuesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>Cold Chickpea Salad → Thu Lunch</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr"/>
+      <c r="I78" s="15" t="inlineStr"/>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="K77" s="15" t="inlineStr"/>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="K78" s="15" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M77" s="15" t="inlineStr">
+      <c r="M78" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N77" s="15" t="inlineStr"/>
-      <c r="O77" s="15" t="inlineStr">
+      <c r="N78" s="15" t="inlineStr"/>
+      <c r="O78" s="15" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P77" s="15" t="inlineStr">
+      <c r="P78" s="15" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q77" s="15" t="inlineStr">
+      <c r="Q78" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R77" s="16" t="inlineStr">
+      <c r="R78" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Tue Production (LAN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>HOT Halal Beef Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I78" s="3" t="inlineStr"/>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr"/>
-      <c r="L78" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N78" s="3" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P78" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q78" s="3" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R78" s="4" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -35222,29 +35224,21 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>HOT Black Bean Patties → Lunch (Veg)</t>
+          <t>HOT Halal Beef Burgers → Lunch</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
+      <c r="I79" s="3" t="inlineStr"/>
       <c r="J79" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -35261,16 +35255,18 @@
           <t>4</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P79" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
@@ -35279,7 +35275,7 @@
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
-          <t>Produced: Wk.4 Sun Production (LAN — shaped earlier)</t>
+          <t>Produced: Wk. 4 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -35306,34 +35302,38 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Cold Lettuce / Tomato → Lunch</t>
+          <t>HOT Black Bean Patties → Lunch (Veg)</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>1 unit</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr"/>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>bag</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>1 unit</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr"/>
-      <c r="L80" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -35344,100 +35344,100 @@
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R80" s="4" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Sun Production (LAN — shaped earlier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Cold Lettuce / Tomato → Lunch</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>1 unit</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>1 unit</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr"/>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr"/>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P80" s="18" t="n">
+      <c r="P81" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" s="3" t="inlineStr">
+      <c r="Q81" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R80" s="4" t="inlineStr">
+      <c r="R81" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Thu Lunch (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E81" s="14" t="inlineStr">
-        <is>
-          <t>Halal Beef Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="inlineStr">
-        <is>
-          <t>160 pcs</t>
-        </is>
-      </c>
-      <c r="G81" s="13" t="inlineStr"/>
-      <c r="H81" s="13" t="inlineStr"/>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="J81" s="14" t="inlineStr">
-        <is>
-          <t>From freezer; oven 30 min day-of</t>
-        </is>
-      </c>
-      <c r="K81" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M81" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N81" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O81" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P81" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q81" s="13" t="inlineStr"/>
-      <c r="R81" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Lunch</t>
         </is>
       </c>
     </row>
@@ -35464,37 +35464,29 @@
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Black Bean Patties (Thu Lunch — Veg)</t>
+          <t>Halal Beef Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="H82" s="13" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
+          <t>160 pcs</t>
+        </is>
+      </c>
+      <c r="G82" s="13" t="inlineStr"/>
+      <c r="H82" s="13" t="inlineStr"/>
       <c r="I82" s="13" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>Oven or pan</t>
+          <t>From freezer; oven 30 min day-of</t>
         </is>
       </c>
       <c r="K82" s="13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L82" s="5" t="inlineStr">
@@ -35519,101 +35511,102 @@
       </c>
       <c r="P82" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q82" s="13" t="inlineStr"/>
       <c r="R82" s="14" t="inlineStr">
         <is>
+          <t>Serves: Wk. 4 Thursday Lunch</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>Black Bean Patties (Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="H83" s="13" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>Oven or pan</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M83" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N83" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O83" s="13" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P83" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q83" s="13" t="inlineStr"/>
+      <c r="R83" s="14" t="inlineStr">
+        <is>
           <t>Serves: Wk.4 Thursday Lunch</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
-        </is>
-      </c>
-      <c r="K83" s="9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L83" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M83" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N83" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O83" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P83" s="9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q83" s="9" t="inlineStr"/>
-      <c r="R83" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk.4 Saturday Lunch</t>
-        </is>
-      </c>
-      <c r="S83" s="11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -35639,12 +35632,12 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
+          <t>Tuna Rex Salad Mix (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="G84" s="9" t="inlineStr"/>
@@ -35655,17 +35648,17 @@
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>3 bins</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
+          <t>⚠ NO RECIPE | Mix; chill; send cold day-of</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -35688,8 +35681,10 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P84" s="9" t="n">
-        <v>6</v>
+      <c r="P84" s="9" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="Q84" s="9" t="inlineStr"/>
       <c r="R84" s="10" t="inlineStr">
@@ -35709,7 +35704,7 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
@@ -35724,12 +35719,12 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>Prep Slaw (→ Fri Lunch)</t>
+          <t>Chickpea Rex Salad (→ Sat Lunch — make day before)</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr"/>
@@ -35738,15 +35733,19 @@
           <t>bus bin</t>
         </is>
       </c>
-      <c r="I85" s="9" t="inlineStr"/>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
       <c r="J85" s="10" t="inlineStr">
         <is>
-          <t>Shred; dress; chill; send Thu PM</t>
+          <t>⚠ NO RECIPE | Dress; chill; send cold</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -35761,7 +35760,7 @@
       </c>
       <c r="N85" s="9" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="O85" s="9" t="inlineStr">
@@ -35770,12 +35769,12 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q85" s="9" t="inlineStr"/>
       <c r="R85" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk.4 Friday Lunch</t>
+          <t>Serves: Wk.4 Saturday Lunch</t>
         </is>
       </c>
       <c r="S85" s="11" t="n">
@@ -35783,79 +35782,84 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="13" t="inlineStr">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C86" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D86" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="G86" s="13" t="inlineStr"/>
-      <c r="H86" s="13" t="inlineStr"/>
-      <c r="I86" s="13" t="inlineStr"/>
-      <c r="J86" s="14" t="inlineStr">
-        <is>
-          <t>Combi roast</t>
-        </is>
-      </c>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M86" s="13" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Prep Slaw (→ Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr"/>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr"/>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>Shred; dress; chill; send Thu PM</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M86" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N86" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O86" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P86" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q86" s="13" t="inlineStr"/>
-      <c r="R86" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Thursday Dinner</t>
-        </is>
+      <c r="N86" s="9" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O86" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P86" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q86" s="9" t="inlineStr"/>
+      <c r="R86" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk.4 Friday Lunch</t>
+        </is>
+      </c>
+      <c r="S86" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -35881,12 +35885,12 @@
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+          <t>Teriyaki Chicken Legs (Thu Dinner)</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>6 hotels</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr"/>
@@ -35894,12 +35898,12 @@
       <c r="I87" s="13" t="inlineStr"/>
       <c r="J87" s="14" t="inlineStr">
         <is>
-          <t>Wok/oven</t>
+          <t>Combi roast</t>
         </is>
       </c>
       <c r="K87" s="13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L87" s="5" t="inlineStr">
@@ -35924,7 +35928,7 @@
       </c>
       <c r="P87" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q87" s="13" t="inlineStr"/>
@@ -35935,78 +35939,78 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="15" t="inlineStr">
+      <c r="A88" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D88" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E88" s="16" t="inlineStr">
-        <is>
-          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
-        </is>
-      </c>
-      <c r="F88" s="15" t="inlineStr">
-        <is>
-          <t>215 pcs</t>
-        </is>
-      </c>
-      <c r="G88" s="15" t="inlineStr"/>
-      <c r="H88" s="15" t="inlineStr">
-        <is>
-          <t>hotel/vac</t>
-        </is>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Chow Mein + Nappa Cabbage (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="inlineStr">
         <is>
           <t>6 hotels</t>
         </is>
       </c>
-      <c r="J88" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K88" s="15" t="inlineStr"/>
+      <c r="G88" s="13" t="inlineStr"/>
+      <c r="H88" s="13" t="inlineStr"/>
+      <c r="I88" s="13" t="inlineStr"/>
+      <c r="J88" s="14" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M88" s="15" t="inlineStr">
+      <c r="M88" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N88" s="15" t="inlineStr"/>
-      <c r="O88" s="15" t="inlineStr"/>
-      <c r="P88" s="15" t="inlineStr">
+      <c r="N88" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O88" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P88" s="13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q88" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R88" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
+      <c r="Q88" s="13" t="inlineStr"/>
+      <c r="R88" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Thursday Dinner</t>
         </is>
       </c>
     </row>
@@ -36033,23 +36037,23 @@
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
-          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
+          <t>HOT Teriyaki Chicken + Five-Spice Tofu → Dinner</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>215 pcs</t>
         </is>
       </c>
       <c r="G89" s="15" t="inlineStr"/>
       <c r="H89" s="15" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>hotel/vac</t>
         </is>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t>8 hotels</t>
+          <t>6 hotels</t>
         </is>
       </c>
       <c r="J89" s="16" t="inlineStr">
@@ -36068,19 +36072,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="N89" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O89" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
+      <c r="N89" s="15" t="inlineStr"/>
+      <c r="O89" s="15" t="inlineStr"/>
       <c r="P89" s="15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Q89" s="15" t="inlineStr">
@@ -36090,7 +36086,7 @@
       </c>
       <c r="R89" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 4 Tue (seasoned) → cooked Thu</t>
         </is>
       </c>
     </row>
@@ -36117,28 +36113,28 @@
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>Cold Beef Nacho Mix → Rex fridge</t>
+          <t>HOT Chow Mein + Nappa Cabbage → Dinner</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>vac</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>8 hotels</t>
         </is>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K90" s="15" t="inlineStr"/>
@@ -36154,16 +36150,18 @@
       </c>
       <c r="N90" s="15" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O90" s="15" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P90" s="17" t="n">
-        <v>2</v>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P90" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="Q90" s="15" t="inlineStr">
         <is>
@@ -36172,7 +36170,7 @@
       </c>
       <c r="R90" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Wednesday Production</t>
+          <t>Produced: Wk. 4 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
@@ -36199,12 +36197,12 @@
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>Cold Vegan Nacho Mix → Rex fridge</t>
+          <t>Cold Beef Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="G91" s="15" t="inlineStr"/>
@@ -36215,7 +36213,7 @@
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="J91" s="16" t="inlineStr">
@@ -36245,7 +36243,7 @@
         </is>
       </c>
       <c r="P91" s="17" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="15" t="inlineStr">
         <is>
@@ -36281,34 +36279,34 @@
       </c>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
+          <t>Cold Vegan Nacho Mix → Rex fridge</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>15 lbs</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>0.5u</t>
         </is>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex; Rex holds until Wk1 Mon AM pull</t>
         </is>
       </c>
       <c r="K92" s="15" t="inlineStr"/>
-      <c r="L92" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
@@ -36316,14 +36314,18 @@
           <t>4</t>
         </is>
       </c>
-      <c r="N92" s="15" t="inlineStr"/>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
       <c r="O92" s="15" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P92" s="15" t="n">
-        <v>4</v>
+      <c r="P92" s="17" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q92" s="15" t="inlineStr">
         <is>
@@ -36332,7 +36334,7 @@
       </c>
       <c r="R92" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk.4 Wed Production (LAN)</t>
+          <t>Produced: Wk. 4 Wednesday Production</t>
         </is>
       </c>
     </row>
@@ -36359,7 +36361,7 @@
       </c>
       <c r="E93" s="16" t="inlineStr">
         <is>
-          <t>Cold Slaw → Fri Lunch side</t>
+          <t>Cold Chicken Ranch Mix → Fri Lunch</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
@@ -36368,11 +36370,19 @@
         </is>
       </c>
       <c r="G93" s="15" t="inlineStr"/>
-      <c r="H93" s="15" t="inlineStr"/>
-      <c r="I93" s="15" t="inlineStr"/>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="K93" s="15" t="inlineStr"/>
@@ -36392,7 +36402,7 @@
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P93" s="18" t="n">
+      <c r="P93" s="15" t="n">
         <v>4</v>
       </c>
       <c r="Q93" s="15" t="inlineStr">
@@ -36407,327 +36417,314 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B94" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>Cold Slaw → Fri Lunch side</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr"/>
+      <c r="H94" s="15" t="inlineStr"/>
+      <c r="I94" s="15" t="inlineStr"/>
+      <c r="J94" s="16" t="inlineStr">
+        <is>
+          <t>⚠ CONFIRM 2 bins/4u — LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K94" s="15" t="inlineStr"/>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M94" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N94" s="15" t="inlineStr"/>
+      <c r="O94" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P94" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q94" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R94" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk.4 Wed Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>HOT Crispy Falafel → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="G95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I95" s="3" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="J95" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K94" s="3" t="inlineStr"/>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="M95" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N94" s="3" t="inlineStr"/>
-      <c r="O94" s="3" t="inlineStr">
+      <c r="N95" s="3" t="inlineStr"/>
+      <c r="O95" s="3" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P94" s="3" t="inlineStr">
+      <c r="P95" s="3" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="Q94" s="3" t="inlineStr">
+      <c r="Q95" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R94" s="4" t="inlineStr">
+      <c r="R95" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Fri Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="7" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E95" s="8" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>Heat Falafel (frozen → oven) (Fri Lunch — Veg)</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>30 pcs</t>
         </is>
       </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="7" t="inlineStr"/>
-      <c r="J95" s="8" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="8" t="inlineStr">
         <is>
           <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="K96" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M95" s="7" t="inlineStr">
+      <c r="M96" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N95" s="7" t="inlineStr">
+      <c r="N96" s="7" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O95" s="7" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P95" s="7" t="n">
+      <c r="P96" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q95" s="7" t="inlineStr"/>
-      <c r="R95" s="8" t="inlineStr">
+      <c r="Q96" s="7" t="inlineStr"/>
+      <c r="R96" s="8" t="inlineStr">
         <is>
           <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B96" s="13" t="inlineStr">
+      <c r="B97" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C96" s="13" t="inlineStr">
+      <c r="C97" s="13" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D96" s="13" t="inlineStr">
+      <c r="D97" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E96" s="14" t="inlineStr">
+      <c r="E97" s="14" t="inlineStr">
         <is>
           <t>Vegan Carnitas</t>
         </is>
       </c>
-      <c r="F96" s="13" t="inlineStr">
+      <c r="F97" s="13" t="inlineStr">
         <is>
           <t>15 lbs</t>
         </is>
       </c>
-      <c r="G96" s="13" t="inlineStr"/>
-      <c r="H96" s="13" t="inlineStr">
+      <c r="G97" s="13" t="inlineStr"/>
+      <c r="H97" s="13" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I96" s="13" t="inlineStr">
+      <c r="I97" s="13" t="inlineStr">
         <is>
           <t>1/2 hotel</t>
         </is>
       </c>
-      <c r="J96" s="14" t="inlineStr">
+      <c r="J97" s="14" t="inlineStr">
         <is>
           <t>Stove</t>
         </is>
       </c>
-      <c r="K96" s="13" t="inlineStr">
+      <c r="K97" s="13" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M96" s="13" t="inlineStr">
+      <c r="M97" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N96" s="13" t="inlineStr">
+      <c r="N97" s="13" t="inlineStr">
         <is>
           <t>TUESDAY</t>
         </is>
       </c>
-      <c r="O96" s="13" t="inlineStr">
+      <c r="O97" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P96" s="13" t="inlineStr">
+      <c r="P97" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q96" s="13" t="inlineStr"/>
-      <c r="R96" s="14" t="inlineStr">
+      <c r="Q97" s="13" t="inlineStr"/>
+      <c r="R97" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
         </is>
       </c>
-      <c r="S96" s="12" t="n">
+      <c r="S97" s="12" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>Broccoli Prep (Saturday Lunch)</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="J97" s="10" t="inlineStr"/>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L97" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O97" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P97" s="9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="Q97" s="9" t="inlineStr"/>
-      <c r="R97" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Saturday Lunch</t>
-        </is>
-      </c>
-      <c r="S97" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -36753,30 +36750,34 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
+          <t>Broccoli Prep (Saturday Lunch)</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>4 hotels veg</t>
+          <t>3 bins</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr"/>
-      <c r="I98" s="9" t="inlineStr"/>
-      <c r="J98" s="10" t="inlineStr">
-        <is>
-          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
-        </is>
-      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="J98" s="10" t="inlineStr"/>
       <c r="K98" s="9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr">
@@ -36786,24 +36787,27 @@
       </c>
       <c r="N98" s="9" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="O98" s="9" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>LUNCH</t>
         </is>
       </c>
       <c r="P98" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
-        </is>
+          <t>Serves: Wk. 4 Saturday Lunch</t>
+        </is>
+      </c>
+      <c r="S98" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -36829,26 +36833,22 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>Jerk Marinade</t>
+          <t>Prep Vegetable Biryani (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>4 hotels veg</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>cambro/bag</t>
-        </is>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>1 bag/8 qt</t>
-        </is>
-      </c>
-      <c r="J99" s="10" t="inlineStr"/>
+      <c r="H99" s="9" t="inlineStr"/>
+      <c r="I99" s="9" t="inlineStr"/>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE | Chop veg; hold for oven rice</t>
+        </is>
+      </c>
       <c r="K99" s="9" t="inlineStr">
         <is>
           <t>30</t>
@@ -36861,12 +36861,12 @@
       </c>
       <c r="M99" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N99" s="9" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="O99" s="9" t="inlineStr">
@@ -36874,17 +36874,16 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P99" s="9" t="n">
-        <v>1</v>
+      <c r="P99" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Q99" s="9" t="inlineStr"/>
       <c r="R99" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Monday Dinner</t>
-        </is>
-      </c>
-      <c r="S99" s="12" t="n">
-        <v>3</v>
+          <t>Serves: Wk. 4 Friday Dinner</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -36910,29 +36909,29 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>Jerk Cauliflower</t>
+          <t>Jerk Marinade</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>15 pcs</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr"/>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>cambro/bag</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>1/2 hotel</t>
+          <t>1 bag/8 qt</t>
         </is>
       </c>
       <c r="J100" s="10" t="inlineStr"/>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L100" s="5" t="inlineStr">
@@ -36955,10 +36954,8 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P100" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="P100" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q100" s="9" t="inlineStr"/>
       <c r="R100" s="10" t="inlineStr">
@@ -36971,76 +36968,86 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="9" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="9" t="inlineStr">
         <is>
           <t>PREP</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>Jerk Cauliflower</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>15 pcs</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>1/2 hotel</t>
+        </is>
+      </c>
+      <c r="J101" s="10" t="inlineStr"/>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M101" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
+      <c r="N101" s="9" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="O101" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P101" t="n">
-        <v>1</v>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-      <c r="S101" t="n">
-        <v>5</v>
+      <c r="P101" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q101" s="9" t="inlineStr"/>
+      <c r="R101" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Monday Dinner</t>
+        </is>
+      </c>
+      <c r="S101" s="12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -37066,27 +37073,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
+          <t>Carnitas Sauce (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1 cs</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1 bin</t>
+          <t>cambro</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -37109,10 +37111,8 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="P102" t="n">
+        <v>1</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
+          <t>Season Carnitas Chicken (→ Wk. 1 Tues. Dinner)</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -37166,7 +37166,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -37204,85 +37204,83 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="inlineStr">
+      <c r="A104" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Season Carnitas Pork (→ Wk. 1 Tues. Dinner)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>Reheat Tandoori Pork (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="J104" s="8" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="K104" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L104" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M104" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N104" s="7" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="O104" s="7" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P104" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q104" s="7" t="inlineStr"/>
-      <c r="R104" s="8" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Monday Production</t>
-        </is>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -37308,12 +37306,12 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>Reheat Tandoori Chicken — Halal (Fri Dinner)</t>
+          <t>Reheat Tandoori Pork (Fri Dinner)</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr"/>
@@ -37324,7 +37322,7 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
@@ -37349,7 +37347,7 @@
       </c>
       <c r="N105" s="7" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="O105" s="7" t="inlineStr">
@@ -37358,168 +37356,172 @@
         </is>
       </c>
       <c r="P105" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="7" t="inlineStr"/>
       <c r="R105" s="8" t="inlineStr">
         <is>
+          <t>Produced: Wk. 4 Monday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Reheat Tandoori Chicken — Halal (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I106" s="7" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="J106" s="8" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O106" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" s="7" t="inlineStr"/>
+      <c r="R106" s="8" t="inlineStr">
+        <is>
           <t>Produced: Wk. 4 Tuesday Production</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="13" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B106" s="13" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C106" s="13" t="inlineStr">
+      <c r="C107" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D106" s="13" t="inlineStr">
+      <c r="D107" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E106" s="14" t="inlineStr">
+      <c r="E107" s="14" t="inlineStr">
         <is>
           <t>Roast Tandoori Tofu (Fri Dinner — Veg)</t>
         </is>
       </c>
-      <c r="F106" s="13" t="inlineStr">
+      <c r="F107" s="13" t="inlineStr">
         <is>
           <t>12 pcs</t>
         </is>
       </c>
-      <c r="G106" s="13" t="inlineStr"/>
-      <c r="H106" s="13" t="inlineStr"/>
-      <c r="I106" s="13" t="inlineStr">
+      <c r="G107" s="13" t="inlineStr"/>
+      <c r="H107" s="13" t="inlineStr"/>
+      <c r="I107" s="13" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="J106" s="14" t="inlineStr">
+      <c r="J107" s="14" t="inlineStr">
         <is>
           <t>Oven roast</t>
         </is>
       </c>
-      <c r="K106" s="13" t="inlineStr">
+      <c r="K107" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M106" s="13" t="inlineStr">
+      <c r="M107" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N106" s="13" t="inlineStr">
+      <c r="N107" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O106" s="13" t="inlineStr">
+      <c r="O107" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P106" s="13" t="n">
+      <c r="P107" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q106" s="13" t="inlineStr"/>
-      <c r="R106" s="14" t="inlineStr">
+      <c r="Q107" s="13" t="inlineStr"/>
+      <c r="R107" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C107" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E107" s="16" t="inlineStr">
-        <is>
-          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="F107" s="15" t="inlineStr">
-        <is>
-          <t>0.5 hotels</t>
-        </is>
-      </c>
-      <c r="G107" s="15" t="inlineStr"/>
-      <c r="H107" s="15" t="inlineStr"/>
-      <c r="I107" s="15" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="J107" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K107" s="15" t="inlineStr"/>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M107" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N107" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O107" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P107" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q107" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R107" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -37546,33 +37548,49 @@
       </c>
       <c r="E108" s="16" t="inlineStr">
         <is>
-          <t>Pick up Baked Rolls at GC</t>
+          <t>HOT Tandoori Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>pickup</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr"/>
-      <c r="I108" s="15" t="inlineStr"/>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>GC → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K108" s="15" t="inlineStr"/>
-      <c r="L108" s="19" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M108" s="15" t="inlineStr"/>
-      <c r="N108" s="15" t="inlineStr"/>
-      <c r="O108" s="15" t="inlineStr"/>
-      <c r="P108" s="18" t="n">
-        <v>0</v>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N108" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P108" s="17" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q108" s="15" t="inlineStr">
         <is>
@@ -37581,7 +37599,7 @@
       </c>
       <c r="R108" s="16" t="inlineStr">
         <is>
-          <t>N/A — logistics</t>
+          <t>Produced: Wk. 4 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -37608,355 +37626,330 @@
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
+          <t>Pick up Baked Rolls at GC</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="G109" s="15" t="inlineStr"/>
+      <c r="H109" s="15" t="inlineStr"/>
+      <c r="I109" s="15" t="inlineStr"/>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>GC → Rex</t>
+        </is>
+      </c>
+      <c r="K109" s="15" t="inlineStr"/>
+      <c r="L109" s="19" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="M109" s="15" t="inlineStr"/>
+      <c r="N109" s="15" t="inlineStr"/>
+      <c r="O109" s="15" t="inlineStr"/>
+      <c r="P109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R109" s="16" t="inlineStr">
+        <is>
+          <t>N/A — logistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
           <t>HOT Vegetable Biryani → Dinner</t>
         </is>
       </c>
-      <c r="F109" s="15" t="inlineStr">
+      <c r="F110" s="15" t="inlineStr">
         <is>
           <t>6 hotels</t>
         </is>
       </c>
-      <c r="G109" s="15" t="inlineStr">
+      <c r="G110" s="15" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="H109" s="15" t="inlineStr">
+      <c r="H110" s="15" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I109" s="15" t="inlineStr">
+      <c r="I110" s="15" t="inlineStr">
         <is>
           <t>6 hotels</t>
         </is>
       </c>
-      <c r="J109" s="16" t="inlineStr">
+      <c r="J110" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K109" s="15" t="inlineStr"/>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="K110" s="15" t="inlineStr"/>
+      <c r="L110" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M109" s="15" t="inlineStr">
+      <c r="M110" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N109" s="15" t="inlineStr">
+      <c r="N110" s="15" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O109" s="15" t="inlineStr">
+      <c r="O110" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P109" s="15" t="inlineStr">
+      <c r="P110" s="15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q109" s="15" t="inlineStr">
+      <c r="Q110" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R109" s="16" t="inlineStr">
+      <c r="R110" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Friday Dinner (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>Cold Tuna Rex Salad Mix → Sat Lunch</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>2 bins</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr">
+      <c r="R111" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Friday Production</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Cold Mixed Lettuce → Lunch</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr"/>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="J111" s="4" t="inlineStr">
+      <c r="J112" s="4" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="K111" s="3" t="inlineStr"/>
-      <c r="L111" s="6" t="inlineStr">
+      <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M111" s="3" t="inlineStr">
+      <c r="M112" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N111" s="3" t="inlineStr"/>
-      <c r="O111" s="3" t="inlineStr">
+      <c r="N112" s="3" t="inlineStr"/>
+      <c r="O112" s="3" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P111" s="3" t="inlineStr">
+      <c r="P112" s="3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="Q111" s="3" t="inlineStr">
+      <c r="Q112" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R111" s="4" t="inlineStr">
+      <c r="R112" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk.4 Sat Lunch (LAN same day)</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>Tuna Rex + Chickpea Rex Salad (Sat Lunch)</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>Cold salad pre-sent Fri PM; Mixed Lettuce sent AM</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr">
+      <c r="N113" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>Tuna Salad Mix (→ NC Wk1 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G113" s="9" t="inlineStr"/>
-      <c r="H113" s="9" t="inlineStr">
-        <is>
-          <t>bus bin</t>
-        </is>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="J113" s="10" t="inlineStr">
-        <is>
-          <t>Mix; chill; send Sun PM</t>
-        </is>
-      </c>
-      <c r="K113" s="9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L113" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M113" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N113" s="9" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="O113" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P113" s="9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="Q113" s="9" t="inlineStr"/>
-      <c r="R113" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk.1 Monday Lunch (next cycle)</t>
-        </is>
-      </c>
-      <c r="S113" s="11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -37982,30 +37975,38 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>Prep Broccoli Salad (→ NC Wk1 Sun Lunch)</t>
+          <t>Tuna Salad Mix (→ NC Wk1 Mon Lunch)</t>
         </is>
       </c>
       <c r="F114" s="9" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="G114" s="9" t="inlineStr"/>
-      <c r="H114" s="9" t="inlineStr"/>
-      <c r="I114" s="9" t="inlineStr"/>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
       <c r="J114" s="10" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
+          <t>Mix; chill; send Sun PM</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M114" s="9" t="inlineStr">
@@ -38015,7 +38016,7 @@
       </c>
       <c r="N114" s="9" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="O114" s="9" t="inlineStr">
@@ -38025,17 +38026,17 @@
       </c>
       <c r="P114" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Q114" s="9" t="inlineStr"/>
       <c r="R114" s="10" t="inlineStr">
         <is>
-          <t>Serves: NC Wk. 1 Sunday Lunch</t>
+          <t>Serves: Wk.1 Monday Lunch (next cycle)</t>
         </is>
       </c>
       <c r="S114" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -38061,12 +38062,12 @@
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>Trim/Season Jerk Chicken Legs (→ NC Wk1 Mon Dinner)</t>
+          <t>Prep Broccoli Salad (→ NC Wk1 Sun Lunch)</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>165 pcs / 3 bins</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr"/>
@@ -38074,12 +38075,12 @@
       <c r="I115" s="9" t="inlineStr"/>
       <c r="J115" s="10" t="inlineStr">
         <is>
-          <t>Season; hold in bins at Bloor</t>
+          <t>⚠ NO RECIPE | Make at Bloor; send PM to Rex</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr">
@@ -38094,27 +38095,27 @@
       </c>
       <c r="N115" s="9" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>SUNDAY</t>
         </is>
       </c>
       <c r="O115" s="9" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>LUNCH</t>
         </is>
       </c>
       <c r="P115" s="9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q115" s="9" t="inlineStr"/>
       <c r="R115" s="10" t="inlineStr">
         <is>
-          <t>Serves: NC Wk. 1 Monday Dinner</t>
+          <t>Serves: NC Wk. 1 Sunday Lunch</t>
         </is>
       </c>
       <c r="S115" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -38140,12 +38141,12 @@
       </c>
       <c r="E116" s="10" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg Stacks (→ NC Wk1 Sun Lunch — Veg)</t>
+          <t>Trim/Season Jerk Chicken Legs (→ NC Wk1 Mon Dinner)</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>165 pcs / 3 bins</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr"/>
@@ -38153,12 +38154,12 @@
       <c r="I116" s="9" t="inlineStr"/>
       <c r="J116" s="10" t="inlineStr">
         <is>
-          <t>Slice/season at Bloor; roast Sun AM</t>
+          <t>Season; hold in bins at Bloor</t>
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
@@ -38173,117 +38174,106 @@
       </c>
       <c r="N116" s="9" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>LUNCH</t>
+          <t>DINNER</t>
         </is>
       </c>
       <c r="P116" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Q116" s="9" t="inlineStr"/>
       <c r="R116" s="10" t="inlineStr">
         <is>
+          <t>Serves: NC Wk. 1 Monday Dinner</t>
+        </is>
+      </c>
+      <c r="S116" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg Stacks (→ NC Wk1 Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr"/>
+      <c r="H117" s="9" t="inlineStr"/>
+      <c r="I117" s="9" t="inlineStr"/>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor; roast Sun AM</t>
+        </is>
+      </c>
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M117" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O117" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P117" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q117" s="9" t="inlineStr"/>
+      <c r="R117" s="10" t="inlineStr">
+        <is>
           <t>Serves: NC Wk. 1 Sunday Lunch</t>
         </is>
       </c>
-      <c r="S116" s="11" t="n">
+      <c r="S117" s="11" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Cook Carnitas Pork (→ NC Wk1 Tue Dinner)</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Oven; cool then vac bag; hold Bloor fridge</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
-        </is>
-      </c>
-      <c r="S117" t="n">
-        <v>3</v>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
       </c>
     </row>
     <row r="118">
@@ -38309,7 +38299,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Cook Carnitas Chicken (→ NC Wk1 Tue Dinner)</t>
+          <t>Cook Carnitas Pork (→ NC Wk1 Tue Dinner)</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -38324,7 +38314,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>1.0u</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -38334,7 +38324,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -38359,7 +38349,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
@@ -38377,166 +38367,174 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+      <c r="A119" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B119" s="9" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Cook Carnitas Chicken (→ NC Wk1 Tue Dinner)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1 cs</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Oven; cool then vac bag; hold Bloor fridge</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>TUESDAY</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Tuesday Dinner (next cycle)</t>
+        </is>
+      </c>
+      <c r="S119" t="n">
+        <v>3</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="E119" s="10" t="inlineStr">
+      <c r="E120" s="10" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (3 pcs) + Naan + Stirfry Veg (NO PEANUTS) (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F119" s="9" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>3 pcs</t>
         </is>
       </c>
-      <c r="G119" s="9" t="inlineStr">
+      <c r="G120" s="9" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="H119" s="9" t="inlineStr">
+      <c r="H120" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I119" s="9" t="inlineStr"/>
-      <c r="J119" s="10" t="inlineStr">
+      <c r="I120" s="9" t="inlineStr"/>
+      <c r="J120" s="10" t="inlineStr">
         <is>
           <t>For no-peanuts/no-nuts restrictions (2-3 ppl)</t>
         </is>
       </c>
-      <c r="K119" s="9" t="inlineStr">
+      <c r="K120" s="9" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L119" s="6" t="inlineStr">
+      <c r="L120" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M119" s="9" t="inlineStr">
+      <c r="M120" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N119" s="9" t="inlineStr">
+      <c r="N120" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O119" s="9" t="inlineStr">
+      <c r="O120" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P119" s="9" t="n">
+      <c r="P120" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" s="9" t="inlineStr"/>
-      <c r="R119" s="10" t="inlineStr">
+      <c r="Q120" s="9" t="inlineStr"/>
+      <c r="R120" s="10" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C120" s="7" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>110 lbs</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr"/>
-      <c r="H120" s="7" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I120" s="7" t="inlineStr">
-        <is>
-          <t>3u</t>
-        </is>
-      </c>
-      <c r="J120" s="8" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="K120" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L120" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M120" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N120" s="7" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O120" s="7" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P120" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q120" s="7" t="inlineStr"/>
-      <c r="R120" s="8" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -38563,12 +38561,12 @@
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
+          <t>Reheat Beef Massaman Curry (Sat Dinner)</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>15 lbs</t>
+          <t>110 lbs</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr"/>
@@ -38579,7 +38577,7 @@
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>3u</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
@@ -38589,7 +38587,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L121" s="5" t="inlineStr">
@@ -38613,7 +38611,7 @@
         </is>
       </c>
       <c r="P121" s="7" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="Q121" s="7" t="inlineStr"/>
       <c r="R121" s="8" t="inlineStr">
@@ -38623,160 +38621,164 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="13" t="inlineStr">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B122" s="13" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C122" s="13" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D122" s="13" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>Reheat Vegan Massaman Curry (Sat Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I122" s="7" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="J122" s="8" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M122" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N122" s="7" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O122" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P122" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q122" s="7" t="inlineStr"/>
+      <c r="R122" s="8" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C123" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E122" s="14" t="inlineStr">
+      <c r="E123" s="14" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F122" s="13" t="inlineStr">
+      <c r="F123" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G122" s="13" t="inlineStr"/>
-      <c r="H122" s="13" t="inlineStr">
+      <c r="G123" s="13" t="inlineStr"/>
+      <c r="H123" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I122" s="13" t="inlineStr">
+      <c r="I123" s="13" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J122" s="14" t="inlineStr"/>
-      <c r="K122" s="13" t="inlineStr">
+      <c r="J123" s="14" t="inlineStr"/>
+      <c r="K123" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L122" s="5" t="inlineStr">
+      <c r="L123" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M122" s="13" t="inlineStr">
+      <c r="M123" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N122" s="13" t="inlineStr">
+      <c r="N123" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O122" s="13" t="inlineStr">
+      <c r="O123" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P122" s="13" t="inlineStr">
+      <c r="P123" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q122" s="13" t="inlineStr"/>
-      <c r="R122" s="14" t="inlineStr">
+      <c r="Q123" s="13" t="inlineStr"/>
+      <c r="R123" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B123" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D123" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E123" s="16" t="inlineStr">
-        <is>
-          <t>HOT Beef Massaman Curry → Dinner</t>
-        </is>
-      </c>
-      <c r="F123" s="15" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G123" s="15" t="inlineStr"/>
-      <c r="H123" s="15" t="inlineStr"/>
-      <c r="I123" s="15" t="inlineStr">
-        <is>
-          <t>3u</t>
-        </is>
-      </c>
-      <c r="J123" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K123" s="15" t="inlineStr"/>
-      <c r="L123" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M123" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N123" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O123" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P123" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q123" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R123" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -38803,19 +38805,19 @@
       </c>
       <c r="E124" s="16" t="inlineStr">
         <is>
-          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
+          <t>HOT Beef Massaman Curry → Dinner</t>
         </is>
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>0.5 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G124" s="15" t="inlineStr"/>
       <c r="H124" s="15" t="inlineStr"/>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>3u</t>
         </is>
       </c>
       <c r="J124" s="16" t="inlineStr">
@@ -38845,7 +38847,7 @@
         </is>
       </c>
       <c r="P124" s="17" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="Q124" s="15" t="inlineStr">
         <is>
@@ -38881,21 +38883,21 @@
       </c>
       <c r="E125" s="16" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner side</t>
+          <t>HOT Vegan Massaman Curry → Dinner (Veg)</t>
         </is>
       </c>
       <c r="F125" s="15" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>0.5 hotels</t>
         </is>
       </c>
       <c r="G125" s="15" t="inlineStr"/>
-      <c r="H125" s="15" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I125" s="15" t="inlineStr"/>
+      <c r="H125" s="15" t="inlineStr"/>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -38909,7 +38911,7 @@
       </c>
       <c r="M125" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N125" s="15" t="inlineStr">
@@ -38919,11 +38921,11 @@
       </c>
       <c r="O125" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P125" s="26" t="n">
-        <v>4</v>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P125" s="17" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q125" s="15" t="inlineStr">
         <is>
@@ -38932,7 +38934,7 @@
       </c>
       <c r="R125" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+          <t>Produced: Wk. 3 Saturday Production</t>
         </is>
       </c>
     </row>
@@ -38959,24 +38961,24 @@
       </c>
       <c r="E126" s="16" t="inlineStr">
         <is>
-          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+          <t>HOT Rice → Dinner side</t>
         </is>
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="G126" s="15" t="inlineStr"/>
-      <c r="H126" s="15" t="inlineStr"/>
-      <c r="I126" s="15" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I126" s="15" t="inlineStr"/>
       <c r="J126" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex fridge</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K126" s="15" t="inlineStr"/>
@@ -38997,20 +38999,98 @@
       </c>
       <c r="O126" s="15" t="inlineStr">
         <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P126" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q126" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R126" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E127" s="16" t="inlineStr">
+        <is>
+          <t>Cold Broccoli Salad → NC Wk1 Sun Lunch</t>
+        </is>
+      </c>
+      <c r="F127" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G127" s="15" t="inlineStr"/>
+      <c r="H127" s="15" t="inlineStr"/>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex fridge</t>
+        </is>
+      </c>
+      <c r="K127" s="15" t="inlineStr"/>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M127" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N127" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O127" s="15" t="inlineStr">
+        <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P126" s="15" t="inlineStr">
+      <c r="P127" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q126" s="15" t="inlineStr">
+      <c r="Q127" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R126" s="16" t="inlineStr">
+      <c r="R127" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Saturday Production</t>
         </is>

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -1457,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T111"/>
+  <dimension ref="A1:T114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>Dress; chill; send Thu PM</t>
+          <t>Dress; chill; send Thu PM | ⚠ NO RECIPE</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
@@ -5897,10 +5897,8 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P54" s="9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="P54" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Q54" s="9" t="inlineStr"/>
       <c r="R54" s="10" t="inlineStr">
@@ -5930,42 +5928,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>COOK</t>
+          <t>PREP</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cook Pork Adobo (→ Fri Dinner)</t>
+          <t>Egg Salad Mix (→ Fri Lunch — make at LAN)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>40 lbs cooked</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>vac</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Oven/Combi; cool; vac bag</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Bloor</t>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5980,21 +5968,16 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>2</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Serves: Wk. 1 Friday Dinner</t>
-        </is>
-      </c>
-      <c r="S55" t="n">
-        <v>2</v>
+          <t>Serves: Wk. 1 Friday Lunch</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -6020,12 +6003,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
+          <t>Cook Pork Adobo (→ Fri Dinner)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>32 lbs cooked</t>
+          <t>40 lbs cooked</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6035,7 +6018,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6045,7 +6028,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6070,7 +6053,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6095,307 +6078,326 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Cook Chicken Adobo — Halal (→ Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>32 lbs cooked</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Oven/Combi; cool; vac bag</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 1 Friday Dinner</t>
+        </is>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Roast Shakshuka Chicken Legs (Wed Dinner)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>165 pcs</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>⚠ CONFIRM qty/hotels | Same-day roast at Bloor</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P57" t="n">
+      <c r="P58" t="n">
         <v>4</v>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="S58" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>Reheat Chickpea Shakshuka Sauce (Wed Dinner)</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J58" s="8" t="inlineStr">
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged batch</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="K59" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M58" s="7" t="inlineStr">
+      <c r="M59" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N58" s="7" t="inlineStr">
+      <c r="N59" s="7" t="inlineStr">
         <is>
           <t>MONDAY</t>
         </is>
       </c>
-      <c r="O58" s="7" t="inlineStr">
+      <c r="O59" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P58" s="7" t="inlineStr">
+      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q58" s="7" t="inlineStr"/>
-      <c r="R58" s="8" t="inlineStr">
+      <c r="Q59" s="7" t="inlineStr"/>
+      <c r="R59" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 4 Monday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B59" s="13" t="inlineStr">
+      <c r="B60" s="13" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>Herbed Couscous (Wed Dinner)</t>
         </is>
       </c>
-      <c r="F59" s="13" t="inlineStr">
+      <c r="F60" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G59" s="13" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="H59" s="13" t="inlineStr">
+      <c r="H60" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I59" s="13" t="inlineStr">
+      <c r="I60" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J59" s="14" t="inlineStr"/>
-      <c r="K59" s="13" t="inlineStr">
+      <c r="J60" s="14" t="inlineStr"/>
+      <c r="K60" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr">
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M59" s="13" t="inlineStr">
+      <c r="M60" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N59" s="13" t="inlineStr">
+      <c r="N60" s="13" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O59" s="13" t="inlineStr">
+      <c r="O60" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P59" s="13" t="inlineStr">
+      <c r="P60" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q59" s="13" t="inlineStr"/>
-      <c r="R59" s="14" t="inlineStr">
+      <c r="Q60" s="13" t="inlineStr"/>
+      <c r="R60" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Wednesday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr"/>
-      <c r="H60" s="15" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I60" s="15" t="inlineStr"/>
-      <c r="J60" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K60" s="15" t="inlineStr"/>
-      <c r="L60" s="19" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M60" s="15" t="inlineStr"/>
-      <c r="N60" s="15" t="inlineStr"/>
-      <c r="O60" s="15" t="inlineStr"/>
-      <c r="P60" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R60" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -6422,43 +6424,37 @@
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>HOT Shakshuka Sauce → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="G61" s="15" t="inlineStr"/>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I61" s="15" t="inlineStr"/>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K61" s="15" t="inlineStr"/>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>GC</t>
         </is>
       </c>
       <c r="M61" s="15" t="inlineStr"/>
       <c r="N61" s="15" t="inlineStr"/>
       <c r="O61" s="15" t="inlineStr"/>
-      <c r="P61" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="P61" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="Q61" s="15" t="inlineStr">
         <is>
@@ -6467,7 +6463,7 @@
       </c>
       <c r="R61" s="16" t="inlineStr">
         <is>
-          <t>Produced: pre-loaded batch (prev. cycle)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -6494,137 +6490,132 @@
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
+          <t>HOT Shakshuka Sauce → Dinner</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr"/>
+      <c r="H62" s="15" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K62" s="15" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M62" s="15" t="inlineStr"/>
+      <c r="N62" s="15" t="inlineStr"/>
+      <c r="O62" s="15" t="inlineStr"/>
+      <c r="P62" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q62" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R62" s="16" t="inlineStr">
+        <is>
+          <t>Produced: pre-loaded batch (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
           <t>HOT Herbed Couscous → Dinner side</t>
         </is>
       </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="F63" s="15" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G62" s="15" t="inlineStr"/>
-      <c r="H62" s="15" t="inlineStr"/>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="G63" s="15" t="inlineStr"/>
+      <c r="H63" s="15" t="inlineStr"/>
+      <c r="I63" s="15" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J62" s="16" t="inlineStr">
+      <c r="J63" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="K62" s="15" t="inlineStr"/>
-      <c r="L62" s="6" t="inlineStr">
+      <c r="K63" s="15" t="inlineStr"/>
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M62" s="15" t="inlineStr">
+      <c r="M63" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N62" s="15" t="inlineStr">
+      <c r="N63" s="15" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O62" s="15" t="inlineStr">
+      <c r="O63" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P62" s="15" t="inlineStr">
+      <c r="P63" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q62" s="15" t="inlineStr">
+      <c r="Q63" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R62" s="16" t="inlineStr">
+      <c r="R63" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Cold Pork Vindaloo → Rex fridge</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>40 lbs</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Tuesday Production</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6642,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+          <t>Cold Pork Vindaloo → Rex fridge</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>32 lbs</t>
+          <t>40 lbs</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6666,7 +6657,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1.0u</t>
+          <t>1.5u</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6691,7 +6682,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6728,144 +6719,137 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>Cold Chicken Vindaloo — Halal → Rex fridge</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1.0u</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Tuesday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>HOT Shakshuka Chicken Legs → Dinner</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>165 pcs</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P65" t="n">
+      <c r="P66" t="n">
         <v>4</v>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>HOT Halal Chicken Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>185 pcs</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr"/>
-      <c r="L66" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q66" s="3" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R66" s="4" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
         </is>
       </c>
     </row>
@@ -6892,12 +6876,12 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
+          <t>HOT Halal Chicken Burgers → Lunch</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>20 pcs</t>
+          <t>185 pcs</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr"/>
@@ -6906,7 +6890,11 @@
           <t>hotel</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
@@ -6933,97 +6921,97 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P67" s="7" t="n">
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr"/>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P68" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" s="3" t="inlineStr">
+      <c r="Q68" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R67" s="4" t="inlineStr">
+      <c r="R68" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Lunch (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B68" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C68" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="D68" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E68" s="14" t="inlineStr">
-        <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="F68" s="13" t="inlineStr">
-        <is>
-          <t>185 pcs</t>
-        </is>
-      </c>
-      <c r="G68" s="13" t="inlineStr"/>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="J68" s="14" t="inlineStr"/>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L68" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M68" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N68" s="13" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O68" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P68" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q68" s="13" t="inlineStr"/>
-      <c r="R68" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 1 Thursday Lunch</t>
         </is>
       </c>
     </row>
@@ -7050,29 +7038,29 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>30 pcs</t>
+          <t>185 pcs</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr"/>
-      <c r="H69" s="13" t="inlineStr"/>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J69" s="14" t="inlineStr">
-        <is>
-          <t>Pan fry; send hot AM</t>
-        </is>
-      </c>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J69" s="14" t="inlineStr"/>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
@@ -7087,23 +7075,23 @@
       </c>
       <c r="N69" s="13" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O69" s="13" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
+          <t>LUNCH</t>
         </is>
       </c>
       <c r="P69" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q69" s="13" t="inlineStr"/>
       <c r="R69" s="14" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production</t>
+          <t>Serves: Wk. 1 Thursday Lunch</t>
         </is>
       </c>
     </row>
@@ -7120,70 +7108,71 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>30 pcs</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr"/>
+      <c r="H70" s="13" t="inlineStr"/>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>Pan fry; send hot AM</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M70" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N70" s="13" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O70" s="13" t="inlineStr">
+        <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>130 lbs</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr"/>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>3.5 hotels</t>
-        </is>
-      </c>
-      <c r="J70" s="14" t="inlineStr"/>
-      <c r="K70" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M70" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N70" s="13" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="O70" s="13" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P70" s="13" t="n">
-        <v>3.5</v>
+      <c r="P70" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="Q70" s="13" t="inlineStr"/>
       <c r="R70" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Monday Lunch</t>
-        </is>
-      </c>
-      <c r="S70" s="12" t="n">
-        <v>4</v>
+          <t>Produced: Wk. 1 Wednesday Production</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -7209,12 +7198,12 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
+          <t>Vegan Chili (→ Wk2 Mon Lunch)</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>130 lbs</t>
         </is>
       </c>
       <c r="G71" s="13" t="inlineStr"/>
@@ -7225,14 +7214,12 @@
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
-          <t>0.5 hotel</t>
+          <t>3.5 hotels</t>
         </is>
       </c>
       <c r="J71" s="14" t="inlineStr"/>
-      <c r="K71" s="13" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="K71" s="13" t="n">
+        <v>240</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
@@ -7246,7 +7233,7 @@
       </c>
       <c r="N71" s="13" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="O71" s="13" t="inlineStr">
@@ -7255,16 +7242,16 @@
         </is>
       </c>
       <c r="P71" s="13" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q71" s="13" t="inlineStr"/>
       <c r="R71" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
+          <t>Serves: Wk. 2 Monday Lunch</t>
         </is>
       </c>
       <c r="S71" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -7290,12 +7277,12 @@
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+          <t>Cook Portobello Cheese Melt (→ Wk2 Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>12 lbs</t>
         </is>
       </c>
       <c r="G72" s="13" t="inlineStr"/>
@@ -7306,13 +7293,13 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>2u</t>
+          <t>0.5 hotel</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr"/>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
@@ -7327,113 +7314,106 @@
       </c>
       <c r="N72" s="13" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>SUNDAY</t>
         </is>
       </c>
       <c r="O72" s="13" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>LUNCH</t>
         </is>
       </c>
       <c r="P72" s="13" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="Q72" s="13" t="inlineStr"/>
       <c r="R72" s="14" t="inlineStr">
         <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S72" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk2 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="inlineStr"/>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr"/>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M73" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N73" s="13" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O73" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P73" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q73" s="13" t="inlineStr"/>
+      <c r="R73" s="14" t="inlineStr">
+        <is>
           <t>Serves: Wk. 2 Wednesday Dinner</t>
         </is>
       </c>
-      <c r="S72" s="12" t="n">
+      <c r="S73" s="12" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>Reheat Butter Chicken (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I73" s="7" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="K73" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L73" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M73" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N73" s="7" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O73" s="7" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P73" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q73" s="7" t="inlineStr"/>
-      <c r="R73" s="8" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
-        </is>
       </c>
     </row>
     <row r="74">
@@ -7459,12 +7439,12 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+          <t>Reheat Butter Chicken (Thu Dinner)</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>20 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -7479,10 +7459,14 @@
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr"/>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
           <t>60</t>
@@ -7510,7 +7494,7 @@
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr"/>
@@ -7521,156 +7505,174 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B75" s="13" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>Reheat Butter Chickpeas (Thu Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>20 lbs</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O75" s="7" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q75" s="7" t="inlineStr"/>
+      <c r="R75" s="8" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E75" s="14" t="inlineStr">
+      <c r="E76" s="14" t="inlineStr">
         <is>
           <t>Roasted Cauliflower (Thu Dinner side)</t>
         </is>
       </c>
-      <c r="F75" s="13" t="inlineStr">
+      <c r="F76" s="13" t="inlineStr">
         <is>
           <t>3 bins → 3 hotels</t>
         </is>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="H75" s="13" t="inlineStr">
+      <c r="H76" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I75" s="13" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J75" s="14" t="inlineStr">
+      <c r="J76" s="14" t="inlineStr">
         <is>
           <t>⚠ CONFIRM carrot role in this side</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L75" s="6" t="inlineStr">
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M75" s="13" t="inlineStr">
+      <c r="M76" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N75" s="13" t="inlineStr">
+      <c r="N76" s="13" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="O75" s="13" t="inlineStr">
+      <c r="O76" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P75" s="13" t="inlineStr">
+      <c r="P76" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q75" s="13" t="inlineStr"/>
-      <c r="R75" s="14" t="inlineStr">
+      <c r="Q76" s="13" t="inlineStr"/>
+      <c r="R76" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Thursday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B76" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E76" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F76" s="15" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G76" s="15" t="inlineStr"/>
-      <c r="H76" s="15" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I76" s="15" t="inlineStr"/>
-      <c r="J76" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K76" s="15" t="inlineStr"/>
-      <c r="L76" s="19" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M76" s="15" t="inlineStr"/>
-      <c r="N76" s="15" t="inlineStr"/>
-      <c r="O76" s="15" t="inlineStr"/>
-      <c r="P76" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R76" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -7697,59 +7699,37 @@
       </c>
       <c r="E77" s="16" t="inlineStr">
         <is>
-          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>80+20 lbs</t>
-        </is>
-      </c>
-      <c r="G77" s="15" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr"/>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I77" s="15" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="inlineStr"/>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr"/>
-      <c r="L77" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M77" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N77" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O77" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P77" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="L77" s="19" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="M77" s="15" t="inlineStr"/>
+      <c r="N77" s="15" t="inlineStr"/>
+      <c r="O77" s="15" t="inlineStr"/>
+      <c r="P77" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="Q77" s="15" t="inlineStr">
         <is>
@@ -7758,7 +7738,7 @@
       </c>
       <c r="R77" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -7785,50 +7765,58 @@
       </c>
       <c r="E78" s="16" t="inlineStr">
         <is>
-          <t>HOT Roasted Cauliflower → Dinner side</t>
+          <t>HOT Butter Chicken + Butter Chickpeas → Dinner</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="G78" s="15" t="inlineStr"/>
-      <c r="H78" s="15" t="inlineStr"/>
+          <t>80+20 lbs</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr"/>
-      <c r="L78" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N78" s="15" t="inlineStr">
         <is>
-          <t>THURSDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="O78" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P78" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q78" s="15" t="inlineStr">
@@ -7838,7 +7826,7 @@
       </c>
       <c r="R78" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 4 Saturday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -7865,126 +7853,146 @@
       </c>
       <c r="E79" s="16" t="inlineStr">
         <is>
+          <t>HOT Roasted Cauliflower → Dinner side</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr"/>
+      <c r="H79" s="15" t="inlineStr"/>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K79" s="15" t="inlineStr"/>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N79" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O79" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P79" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q79" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R79" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B80" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
           <t>HOT Naan → Dinner</t>
         </is>
       </c>
-      <c r="F79" s="15" t="inlineStr">
+      <c r="F80" s="15" t="inlineStr">
         <is>
           <t>200 pcs</t>
         </is>
       </c>
-      <c r="G79" s="15" t="inlineStr">
+      <c r="G80" s="15" t="inlineStr">
         <is>
           <t>1 each (?)</t>
         </is>
       </c>
-      <c r="H79" s="15" t="inlineStr">
+      <c r="H80" s="15" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="I79" s="15" t="inlineStr">
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>2 bags</t>
         </is>
       </c>
-      <c r="J79" s="16" t="inlineStr">
+      <c r="J80" s="16" t="inlineStr">
         <is>
           <t>Purchased; delivered direct to Rex or via van</t>
         </is>
       </c>
-      <c r="K79" s="15" t="inlineStr"/>
-      <c r="L79" s="20" t="inlineStr">
+      <c r="K80" s="15" t="inlineStr"/>
+      <c r="L80" s="20" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="M79" s="15" t="inlineStr">
+      <c r="M80" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N79" s="15" t="inlineStr">
+      <c r="N80" s="15" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="O79" s="15" t="inlineStr">
+      <c r="O80" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P79" s="18" t="n">
+      <c r="P80" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" s="15" t="inlineStr">
+      <c r="Q80" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R79" s="16" t="inlineStr">
+      <c r="R80" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Thursday Dinner (LAN same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>AM</t>
         </is>
       </c>
     </row>
@@ -7996,1512 +8004,1475 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="O81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P81" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="P82" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Wednesday Production (LAN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Bean Salad (Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B82" s="13" t="inlineStr">
+      <c r="B85" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C82" s="13" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E82" s="14" t="inlineStr">
+      <c r="E85" s="14" t="inlineStr">
         <is>
           <t>Sausage &amp; Greens Pasta Sauce (→ Wk2 Sun Dinner)</t>
         </is>
       </c>
-      <c r="F82" s="13" t="inlineStr">
+      <c r="F85" s="13" t="inlineStr">
         <is>
           <t>120 lbs</t>
         </is>
       </c>
-      <c r="G82" s="13" t="inlineStr"/>
-      <c r="H82" s="13" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr"/>
+      <c r="H85" s="13" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I82" s="13" t="inlineStr">
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J82" s="14" t="inlineStr">
+      <c r="J85" s="14" t="inlineStr">
         <is>
           <t>Stove top</t>
         </is>
       </c>
-      <c r="K82" s="13" t="inlineStr">
+      <c r="K85" s="13" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M82" s="13" t="inlineStr">
+      <c r="M85" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N82" s="13" t="inlineStr">
+      <c r="N85" s="13" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O82" s="13" t="inlineStr">
+      <c r="O85" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P82" s="13" t="inlineStr">
+      <c r="P85" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q82" s="13" t="inlineStr"/>
-      <c r="R82" s="14" t="inlineStr">
+      <c r="Q85" s="13" t="inlineStr"/>
+      <c r="R85" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Sunday Dinner</t>
         </is>
       </c>
-      <c r="S82" s="11" t="n">
+      <c r="S85" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="13" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B83" s="13" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E83" s="14" t="inlineStr">
+      <c r="E86" s="14" t="inlineStr">
         <is>
           <t>Pineapple Rice (Fri Dinner)</t>
         </is>
       </c>
-      <c r="F83" s="13" t="inlineStr">
+      <c r="F86" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="G86" s="13" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="H83" s="13" t="inlineStr">
+      <c r="H86" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I83" s="13" t="inlineStr">
+      <c r="I86" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J83" s="14" t="inlineStr">
+      <c r="J86" s="14" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE | Oven rice</t>
         </is>
       </c>
-      <c r="K83" s="13" t="inlineStr">
+      <c r="K86" s="13" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L83" s="6" t="inlineStr">
+      <c r="L86" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M83" s="13" t="inlineStr">
+      <c r="M86" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N83" s="13" t="inlineStr">
+      <c r="N86" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O83" s="13" t="inlineStr">
+      <c r="O86" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P83" s="13" t="inlineStr">
+      <c r="P86" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q83" s="13" t="inlineStr"/>
-      <c r="R83" s="14" t="inlineStr">
+      <c r="Q86" s="13" t="inlineStr"/>
+      <c r="R86" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="13" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B87" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C84" s="13" t="inlineStr">
+      <c r="C87" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E84" s="14" t="inlineStr">
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>Steam Green Beans (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="F84" s="13" t="inlineStr">
+      <c r="F87" s="13" t="inlineStr">
         <is>
           <t>3 bins</t>
         </is>
       </c>
-      <c r="G84" s="13" t="inlineStr">
+      <c r="G87" s="13" t="inlineStr">
         <is>
           <t>4 oz</t>
         </is>
       </c>
-      <c r="H84" s="13" t="inlineStr">
+      <c r="H87" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I84" s="13" t="inlineStr">
+      <c r="I87" s="13" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J84" s="14" t="inlineStr">
+      <c r="J87" s="14" t="inlineStr">
         <is>
           <t>Frozen; steam at Bloor</t>
         </is>
       </c>
-      <c r="K84" s="13" t="inlineStr">
+      <c r="K87" s="13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M84" s="13" t="inlineStr">
+      <c r="M87" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N84" s="13" t="inlineStr">
+      <c r="N87" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O84" s="13" t="inlineStr">
+      <c r="O87" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P84" s="13" t="inlineStr">
+      <c r="P87" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q84" s="13" t="inlineStr"/>
-      <c r="R84" s="14" t="inlineStr">
+      <c r="Q87" s="13" t="inlineStr"/>
+      <c r="R87" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Reheat Pork Adobo (Fri Dinner)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>40 lbs</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>10 oz</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>1.5u</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Reheat Halal Chicken Adobo (Fri Dinner)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>32 lbs</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>1u</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Roast Adobo Tofu (Fri Dinner — Veg)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>12 pcs</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>⚠ CONFIRM cook time | Same-day roast at Bloor</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="R90" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Friday Dinner</t>
         </is>
       </c>
-      <c r="S87" t="n">
+      <c r="S90" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="15" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="B91" s="15" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C88" s="15" t="inlineStr">
+      <c r="C91" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D88" s="15" t="inlineStr">
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="E91" s="16" t="inlineStr">
         <is>
           <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
-      <c r="F88" s="15" t="inlineStr">
+      <c r="F91" s="15" t="inlineStr">
         <is>
           <t>pickup</t>
         </is>
       </c>
-      <c r="G88" s="15" t="inlineStr"/>
-      <c r="H88" s="15" t="inlineStr">
+      <c r="G91" s="15" t="inlineStr"/>
+      <c r="H91" s="15" t="inlineStr">
         <is>
           <t>bag</t>
         </is>
       </c>
-      <c r="I88" s="15" t="inlineStr"/>
-      <c r="J88" s="16" t="inlineStr">
+      <c r="I91" s="15" t="inlineStr"/>
+      <c r="J91" s="16" t="inlineStr">
         <is>
           <t>GC → Rex</t>
         </is>
       </c>
-      <c r="K88" s="15" t="inlineStr"/>
-      <c r="L88" s="19" t="inlineStr">
+      <c r="K91" s="15" t="inlineStr"/>
+      <c r="L91" s="19" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="M88" s="15" t="inlineStr"/>
-      <c r="N88" s="15" t="inlineStr"/>
-      <c r="O88" s="15" t="inlineStr"/>
-      <c r="P88" s="18" t="n">
+      <c r="M91" s="15" t="inlineStr"/>
+      <c r="N91" s="15" t="inlineStr"/>
+      <c r="O91" s="15" t="inlineStr"/>
+      <c r="P91" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" s="15" t="inlineStr">
+      <c r="Q91" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R88" s="16" t="inlineStr">
+      <c r="R91" s="16" t="inlineStr">
         <is>
           <t>N/A — logistics</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="15" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B92" s="15" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C89" s="15" t="inlineStr">
+      <c r="C92" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D89" s="15" t="inlineStr">
+      <c r="D92" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E89" s="16" t="inlineStr">
+      <c r="E92" s="16" t="inlineStr">
         <is>
           <t>HOT Pineapple Rice → Dinner side</t>
         </is>
       </c>
-      <c r="F89" s="15" t="inlineStr">
+      <c r="F92" s="15" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G89" s="15" t="inlineStr"/>
-      <c r="H89" s="15" t="inlineStr"/>
-      <c r="I89" s="15" t="inlineStr">
+      <c r="G92" s="15" t="inlineStr"/>
+      <c r="H92" s="15" t="inlineStr"/>
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J89" s="16" t="inlineStr">
+      <c r="J92" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="K89" s="15" t="inlineStr"/>
-      <c r="L89" s="6" t="inlineStr">
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M89" s="15" t="inlineStr">
+      <c r="M92" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N89" s="15" t="inlineStr">
+      <c r="N92" s="15" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O89" s="15" t="inlineStr">
+      <c r="O92" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P89" s="15" t="inlineStr">
+      <c r="P92" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q89" s="15" t="inlineStr">
+      <c r="Q92" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R89" s="16" t="inlineStr">
+      <c r="R92" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B90" s="15" t="inlineStr">
+      <c r="B93" s="15" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D90" s="15" t="inlineStr">
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E93" s="16" t="inlineStr">
         <is>
           <t>HOT Green Beans → Dinner side</t>
         </is>
       </c>
-      <c r="F90" s="15" t="inlineStr">
+      <c r="F93" s="15" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G90" s="15" t="inlineStr"/>
-      <c r="H90" s="15" t="inlineStr"/>
-      <c r="I90" s="15" t="inlineStr">
+      <c r="G93" s="15" t="inlineStr"/>
+      <c r="H93" s="15" t="inlineStr"/>
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J90" s="16" t="inlineStr">
+      <c r="J93" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K90" s="15" t="inlineStr"/>
-      <c r="L90" s="5" t="inlineStr">
+      <c r="K93" s="15" t="inlineStr"/>
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M90" s="15" t="inlineStr">
+      <c r="M93" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N90" s="15" t="inlineStr">
+      <c r="N93" s="15" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O90" s="15" t="inlineStr">
+      <c r="O93" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P90" s="15" t="n">
+      <c r="P93" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="Q90" s="15" t="inlineStr">
+      <c r="Q93" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R90" s="16" t="inlineStr">
+      <c r="R93" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>HOT Pork Adobo → Dinner</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>40 lbs</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>1.5u</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="R94" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>HOT Halal Chicken Adobo → Dinner (Halal)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>32 lbs</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>1u</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="R95" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>HOT Adobo Tofu → Dinner (Veg)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>0.5u</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="R96" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="G97" s="3" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K94" s="3" t="inlineStr"/>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="K97" s="3" t="inlineStr"/>
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M94" s="3" t="inlineStr">
+      <c r="M97" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N94" s="3" t="inlineStr">
+      <c r="N97" s="3" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O94" s="3" t="inlineStr">
+      <c r="O97" s="3" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P94" s="3" t="inlineStr">
+      <c r="P97" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q94" s="3" t="inlineStr">
+      <c r="Q97" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R94" s="4" t="inlineStr">
+      <c r="R97" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>SEND AM</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>0.5 hotel</t>
         </is>
       </c>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I95" s="3" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J95" s="4" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K95" s="3" t="inlineStr"/>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M95" s="3" t="inlineStr">
+      <c r="M98" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N95" s="3" t="inlineStr">
+      <c r="N98" s="3" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O95" s="3" t="inlineStr">
+      <c r="O98" s="3" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P95" s="3" t="n">
+      <c r="P98" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q95" s="3" t="inlineStr">
+      <c r="Q98" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R95" s="4" t="inlineStr">
+      <c r="R98" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>80 lbs + 15 lbs</t>
         </is>
       </c>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr">
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr">
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K96" s="7" t="inlineStr">
+      <c r="K99" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M96" s="7" t="inlineStr">
+      <c r="M99" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N96" s="7" t="inlineStr">
+      <c r="N99" s="7" t="inlineStr">
         <is>
           <t>SUNDAY</t>
         </is>
       </c>
-      <c r="O96" s="7" t="inlineStr">
+      <c r="O99" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P96" s="7" t="inlineStr"/>
-      <c r="Q96" s="7" t="inlineStr"/>
-      <c r="R96" s="8" t="inlineStr">
+      <c r="P99" s="7" t="inlineStr"/>
+      <c r="Q99" s="7" t="inlineStr"/>
+      <c r="R99" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Sunday Production</t>
         </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>Griot Marinade</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="G97" s="9" t="inlineStr"/>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>cambro</t>
-        </is>
-      </c>
-      <c r="I97" s="9" t="inlineStr"/>
-      <c r="J97" s="10" t="inlineStr">
-        <is>
-          <t>For Griot Pork/Chicken/Tofu</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M97" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N97" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O97" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P97" s="9" t="inlineStr"/>
-      <c r="Q97" s="9" t="inlineStr"/>
-      <c r="R97" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S97" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E98" s="10" t="inlineStr">
-        <is>
-          <t>Cut/Marinate Pork Griot</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>30kg raw</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="inlineStr"/>
-      <c r="H98" s="9" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>1 bin/2 hotels</t>
-        </is>
-      </c>
-      <c r="J98" s="10" t="inlineStr"/>
-      <c r="K98" s="9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M98" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N98" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O98" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P98" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q98" s="9" t="inlineStr"/>
-      <c r="R98" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S98" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E99" s="10" t="inlineStr">
-        <is>
-          <t>Marinate Chicken Griot</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>25kg raw</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr"/>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>bus bin/hotel</t>
-        </is>
-      </c>
-      <c r="I99" s="9" t="inlineStr">
-        <is>
-          <t>1 bin</t>
-        </is>
-      </c>
-      <c r="J99" s="10" t="inlineStr"/>
-      <c r="K99" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L99" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M99" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N99" s="9" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O99" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P99" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="Q99" s="9" t="inlineStr"/>
-      <c r="R99" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S99" s="12" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="100">
@@ -9527,68 +9498,60 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Griot Marinade</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr"/>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr"/>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+          <t>For Griot Pork/Chicken/Tofu</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L100" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M100" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N100" s="9" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O100" s="9" t="inlineStr">
         <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P100" s="9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P100" s="9" t="inlineStr"/>
       <c r="Q100" s="9" t="inlineStr"/>
       <c r="R100" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 2 Sunday Lunch</t>
-        </is>
-      </c>
-      <c r="S100" s="11" t="n">
-        <v>1</v>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+      <c r="S100" s="12" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="101">
@@ -9614,33 +9577,29 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Cut/Marinate Pork Griot</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>30kg raw</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr"/>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>bus bin/hotel</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J101" s="10" t="inlineStr">
-        <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
-        </is>
-      </c>
+          <t>1 bin/2 hotels</t>
+        </is>
+      </c>
+      <c r="J101" s="10" t="inlineStr"/>
       <c r="K101" s="9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
@@ -9650,601 +9609,618 @@
       </c>
       <c r="M101" s="9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N101" s="9" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O101" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P101" s="9" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="N101" s="9" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O101" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P101" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="Q101" s="9" t="inlineStr"/>
       <c r="R101" s="10" t="inlineStr">
         <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+      <c r="S101" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>Marinate Chicken Griot</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>25kg raw</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="inlineStr"/>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>bus bin/hotel</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>1 bin</t>
+        </is>
+      </c>
+      <c r="J102" s="10" t="inlineStr"/>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M102" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N102" s="9" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O102" s="9" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P102" s="9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="Q102" s="9" t="inlineStr"/>
+      <c r="R102" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
+        </is>
+      </c>
+      <c r="S102" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M103" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N103" s="9" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O103" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P103" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Q103" s="9" t="inlineStr"/>
+      <c r="R103" s="10" t="inlineStr">
+        <is>
           <t>Serves: Wk. 2 Sunday Lunch</t>
         </is>
       </c>
-      <c r="S101" s="11" t="n">
+      <c r="S103" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="13" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B102" s="13" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C102" s="13" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="inlineStr"/>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J104" s="10" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
+      <c r="K104" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N104" s="9" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O104" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P104" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q104" s="9" t="inlineStr"/>
+      <c r="R104" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 2 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S104" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D102" s="13" t="inlineStr">
+      <c r="D105" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E102" s="14" t="inlineStr">
+      <c r="E105" s="14" t="inlineStr">
         <is>
           <t>Carrot Cabbage Fry (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="F102" s="13" t="inlineStr">
+      <c r="F105" s="13" t="inlineStr">
         <is>
           <t>3 bins → 2 hotels</t>
         </is>
       </c>
-      <c r="G102" s="13" t="inlineStr"/>
-      <c r="H102" s="13" t="inlineStr">
+      <c r="G105" s="13" t="inlineStr"/>
+      <c r="H105" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I102" s="13" t="inlineStr">
+      <c r="I105" s="13" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J102" s="14" t="inlineStr">
+      <c r="J105" s="14" t="inlineStr">
         <is>
           <t>Stir-fry at LAN; send hot PM</t>
         </is>
       </c>
-      <c r="K102" s="13" t="inlineStr">
+      <c r="K105" s="13" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L102" s="6" t="inlineStr">
+      <c r="L105" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M102" s="13" t="inlineStr">
+      <c r="M105" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N102" s="13" t="inlineStr">
+      <c r="N105" s="13" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O102" s="13" t="inlineStr">
+      <c r="O105" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P102" s="13" t="inlineStr">
+      <c r="P105" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q102" s="13" t="inlineStr"/>
-      <c r="R102" s="14" t="inlineStr">
+      <c r="Q105" s="13" t="inlineStr"/>
+      <c r="R105" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 2 Wednesday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>Reheat Gomen Besiga Beef (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F103" s="7" t="inlineStr">
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>80 lbs</t>
         </is>
       </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J103" s="8" t="inlineStr">
+      <c r="J106" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K103" s="7" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M103" s="7" t="inlineStr">
+      <c r="M106" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N103" s="7" t="inlineStr">
+      <c r="N106" s="7" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O103" s="7" t="inlineStr">
+      <c r="O106" s="7" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="P103" s="7" t="inlineStr">
+      <c r="P106" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q103" s="7" t="inlineStr"/>
-      <c r="R103" s="8" t="inlineStr">
+      <c r="Q106" s="7" t="inlineStr"/>
+      <c r="R106" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 1 Wednesday Production</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B104" s="13" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C104" s="13" t="inlineStr">
+      <c r="C107" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D104" s="13" t="inlineStr">
+      <c r="D107" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E104" s="14" t="inlineStr">
+      <c r="E107" s="14" t="inlineStr">
         <is>
           <t>Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F104" s="13" t="inlineStr">
+      <c r="F107" s="13" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G104" s="13" t="inlineStr"/>
-      <c r="H104" s="13" t="inlineStr"/>
-      <c r="I104" s="13" t="inlineStr">
+      <c r="G107" s="13" t="inlineStr"/>
+      <c r="H107" s="13" t="inlineStr"/>
+      <c r="I107" s="13" t="inlineStr">
         <is>
           <t>1 hotel</t>
         </is>
       </c>
-      <c r="J104" s="14" t="inlineStr"/>
-      <c r="K104" s="13" t="inlineStr">
+      <c r="J107" s="14" t="inlineStr"/>
+      <c r="K107" s="13" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L104" s="5" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M104" s="13" t="inlineStr">
+      <c r="M107" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N104" s="13" t="inlineStr">
+      <c r="N107" s="13" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O104" s="13" t="inlineStr">
+      <c r="O107" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P104" s="13" t="inlineStr">
+      <c r="P107" s="13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q104" s="13" t="inlineStr"/>
-      <c r="R104" s="14" t="inlineStr">
+      <c r="Q107" s="13" t="inlineStr"/>
+      <c r="R107" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B108" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
+      <c r="D108" s="9" t="inlineStr">
         <is>
           <t>ALT</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr">
+      <c r="E108" s="10" t="inlineStr">
         <is>
           <t>🔸 BLAND ALT — Plain Chicken Leg (2 pcs) + Cabbage Stirfry + Plain Rice (Sat Dinner)</t>
         </is>
       </c>
-      <c r="F105" s="9" t="inlineStr">
+      <c r="F108" s="9" t="inlineStr">
         <is>
           <t>2 pcs</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
+      <c r="G108" s="9" t="inlineStr">
         <is>
           <t>1 pc</t>
         </is>
       </c>
-      <c r="H105" s="9" t="inlineStr">
+      <c r="H108" s="9" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I105" s="9" t="inlineStr">
+      <c r="I108" s="9" t="inlineStr">
         <is>
           <t>4" hotel</t>
         </is>
       </c>
-      <c r="J105" s="10" t="inlineStr">
+      <c r="J108" s="10" t="inlineStr">
         <is>
           <t>For bland/no-tomato/no-greens</t>
         </is>
       </c>
-      <c r="K105" s="9" t="inlineStr">
+      <c r="K108" s="9" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L105" s="6" t="inlineStr">
+      <c r="L108" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M105" s="9" t="inlineStr">
+      <c r="M108" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N105" s="9" t="inlineStr">
+      <c r="N108" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O105" s="9" t="inlineStr">
+      <c r="O108" s="9" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P105" s="9" t="n">
+      <c r="P108" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" s="9" t="inlineStr"/>
-      <c r="R105" s="10" t="inlineStr">
+      <c r="Q108" s="9" t="inlineStr"/>
+      <c r="R108" s="10" t="inlineStr">
         <is>
           <t>Serves: Wk. 1 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B106" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C106" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D106" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E106" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F106" s="15" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G106" s="15" t="inlineStr"/>
-      <c r="H106" s="15" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I106" s="15" t="inlineStr"/>
-      <c r="J106" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K106" s="15" t="inlineStr"/>
-      <c r="L106" s="19" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M106" s="15" t="inlineStr"/>
-      <c r="N106" s="15" t="inlineStr"/>
-      <c r="O106" s="15" t="inlineStr"/>
-      <c r="P106" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R106" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C107" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E107" s="16" t="inlineStr">
-        <is>
-          <t>HOT Gomen Besiga Beef → Dinner</t>
-        </is>
-      </c>
-      <c r="F107" s="15" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G107" s="15" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="H107" s="15" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I107" s="15" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="J107" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K107" s="15" t="inlineStr"/>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M107" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N107" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O107" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P107" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q107" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R107" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B108" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C108" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D108" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E108" s="16" t="inlineStr">
-        <is>
-          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="F108" s="15" t="inlineStr">
-        <is>
-          <t>15 lbs</t>
-        </is>
-      </c>
-      <c r="G108" s="15" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="H108" s="15" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I108" s="15" t="inlineStr">
-        <is>
-          <t>1 × 4" hotel</t>
-        </is>
-      </c>
-      <c r="J108" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K108" s="15" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M108" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N108" s="15" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O108" s="15" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P108" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q108" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R108" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -10271,55 +10247,37 @@
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="G109" s="15" t="inlineStr"/>
       <c r="H109" s="15" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I109" s="15" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I109" s="15" t="inlineStr"/>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K109" s="15" t="inlineStr"/>
-      <c r="L109" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M109" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N109" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O109" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P109" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="L109" s="19" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="M109" s="15" t="inlineStr"/>
+      <c r="N109" s="15" t="inlineStr"/>
+      <c r="O109" s="15" t="inlineStr"/>
+      <c r="P109" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="Q109" s="15" t="inlineStr">
         <is>
@@ -10328,7 +10286,7 @@
       </c>
       <c r="R109" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -10355,19 +10313,27 @@
       </c>
       <c r="E110" s="16" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>HOT Gomen Besiga Beef → Dinner</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="G110" s="15" t="inlineStr"/>
-      <c r="H110" s="15" t="inlineStr"/>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>2 hotels</t>
         </is>
       </c>
       <c r="J110" s="16" t="inlineStr">
@@ -10383,21 +10349,23 @@
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N110" s="15" t="inlineStr">
         <is>
-          <t>SATURDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O110" s="15" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P110" s="15" t="n">
-        <v>4</v>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P110" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="Q110" s="15" t="inlineStr">
         <is>
@@ -10406,7 +10374,7 @@
       </c>
       <c r="R110" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
         </is>
       </c>
     </row>
@@ -10433,50 +10401,298 @@
       </c>
       <c r="E111" s="16" t="inlineStr">
         <is>
+          <t>HOT Vegan Gomen Besiga → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="inlineStr">
+        <is>
+          <t>15 lbs</t>
+        </is>
+      </c>
+      <c r="G111" s="15" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I111" s="15" t="inlineStr">
+        <is>
+          <t>1 × 4" hotel</t>
+        </is>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K111" s="15" t="inlineStr"/>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M111" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N111" s="15" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P111" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q111" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R111" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 4 Thursday Production (prev. cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>HOT Carrot Cabbage Fry → Dinner side</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="G112" s="15" t="inlineStr"/>
+      <c r="H112" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J112" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K112" s="15" t="inlineStr"/>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N112" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P112" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q112" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R112" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>HOT Rice → Dinner</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="G113" s="15" t="inlineStr"/>
+      <c r="H113" s="15" t="inlineStr"/>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J113" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K113" s="15" t="inlineStr"/>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M113" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N113" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P113" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q113" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R113" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 1 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
           <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
         </is>
       </c>
-      <c r="F111" s="15" t="inlineStr">
+      <c r="F114" s="15" t="inlineStr">
         <is>
           <t>3 bins + 1 bag</t>
         </is>
       </c>
-      <c r="G111" s="15" t="inlineStr"/>
-      <c r="H111" s="15" t="inlineStr">
+      <c r="G114" s="15" t="inlineStr"/>
+      <c r="H114" s="15" t="inlineStr">
         <is>
           <t>bus bin/bag</t>
         </is>
       </c>
-      <c r="I111" s="15" t="inlineStr">
+      <c r="I114" s="15" t="inlineStr">
         <is>
           <t>4 items</t>
         </is>
       </c>
-      <c r="J111" s="16" t="inlineStr">
+      <c r="J114" s="16" t="inlineStr">
         <is>
           <t>LAN → Rex fridge</t>
         </is>
       </c>
-      <c r="K111" s="15" t="inlineStr"/>
-      <c r="L111" s="6" t="inlineStr">
+      <c r="K114" s="15" t="inlineStr"/>
+      <c r="L114" s="6" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M111" s="15" t="inlineStr"/>
-      <c r="N111" s="15" t="inlineStr"/>
-      <c r="O111" s="15" t="inlineStr"/>
-      <c r="P111" s="15" t="inlineStr">
+      <c r="M114" s="15" t="inlineStr"/>
+      <c r="N114" s="15" t="inlineStr"/>
+      <c r="O114" s="15" t="inlineStr"/>
+      <c r="P114" s="15" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="Q111" s="15" t="inlineStr">
+      <c r="Q114" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R111" s="16" t="inlineStr">
+      <c r="R114" s="16" t="inlineStr">
         <is>
           <t>Produced: LAN day-before</t>
         </is>
@@ -19893,7 +20109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T108"/>
+  <dimension ref="A1:T109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -24170,7 +24386,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr"/>
@@ -24181,7 +24397,7 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
@@ -24214,10 +24430,8 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P52" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="P52" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Q52" s="9" t="inlineStr"/>
       <c r="R52" s="10" t="inlineStr">
@@ -24257,7 +24471,7 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr"/>
@@ -24268,12 +24482,12 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>1 bin</t>
+          <t>2 bins</t>
         </is>
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>Prep at LAN; send Thu PM</t>
+          <t>Prep at LAN; send Thu PM | ⚠ NO RECIPE</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
@@ -24301,10 +24515,8 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P53" s="9" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="P53" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Q53" s="9" t="inlineStr"/>
       <c r="R53" s="10" t="inlineStr">
@@ -26442,7 +26654,7 @@
       </c>
       <c r="E80" s="16" t="inlineStr">
         <is>
-          <t>Cold Egg Salad + Bean Salad → Fri Lunch</t>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
@@ -26482,13 +26694,11 @@
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="O80" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
+      <c r="O80" s="15" t="n">
+        <v>0.5</v>
       </c>
       <c r="P80" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="15" t="inlineStr">
         <is>
@@ -26497,7 +26707,7 @@
       </c>
       <c r="R80" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
         </is>
       </c>
     </row>
@@ -26509,55 +26719,70 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
         </is>
       </c>
     </row>
@@ -26574,122 +26799,103 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
         <is>
           <t>NOTE</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Bean Salad (Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>Cold salad pre-sent; no AM run needed</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>Rex</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C83" s="13" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D83" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E83" s="14" t="inlineStr">
-        <is>
-          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
-        </is>
-      </c>
-      <c r="F83" s="13" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="G83" s="13" t="inlineStr"/>
-      <c r="H83" s="13" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I83" s="13" t="inlineStr"/>
-      <c r="J83" s="14" t="inlineStr"/>
-      <c r="K83" s="13" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M83" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N83" s="13" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O83" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P83" s="13" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="Q83" s="13" t="inlineStr"/>
-      <c r="R83" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Sunday Dinner</t>
-        </is>
-      </c>
-      <c r="S83" s="11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -26715,29 +26921,25 @@
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
+          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>80 lbs</t>
+          <t>100 lbs</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr"/>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I84" s="13" t="inlineStr"/>
       <c r="J84" s="14" t="inlineStr"/>
       <c r="K84" s="13" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="L84" s="5" t="inlineStr">
@@ -26752,7 +26954,7 @@
       </c>
       <c r="N84" s="13" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>SUNDAY</t>
         </is>
       </c>
       <c r="O84" s="13" t="inlineStr">
@@ -26760,17 +26962,19 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P84" s="13" t="n">
-        <v>2</v>
+      <c r="P84" s="13" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
       </c>
       <c r="Q84" s="13" t="inlineStr"/>
       <c r="R84" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Wednesday Dinner</t>
-        </is>
-      </c>
-      <c r="S84" s="12" t="n">
-        <v>5</v>
+          <t>Serves: Wk. 4 Sunday Dinner</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -26786,71 +26990,72 @@
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="F85" s="13" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="inlineStr"/>
+      <c r="H85" s="13" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="J85" s="14" t="inlineStr"/>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M85" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N85" s="13" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O85" s="13" t="inlineStr">
+        <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="G85" s="13" t="inlineStr"/>
-      <c r="H85" s="13" t="inlineStr"/>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="J85" s="14" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="K85" s="13" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M85" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N85" s="13" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O85" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P85" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="P85" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="Q85" s="13" t="inlineStr"/>
       <c r="R85" s="14" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
+          <t>Serves: Wk. 4 Wednesday Dinner</t>
+        </is>
+      </c>
+      <c r="S85" s="12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -26876,19 +27081,19 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
+          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
         </is>
       </c>
       <c r="F86" s="13" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="G86" s="13" t="inlineStr"/>
       <c r="H86" s="13" t="inlineStr"/>
       <c r="I86" s="13" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
@@ -26898,7 +27103,7 @@
       </c>
       <c r="K86" s="13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L86" s="5" t="inlineStr">
@@ -26923,7 +27128,7 @@
       </c>
       <c r="P86" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q86" s="13" t="inlineStr"/>
@@ -26934,252 +27139,248 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="A87" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C87" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="inlineStr"/>
+      <c r="H87" s="13" t="inlineStr"/>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J87" s="14" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M87" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N87" s="13" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O87" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P87" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q87" s="13" t="inlineStr"/>
+      <c r="R87" s="14" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Heat Spring Rolls (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>200 pcs</t>
         </is>
       </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>2 hotels</t>
         </is>
       </c>
-      <c r="J87" s="8" t="inlineStr">
+      <c r="J88" s="8" t="inlineStr">
         <is>
           <t>Purchased frozen; heat day-of at Bloor</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="K88" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="L88" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M87" s="7" t="inlineStr">
+      <c r="M88" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N87" s="7" t="inlineStr">
+      <c r="N88" s="7" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O87" s="7" t="inlineStr">
+      <c r="O88" s="7" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P87" s="7" t="inlineStr">
+      <c r="P88" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q87" s="7" t="inlineStr"/>
-      <c r="R87" s="8" t="inlineStr">
+      <c r="Q88" s="7" t="inlineStr"/>
+      <c r="R88" s="8" t="inlineStr">
         <is>
           <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="13" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C88" s="13" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E88" s="14" t="inlineStr">
+      <c r="E89" s="14" t="inlineStr">
         <is>
           <t>Bok Choy (Fri Dinner side)</t>
         </is>
       </c>
-      <c r="F88" s="13" t="inlineStr">
+      <c r="F89" s="13" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="G88" s="13" t="inlineStr"/>
-      <c r="H88" s="13" t="inlineStr">
+      <c r="G89" s="13" t="inlineStr"/>
+      <c r="H89" s="13" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I88" s="13" t="inlineStr">
+      <c r="I89" s="13" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="J88" s="14" t="inlineStr">
+      <c r="J89" s="14" t="inlineStr">
         <is>
           <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
         </is>
       </c>
-      <c r="K88" s="13" t="inlineStr">
+      <c r="K89" s="13" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M88" s="13" t="inlineStr">
+      <c r="M89" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N88" s="13" t="inlineStr">
+      <c r="N89" s="13" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O88" s="13" t="inlineStr">
+      <c r="O89" s="13" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P88" s="13" t="n">
+      <c r="P89" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="Q88" s="13" t="inlineStr"/>
-      <c r="R88" s="14" t="inlineStr">
+      <c r="Q89" s="13" t="inlineStr"/>
+      <c r="R89" s="14" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D89" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E89" s="16" t="inlineStr">
-        <is>
-          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="F89" s="15" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="G89" s="15" t="inlineStr"/>
-      <c r="H89" s="15" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="J89" s="16" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K89" s="15" t="inlineStr"/>
-      <c r="L89" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M89" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N89" s="15" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O89" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P89" s="15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q89" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R89" s="16" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
         </is>
       </c>
     </row>
@@ -27206,19 +27407,23 @@
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr"/>
-      <c r="H90" s="15" t="inlineStr"/>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="J90" s="16" t="inlineStr">
@@ -27249,7 +27454,7 @@
       </c>
       <c r="P90" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q90" s="15" t="inlineStr">
@@ -27286,19 +27491,19 @@
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>HOT Spring Rolls → Dinner side</t>
+          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="G91" s="15" t="inlineStr"/>
       <c r="H91" s="15" t="inlineStr"/>
       <c r="I91" s="15" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J91" s="16" t="inlineStr">
@@ -27329,103 +27534,97 @@
       </c>
       <c r="P91" s="15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q91" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R91" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B92" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>HOT Spring Rolls → Dinner side</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr"/>
+      <c r="H92" s="15" t="inlineStr"/>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J92" s="16" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K92" s="15" t="inlineStr"/>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M92" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N92" s="15" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P92" s="15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q91" s="15" t="inlineStr">
+      <c r="Q92" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R91" s="16" t="inlineStr">
+      <c r="R92" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Friday Dinner (same day)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr"/>
-      <c r="L92" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M92" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O92" s="3" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P92" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q92" s="3" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R92" s="4" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Production</t>
         </is>
       </c>
     </row>
@@ -27452,17 +27651,17 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+          <t>HOT CONC Salad Beef → Lunch</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>12 lbs</t>
+          <t>80 lbs</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>4 oz</t>
+          <t>6 oz</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -27472,7 +27671,7 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>0.5u</t>
+          <t>2u</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -27502,182 +27701,183 @@
         </is>
       </c>
       <c r="P93" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R93" s="4" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Friday Production</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P94" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q93" s="3" t="inlineStr">
+      <c r="Q94" s="3" t="inlineStr">
         <is>
           <t>AM</t>
         </is>
       </c>
-      <c r="R93" s="4" t="inlineStr">
+      <c r="R94" s="4" t="inlineStr">
         <is>
           <t>Produced: Wk. 2 Friday Production</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>HEAT</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>92 lbs (80+12)</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="H94" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr">
         <is>
           <t>Reheat bagged</t>
         </is>
       </c>
-      <c r="K94" s="7" t="inlineStr">
+      <c r="K95" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M94" s="7" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N94" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O94" s="7" t="inlineStr">
+      <c r="O95" s="7" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P94" s="7" t="inlineStr"/>
-      <c r="Q94" s="7" t="inlineStr"/>
-      <c r="R94" s="8" t="inlineStr">
+      <c r="P95" s="7" t="inlineStr"/>
+      <c r="Q95" s="7" t="inlineStr"/>
+      <c r="R95" s="8" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Sunday Production</t>
         </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C95" s="9" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E95" s="10" t="inlineStr">
-        <is>
-          <t>Cut/Season Tandoori Pork</t>
-        </is>
-      </c>
-      <c r="F95" s="9" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="G95" s="9" t="inlineStr"/>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>hotels</t>
-        </is>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="J95" s="10" t="inlineStr">
-        <is>
-          <t>Season w/Vindaloo Dry Spice Mix</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L95" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N95" s="9" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O95" s="9" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P95" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q95" s="9" t="inlineStr"/>
-      <c r="R95" s="10" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
-        </is>
-      </c>
-      <c r="S95" s="12" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="96">
@@ -27703,26 +27903,30 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>Tandoori Marinade</t>
+          <t>Cut/Season Tandoori Pork</t>
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>hotels</t>
         </is>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J96" s="10" t="inlineStr"/>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>Season w/Vindaloo Dry Spice Mix</t>
+        </is>
+      </c>
       <c r="K96" s="9" t="inlineStr">
         <is>
           <t>60</t>
@@ -27740,27 +27944,25 @@
       </c>
       <c r="N96" s="9" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="O96" s="9" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P96" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P96" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Q96" s="9" t="inlineStr"/>
       <c r="R96" s="10" t="inlineStr">
         <is>
-          <t>Serves: Tandoori Production Wk. 4 Monday</t>
-        </is>
-      </c>
-      <c r="S96" s="11" t="n">
-        <v>2</v>
+          <t>Serves: Wk. 4 Friday Dinner</t>
+        </is>
+      </c>
+      <c r="S96" s="12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="97">
@@ -27786,29 +27988,29 @@
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
+          <t>Tandoori Marinade</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr"/>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>bins</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>3 bins (6u)</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J97" s="10" t="inlineStr"/>
       <c r="K97" s="9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L97" s="5" t="inlineStr">
@@ -27823,27 +28025,27 @@
       </c>
       <c r="N97" s="9" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="O97" s="9" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P97" s="9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q97" s="9" t="inlineStr"/>
       <c r="R97" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
-        </is>
-      </c>
-      <c r="S97" s="12" t="n">
-        <v>3</v>
+          <t>Serves: Tandoori Production Wk. 4 Monday</t>
+        </is>
+      </c>
+      <c r="S97" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -27854,7 +28056,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -27869,33 +28071,29 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>Massaman Curry Paste</t>
+          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
         </is>
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>recipe</t>
+          <t>155</t>
         </is>
       </c>
       <c r="G98" s="9" t="inlineStr"/>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>cambro</t>
+          <t>bins</t>
         </is>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J98" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
-        </is>
-      </c>
+          <t>3 bins (6u)</t>
+        </is>
+      </c>
+      <c r="J98" s="10" t="inlineStr"/>
       <c r="K98" s="9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
@@ -27918,8 +28116,10 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P98" s="9" t="n">
-        <v>0.5</v>
+      <c r="P98" s="9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="10" t="inlineStr">
@@ -27928,7 +28128,7 @@
         </is>
       </c>
       <c r="S98" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -27954,29 +28154,33 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>Portobello Cheese Melt prep (→ Wk4 Sun Lunch — Veg)</t>
+          <t>Massaman Curry Paste</t>
         </is>
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="G99" s="9" t="inlineStr"/>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I99" s="9" t="inlineStr"/>
+          <t>cambro</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J99" s="10" t="inlineStr">
         <is>
-          <t>Prep/slice portobello; hold chilled; cook day-of</t>
+          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
         </is>
       </c>
       <c r="K99" s="9" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
@@ -27991,25 +28195,25 @@
       </c>
       <c r="N99" s="9" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="O99" s="9" t="inlineStr">
         <is>
-          <t>LUNCH</t>
+          <t>DINNER</t>
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q99" s="9" t="inlineStr"/>
       <c r="R99" s="10" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
-        </is>
-      </c>
-      <c r="S99" s="11" t="n">
-        <v>2</v>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S99" s="12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="100">
@@ -28020,7 +28224,7 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>SATURDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
@@ -28035,38 +28239,34 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Portobello Cheese Melt prep (→ Wk4 Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>???</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr"/>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr"/>
       <c r="J100" s="10" t="inlineStr">
         <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+          <t>Prep/slice portobello; hold chilled; cook day-of</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L100" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M100" s="9" t="inlineStr">
@@ -28084,10 +28284,8 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P100" s="9" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="P100" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q100" s="9" t="inlineStr"/>
       <c r="R100" s="10" t="inlineStr">
@@ -28096,7 +28294,7 @@
         </is>
       </c>
       <c r="S100" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -28122,20 +28320,28 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>3 bins + 1 bag</t>
         </is>
       </c>
       <c r="G101" s="9" t="inlineStr"/>
-      <c r="H101" s="9" t="inlineStr"/>
-      <c r="I101" s="9" t="inlineStr"/>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
       <c r="J101" s="10" t="inlineStr">
         <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
@@ -28165,7 +28371,7 @@
       </c>
       <c r="P101" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Q101" s="9" t="inlineStr"/>
@@ -28201,38 +28407,30 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>3 hotels</t>
         </is>
       </c>
       <c r="G102" s="9" t="inlineStr"/>
-      <c r="H102" s="9" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
+      <c r="H102" s="9" t="inlineStr"/>
+      <c r="I102" s="9" t="inlineStr"/>
       <c r="J102" s="10" t="inlineStr">
         <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M102" s="9" t="inlineStr">
@@ -28252,7 +28450,7 @@
       </c>
       <c r="P102" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q102" s="9" t="inlineStr"/>
@@ -28266,59 +28464,55 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="13" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B103" s="13" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C103" s="13" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D103" s="13" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E103" s="14" t="inlineStr">
-        <is>
-          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
-        </is>
-      </c>
-      <c r="F103" s="13" t="inlineStr">
-        <is>
-          <t>110lbs</t>
-        </is>
-      </c>
-      <c r="G103" s="13" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="H103" s="13" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="J103" s="14" t="inlineStr">
-        <is>
-          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
-        </is>
-      </c>
-      <c r="K103" s="13" t="inlineStr">
-        <is>
-          <t>320</t>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="inlineStr"/>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
@@ -28326,34 +28520,34 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M103" s="13" t="inlineStr">
+      <c r="M103" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N103" s="13" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O103" s="13" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P103" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q103" s="13" t="inlineStr"/>
-      <c r="R103" s="14" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Saturday Dinner</t>
-        </is>
-      </c>
-      <c r="S103" s="12" t="n">
-        <v>7</v>
+      <c r="N103" s="9" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O103" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P103" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q103" s="9" t="inlineStr"/>
+      <c r="R103" s="10" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S103" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -28369,7 +28563,7 @@
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
@@ -28379,29 +28573,37 @@
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>Potato Wedges (Sat Dinner side)</t>
+          <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
         </is>
       </c>
       <c r="F104" s="13" t="inlineStr">
         <is>
+          <t>110lbs</t>
+        </is>
+      </c>
+      <c r="G104" s="13" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
+      <c r="H104" s="13" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G104" s="13" t="inlineStr"/>
-      <c r="H104" s="13" t="inlineStr"/>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>Purchased frozen; oven</t>
+          <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
         </is>
       </c>
       <c r="K104" s="13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>320</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
@@ -28411,7 +28613,7 @@
       </c>
       <c r="M104" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N104" s="13" t="inlineStr">
@@ -28432,73 +28634,90 @@
       <c r="Q104" s="13" t="inlineStr"/>
       <c r="R104" s="14" t="inlineStr">
         <is>
+          <t>Serves: Wk. 4 Saturday Dinner</t>
+        </is>
+      </c>
+      <c r="S104" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E105" s="14" t="inlineStr">
+        <is>
+          <t>Potato Wedges (Sat Dinner side)</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G105" s="13" t="inlineStr"/>
+      <c r="H105" s="13" t="inlineStr"/>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>Purchased frozen; oven</t>
+        </is>
+      </c>
+      <c r="K105" s="13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M105" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N105" s="13" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O105" s="13" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P105" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q105" s="13" t="inlineStr"/>
+      <c r="R105" s="14" t="inlineStr">
+        <is>
           <t>Serves: Wk. 3 Saturday Dinner</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B105" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C105" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E105" s="16" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F105" s="15" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G105" s="15" t="inlineStr"/>
-      <c r="H105" s="15" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I105" s="15" t="inlineStr"/>
-      <c r="J105" s="16" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K105" s="15" t="inlineStr"/>
-      <c r="L105" s="19" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M105" s="15" t="inlineStr"/>
-      <c r="N105" s="15" t="inlineStr"/>
-      <c r="O105" s="15" t="inlineStr"/>
-      <c r="P105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="15" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R105" s="16" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -28525,7 +28744,7 @@
       </c>
       <c r="E106" s="16" t="inlineStr">
         <is>
-          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
@@ -28536,40 +28755,24 @@
       <c r="G106" s="15" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>boxes</t>
-        </is>
-      </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I106" s="15" t="inlineStr"/>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>Vendor → Rex | Driver collects ordered pizza</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K106" s="15" t="inlineStr"/>
-      <c r="L106" s="20" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="M106" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N106" s="15" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O106" s="15" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
+      <c r="L106" s="19" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="M106" s="15" t="inlineStr"/>
+      <c r="N106" s="15" t="inlineStr"/>
+      <c r="O106" s="15" t="inlineStr"/>
       <c r="P106" s="18" t="n">
         <v>0</v>
       </c>
@@ -28580,7 +28783,7 @@
       </c>
       <c r="R106" s="16" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Saturday Dinner</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
     </row>
@@ -28607,34 +28810,34 @@
       </c>
       <c r="E107" s="16" t="inlineStr">
         <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="G107" s="15" t="inlineStr"/>
       <c r="H107" s="15" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
+          <t>boxes</t>
         </is>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>order</t>
         </is>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>LAN → Rex fridge</t>
+          <t>Vendor → Rex | Driver collects ordered pizza</t>
         </is>
       </c>
       <c r="K107" s="15" t="inlineStr"/>
-      <c r="L107" s="6" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L107" s="20" t="inlineStr">
+        <is>
+          <t>Vendor</t>
         </is>
       </c>
       <c r="M107" s="15" t="inlineStr">
@@ -28652,10 +28855,8 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P107" s="15" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="P107" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="Q107" s="15" t="inlineStr">
         <is>
@@ -28664,7 +28865,7 @@
       </c>
       <c r="R107" s="16" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
+          <t>Serves: Wk. 3 Saturday Dinner</t>
         </is>
       </c>
     </row>
@@ -28691,66 +28892,150 @@
       </c>
       <c r="E108" s="16" t="inlineStr">
         <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="inlineStr"/>
+      <c r="H108" s="15" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="J108" s="16" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="K108" s="15" t="inlineStr"/>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M108" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N108" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P108" s="15" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Q108" s="15" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R108" s="16" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
           <t>HOT Potato Wedges → Dinner</t>
         </is>
       </c>
-      <c r="F108" s="15" t="inlineStr">
+      <c r="F109" s="15" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G108" s="15" t="inlineStr">
+      <c r="G109" s="15" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="H108" s="15" t="inlineStr">
+      <c r="H109" s="15" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I108" s="15" t="inlineStr">
+      <c r="I109" s="15" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J108" s="16" t="inlineStr">
+      <c r="J109" s="16" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K108" s="15" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="K109" s="15" t="inlineStr"/>
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M108" s="15" t="inlineStr">
+      <c r="M109" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N108" s="15" t="inlineStr">
+      <c r="N109" s="15" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O108" s="15" t="inlineStr">
+      <c r="O109" s="15" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P108" s="15" t="inlineStr">
+      <c r="P109" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q108" s="15" t="inlineStr">
+      <c r="Q109" s="15" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R108" s="16" t="inlineStr">
+      <c r="R109" s="16" t="inlineStr">
         <is>
           <t>Produced: Wk. 3 Saturday Dinner (same day)</t>
         </is>

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -5918,7 +5918,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>LAN</t>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Produced: Wk. 1 Wednesday Production (LAN)</t>
+          <t>Produced: Wk. 1 Thursday Production (Bloor)</t>
         </is>
       </c>
     </row>

--- a/00_Production_Source_Table.xlsx
+++ b/00_Production_Source_Table.xlsx
@@ -20868,7 +20868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:T112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -25638,330 +25638,340 @@
       <c r="T56" s="43" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="44" t="inlineStr">
+      <c r="A57" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="44" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D57" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E57" s="45" t="inlineStr">
+        <is>
+          <t>Bake Tomato Fish (Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="F57" s="44" t="inlineStr">
+        <is>
+          <t>150 pcs</t>
+        </is>
+      </c>
+      <c r="G57" s="44" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="H57" s="44" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I57" s="44" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="J57" s="45" t="inlineStr">
+        <is>
+          <t>Trayed/seasoned prev day; bake day-of</t>
+        </is>
+      </c>
+      <c r="K57" s="44" t="n">
+        <v>90</v>
+      </c>
+      <c r="L57" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M57" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" s="44" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O57" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P57" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="44" t="n"/>
+      <c r="R57" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Wednesday Dinner</t>
+        </is>
+      </c>
+      <c r="S57" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="43" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C58" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D58" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E58" s="45" t="inlineStr">
+        <is>
+          <t>Bake Tomato Tofu (Wed Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="F58" s="44" t="inlineStr">
+        <is>
+          <t>15 pcs</t>
+        </is>
+      </c>
+      <c r="G58" s="44" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="H58" s="44" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I58" s="44" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J58" s="45" t="inlineStr">
+        <is>
+          <t>Seasoned prev day; bake day-of</t>
+        </is>
+      </c>
+      <c r="K58" s="44" t="n">
+        <v>30</v>
+      </c>
+      <c r="L58" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M58" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" s="44" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O58" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P58" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="44" t="n"/>
+      <c r="R58" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Wednesday Dinner</t>
+        </is>
+      </c>
+      <c r="S58" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="43" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B57" s="44" t="inlineStr">
+      <c r="B59" s="44" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C57" s="44" t="inlineStr">
+      <c r="C59" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D57" s="44" t="inlineStr">
+      <c r="D59" s="44" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E57" s="45" t="inlineStr">
+      <c r="E59" s="45" t="inlineStr">
         <is>
           <t>Herbed Couscous (Wed Dinner)</t>
         </is>
       </c>
-      <c r="F57" s="44" t="inlineStr">
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G57" s="44" t="inlineStr">
+      <c r="G59" s="44" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="H57" s="44" t="inlineStr">
+      <c r="H59" s="44" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I57" s="44" t="inlineStr">
+      <c r="I59" s="44" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J57" s="45" t="inlineStr"/>
-      <c r="K57" s="44" t="inlineStr">
+      <c r="J59" s="45" t="inlineStr"/>
+      <c r="K59" s="44" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="L57" s="41" t="inlineStr">
+      <c r="L59" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M57" s="44" t="inlineStr">
+      <c r="M59" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N57" s="44" t="inlineStr">
+      <c r="N59" s="44" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O57" s="44" t="inlineStr">
+      <c r="O59" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P57" s="44" t="inlineStr">
+      <c r="P59" s="44" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q57" s="44" t="inlineStr"/>
-      <c r="R57" s="45" t="inlineStr">
+      <c r="Q59" s="44" t="inlineStr"/>
+      <c r="R59" s="45" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Wednesday Dinner</t>
-        </is>
-      </c>
-      <c r="S57" s="42" t="n"/>
-      <c r="T57" s="43" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B58" s="44" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C58" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D58" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E58" s="45" t="inlineStr">
-        <is>
-          <t>Steam Broccoli (Wed Dinner side)</t>
-        </is>
-      </c>
-      <c r="F58" s="44" t="inlineStr">
-        <is>
-          <t>3 bins</t>
-        </is>
-      </c>
-      <c r="G58" s="44" t="inlineStr">
-        <is>
-          <t>4 oz</t>
-        </is>
-      </c>
-      <c r="H58" s="44" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I58" s="44" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="J58" s="45" t="inlineStr"/>
-      <c r="K58" s="44" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="L58" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M58" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N58" s="44" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="O58" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P58" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Q58" s="44" t="inlineStr"/>
-      <c r="R58" s="45" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Wednesday Dinner</t>
-        </is>
-      </c>
-      <c r="S58" s="42" t="n"/>
-      <c r="T58" s="43" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B59" s="52" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="C59" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D59" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E59" s="53" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F59" s="52" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G59" s="52" t="inlineStr"/>
-      <c r="H59" s="52" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I59" s="52" t="inlineStr"/>
-      <c r="J59" s="53" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K59" s="52" t="inlineStr"/>
-      <c r="L59" s="55" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M59" s="52" t="inlineStr"/>
-      <c r="N59" s="52" t="inlineStr"/>
-      <c r="O59" s="52" t="inlineStr"/>
-      <c r="P59" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R59" s="53" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
         </is>
       </c>
       <c r="S59" s="42" t="n"/>
       <c r="T59" s="43" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="52" t="inlineStr">
+      <c r="A60" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B60" s="52" t="inlineStr">
+      <c r="B60" s="44" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="C60" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D60" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E60" s="53" t="inlineStr">
-        <is>
-          <t>HOT Baked Tomato Fish → Dinner</t>
-        </is>
-      </c>
-      <c r="F60" s="52" t="inlineStr">
-        <is>
-          <t>150 pcs</t>
-        </is>
-      </c>
-      <c r="G60" s="52" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="H60" s="52" t="inlineStr">
-        <is>
-          <t>hotels</t>
-        </is>
-      </c>
-      <c r="I60" s="52" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="J60" s="53" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K60" s="52" t="inlineStr"/>
-      <c r="L60" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M60" s="52" t="inlineStr">
+      <c r="C60" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D60" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E60" s="45" t="inlineStr">
+        <is>
+          <t>Steam Broccoli (Wed Dinner side)</t>
+        </is>
+      </c>
+      <c r="F60" s="44" t="inlineStr">
+        <is>
+          <t>3 bins</t>
+        </is>
+      </c>
+      <c r="G60" s="44" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="H60" s="44" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I60" s="44" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J60" s="45" t="inlineStr"/>
+      <c r="K60" s="44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L60" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M60" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N60" s="52" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="O60" s="52" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P60" s="52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q60" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R60" s="53" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Tuesday Production (trayed prev day)</t>
+      <c r="N60" s="44" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O60" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P60" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q60" s="44" t="inlineStr"/>
+      <c r="R60" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Wednesday Dinner</t>
         </is>
       </c>
       <c r="S60" s="42" t="n"/>
@@ -25990,59 +26000,37 @@
       </c>
       <c r="E61" s="53" t="inlineStr">
         <is>
-          <t>HOT Baked Tomato Tofu → Dinner (Veg)</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F61" s="52" t="inlineStr">
         <is>
-          <t>50 pcs</t>
-        </is>
-      </c>
-      <c r="G61" s="52" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="G61" s="52" t="inlineStr"/>
       <c r="H61" s="52" t="inlineStr">
         <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I61" s="52" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I61" s="52" t="inlineStr"/>
       <c r="J61" s="53" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K61" s="52" t="inlineStr"/>
-      <c r="L61" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M61" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N61" s="52" t="inlineStr">
-        <is>
-          <t>TUESDAY</t>
-        </is>
-      </c>
-      <c r="O61" s="52" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P61" s="52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="L61" s="55" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="M61" s="52" t="inlineStr"/>
+      <c r="N61" s="52" t="inlineStr"/>
+      <c r="O61" s="52" t="inlineStr"/>
+      <c r="P61" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="Q61" s="52" t="inlineStr">
         <is>
@@ -26051,7 +26039,7 @@
       </c>
       <c r="R61" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Tuesday Production (seasoned prev day)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
       <c r="S61" s="42" t="n"/>
@@ -26080,16 +26068,24 @@
       </c>
       <c r="E62" s="53" t="inlineStr">
         <is>
-          <t>HOT Herbed Couscous → Dinner side</t>
+          <t>HOT Baked Tomato Fish → Dinner</t>
         </is>
       </c>
       <c r="F62" s="52" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="G62" s="52" t="inlineStr"/>
-      <c r="H62" s="52" t="inlineStr"/>
+          <t>150 pcs</t>
+        </is>
+      </c>
+      <c r="G62" s="52" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="H62" s="52" t="inlineStr">
+        <is>
+          <t>hotels</t>
+        </is>
+      </c>
       <c r="I62" s="52" t="inlineStr">
         <is>
           <t>4 hotels</t>
@@ -26113,12 +26109,12 @@
       </c>
       <c r="N62" s="52" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="O62" s="52" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P62" s="52" t="inlineStr">
@@ -26133,7 +26129,7 @@
       </c>
       <c r="R62" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Wednesday Dinner (same day)</t>
+          <t>Produced: Wk. 3 Tuesday Production (trayed prev day)</t>
         </is>
       </c>
       <c r="S62" s="42" t="n"/>
@@ -26162,30 +26158,38 @@
       </c>
       <c r="E63" s="53" t="inlineStr">
         <is>
-          <t>HOT Broccoli → Dinner side</t>
+          <t>HOT Baked Tomato Tofu → Dinner (Veg)</t>
         </is>
       </c>
       <c r="F63" s="52" t="inlineStr">
         <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G63" s="52" t="inlineStr"/>
-      <c r="H63" s="52" t="inlineStr"/>
+          <t>50 pcs</t>
+        </is>
+      </c>
+      <c r="G63" s="52" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="H63" s="52" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
       <c r="I63" s="52" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J63" s="53" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K63" s="52" t="inlineStr"/>
-      <c r="L63" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L63" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M63" s="52" t="inlineStr">
@@ -26195,17 +26199,17 @@
       </c>
       <c r="N63" s="52" t="inlineStr">
         <is>
-          <t>WEDNESDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="O63" s="52" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P63" s="52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q63" s="52" t="inlineStr">
@@ -26215,7 +26219,7 @@
       </c>
       <c r="R63" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Wednesday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 3 Tuesday Production (seasoned prev day)</t>
         </is>
       </c>
       <c r="S63" s="42" t="n"/>
@@ -26244,26 +26248,30 @@
       </c>
       <c r="E64" s="53" t="inlineStr">
         <is>
-          <t>Cold Tomato Cucumber Salad → Thu Lunch</t>
+          <t>HOT Herbed Couscous → Dinner side</t>
         </is>
       </c>
       <c r="F64" s="52" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="G64" s="52" t="inlineStr"/>
       <c r="H64" s="52" t="inlineStr"/>
-      <c r="I64" s="52" t="inlineStr"/>
+      <c r="I64" s="52" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
       <c r="J64" s="53" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K64" s="52" t="inlineStr"/>
-      <c r="L64" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L64" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M64" s="52" t="inlineStr">
@@ -26271,15 +26279,19 @@
           <t>3</t>
         </is>
       </c>
-      <c r="N64" s="52" t="inlineStr"/>
+      <c r="N64" s="52" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
       <c r="O64" s="52" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
+          <t>DINNER</t>
         </is>
       </c>
       <c r="P64" s="52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q64" s="52" t="inlineStr">
@@ -26289,418 +26301,420 @@
       </c>
       <c r="R64" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk.3 Tue Production (LAN)</t>
+          <t>Produced: Wk. 3 Wednesday Dinner (same day)</t>
         </is>
       </c>
       <c r="S64" s="42" t="n"/>
       <c r="T64" s="43" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="39" t="inlineStr">
+      <c r="A65" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B65" s="39" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C65" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D65" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E65" s="40" t="inlineStr">
-        <is>
-          <t>HOT Halal Chicken Burgers → Lunch</t>
-        </is>
-      </c>
-      <c r="F65" s="39" t="inlineStr">
-        <is>
-          <t>185 pcs</t>
-        </is>
-      </c>
-      <c r="G65" s="39" t="inlineStr"/>
-      <c r="H65" s="39" t="inlineStr"/>
-      <c r="I65" s="39" t="inlineStr">
+      <c r="B65" s="52" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="C65" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D65" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E65" s="53" t="inlineStr">
+        <is>
+          <t>HOT Broccoli → Dinner side</t>
+        </is>
+      </c>
+      <c r="F65" s="52" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J65" s="40" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K65" s="39" t="inlineStr"/>
-      <c r="L65" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M65" s="39" t="inlineStr">
+      <c r="G65" s="52" t="inlineStr"/>
+      <c r="H65" s="52" t="inlineStr"/>
+      <c r="I65" s="52" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J65" s="53" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K65" s="52" t="inlineStr"/>
+      <c r="L65" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M65" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N65" s="39" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O65" s="39" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P65" s="39" t="inlineStr">
+      <c r="N65" s="52" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O65" s="52" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P65" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q65" s="39" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R65" s="40" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Sunday Production (shaped); Wk. 3 Thursday Lunch (cooked)</t>
+      <c r="Q65" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R65" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Wednesday Dinner (LAN same day)</t>
         </is>
       </c>
       <c r="S65" s="42" t="n"/>
       <c r="T65" s="43" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="39" t="inlineStr">
+      <c r="A66" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B66" s="39" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C66" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D66" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E66" s="40" t="inlineStr">
-        <is>
-          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="F66" s="39" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="G66" s="39" t="inlineStr"/>
-      <c r="H66" s="39" t="inlineStr"/>
-      <c r="I66" s="39" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J66" s="40" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K66" s="39" t="inlineStr"/>
-      <c r="L66" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M66" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N66" s="39" t="inlineStr">
+      <c r="B66" s="52" t="inlineStr">
         <is>
           <t>WEDNESDAY</t>
         </is>
       </c>
-      <c r="O66" s="39" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P66" s="39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q66" s="39" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R66" s="40" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Wednesday Production; Wk. 3 Thursday Lunch (cooked)</t>
+      <c r="C66" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D66" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E66" s="53" t="inlineStr">
+        <is>
+          <t>Cold Tomato Cucumber Salad → Thu Lunch</t>
+        </is>
+      </c>
+      <c r="F66" s="52" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="G66" s="52" t="inlineStr"/>
+      <c r="H66" s="52" t="inlineStr"/>
+      <c r="I66" s="52" t="inlineStr"/>
+      <c r="J66" s="53" t="inlineStr">
+        <is>
+          <t>LAN → Rex</t>
+        </is>
+      </c>
+      <c r="K66" s="52" t="inlineStr"/>
+      <c r="L66" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M66" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N66" s="52" t="inlineStr"/>
+      <c r="O66" s="52" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P66" s="52" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="Q66" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R66" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk.3 Tue Production (LAN)</t>
         </is>
       </c>
       <c r="S66" s="42" t="n"/>
       <c r="T66" s="43" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="44" t="inlineStr">
+      <c r="A67" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B67" s="44" t="inlineStr">
+      <c r="B67" s="39" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C67" s="44" t="inlineStr">
+      <c r="C67" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D67" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E67" s="40" t="inlineStr">
+        <is>
+          <t>HOT Halal Chicken Burgers → Lunch</t>
+        </is>
+      </c>
+      <c r="F67" s="39" t="inlineStr">
+        <is>
+          <t>185 pcs</t>
+        </is>
+      </c>
+      <c r="G67" s="39" t="inlineStr"/>
+      <c r="H67" s="39" t="inlineStr"/>
+      <c r="I67" s="39" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J67" s="40" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K67" s="39" t="inlineStr"/>
+      <c r="L67" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M67" s="39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N67" s="39" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O67" s="39" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D67" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E67" s="45" t="inlineStr">
-        <is>
-          <t>Halal Chicken Burgers (Thu Lunch)</t>
-        </is>
-      </c>
-      <c r="F67" s="44" t="inlineStr">
-        <is>
-          <t>150 pcs</t>
-        </is>
-      </c>
-      <c r="G67" s="44" t="inlineStr">
-        <is>
-          <t>1 pc</t>
-        </is>
-      </c>
-      <c r="H67" s="44" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I67" s="44" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="J67" s="45" t="inlineStr">
-        <is>
-          <t>Oven — 30 min day-of</t>
-        </is>
-      </c>
-      <c r="K67" s="44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L67" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M67" s="44" t="inlineStr">
+      <c r="P67" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N67" s="44" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O67" s="44" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P67" s="44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q67" s="44" t="inlineStr"/>
-      <c r="R67" s="45" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Lunch</t>
+      <c r="Q67" s="39" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R67" s="40" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Sunday Production (shaped); Wk. 3 Thursday Lunch (cooked)</t>
         </is>
       </c>
       <c r="S67" s="42" t="n"/>
       <c r="T67" s="43" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="44" t="inlineStr">
+      <c r="A68" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B68" s="44" t="inlineStr">
+      <c r="B68" s="39" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C68" s="44" t="inlineStr">
+      <c r="C68" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D68" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E68" s="40" t="inlineStr">
+        <is>
+          <t>HOT Quinoa Burgers → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="F68" s="39" t="inlineStr">
+        <is>
+          <t>30 pcs</t>
+        </is>
+      </c>
+      <c r="G68" s="39" t="inlineStr"/>
+      <c r="H68" s="39" t="inlineStr"/>
+      <c r="I68" s="39" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J68" s="40" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K68" s="39" t="inlineStr"/>
+      <c r="L68" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M68" s="39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N68" s="39" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O68" s="39" t="inlineStr">
         <is>
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="D68" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E68" s="45" t="inlineStr">
-        <is>
-          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
-        </is>
-      </c>
-      <c r="F68" s="44" t="inlineStr">
-        <is>
-          <t>30 pcs</t>
-        </is>
-      </c>
-      <c r="G68" s="44" t="inlineStr"/>
-      <c r="H68" s="44" t="inlineStr"/>
-      <c r="I68" s="44" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J68" s="45" t="inlineStr">
-        <is>
-          <t>Pan fry; send hot AM</t>
-        </is>
-      </c>
-      <c r="K68" s="44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L68" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M68" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N68" s="44" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O68" s="44" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P68" s="44" t="inlineStr">
+      <c r="P68" s="39" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q68" s="44" t="inlineStr"/>
-      <c r="R68" s="45" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Lunch</t>
+      <c r="Q68" s="39" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R68" s="40" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Wednesday Production; Wk. 3 Thursday Lunch (cooked)</t>
         </is>
       </c>
       <c r="S68" s="42" t="n"/>
       <c r="T68" s="43" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="46" t="inlineStr">
+      <c r="A69" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B69" s="46" t="inlineStr">
+      <c r="B69" s="44" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C69" s="46" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D69" s="46" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E69" s="47" t="inlineStr">
-        <is>
-          <t>Black Bean Patty (→Wk. 4 Sunday Lunch)</t>
-        </is>
-      </c>
-      <c r="F69" s="46" t="inlineStr">
-        <is>
-          <t>20 pcs</t>
-        </is>
-      </c>
-      <c r="G69" s="46" t="inlineStr"/>
-      <c r="H69" s="46" t="inlineStr"/>
-      <c r="I69" s="46" t="inlineStr"/>
-      <c r="J69" s="47" t="inlineStr">
-        <is>
-          <t>??? / no recipe</t>
-        </is>
-      </c>
-      <c r="K69" s="46" t="inlineStr"/>
-      <c r="L69" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M69" s="46" t="inlineStr">
+      <c r="C69" s="44" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D69" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E69" s="45" t="inlineStr">
+        <is>
+          <t>Halal Chicken Burgers (Thu Lunch)</t>
+        </is>
+      </c>
+      <c r="F69" s="44" t="inlineStr">
+        <is>
+          <t>150 pcs</t>
+        </is>
+      </c>
+      <c r="G69" s="44" t="inlineStr">
+        <is>
+          <t>1 pc</t>
+        </is>
+      </c>
+      <c r="H69" s="44" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I69" s="44" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="J69" s="45" t="inlineStr">
+        <is>
+          <t>Oven — 30 min day-of</t>
+        </is>
+      </c>
+      <c r="K69" s="44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L69" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M69" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N69" s="44" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O69" s="44" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P69" s="44" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N69" s="46" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O69" s="46" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P69" s="46" t="inlineStr"/>
-      <c r="Q69" s="46" t="inlineStr"/>
-      <c r="R69" s="47" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
-        </is>
-      </c>
-      <c r="S69" s="48" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q69" s="44" t="inlineStr"/>
+      <c r="R69" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Lunch</t>
+        </is>
+      </c>
+      <c r="S69" s="42" t="n"/>
       <c r="T69" s="43" t="n"/>
     </row>
     <row r="70">
@@ -26716,7 +26730,7 @@
       </c>
       <c r="C70" s="44" t="inlineStr">
         <is>
-          <t>PRODUCTION</t>
+          <t>LUNCH</t>
         </is>
       </c>
       <c r="D70" s="44" t="inlineStr">
@@ -26726,32 +26740,30 @@
       </c>
       <c r="E70" s="45" t="inlineStr">
         <is>
-          <t>Vegan Chili (→ Wk4 Mon Lunch)</t>
+          <t>Quinoa Burgers (Thu Lunch — Veg)</t>
         </is>
       </c>
       <c r="F70" s="44" t="inlineStr">
         <is>
-          <t>130 lbs</t>
+          <t>30 pcs</t>
         </is>
       </c>
       <c r="G70" s="44" t="inlineStr"/>
-      <c r="H70" s="44" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
+      <c r="H70" s="44" t="inlineStr"/>
       <c r="I70" s="44" t="inlineStr">
         <is>
-          <t>4 hotels</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J70" s="45" t="inlineStr">
         <is>
-          <t>Stove top</t>
-        </is>
-      </c>
-      <c r="K70" s="44" t="n">
-        <v>240</v>
+          <t>Pan fry; send hot AM</t>
+        </is>
+      </c>
+      <c r="K70" s="44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="L70" s="41" t="inlineStr">
         <is>
@@ -26760,12 +26772,12 @@
       </c>
       <c r="M70" s="44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N70" s="44" t="inlineStr">
         <is>
-          <t>MONDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="O70" s="44" t="inlineStr">
@@ -26775,328 +26787,316 @@
       </c>
       <c r="P70" s="44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q70" s="44" t="inlineStr"/>
       <c r="R70" s="45" t="inlineStr">
         <is>
+          <t>Serves: Wk. 3 Thursday Lunch</t>
+        </is>
+      </c>
+      <c r="S70" s="42" t="n"/>
+      <c r="T70" s="43" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C71" s="46" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E71" s="47" t="inlineStr">
+        <is>
+          <t>Black Bean Patty (→Wk. 4 Sunday Lunch)</t>
+        </is>
+      </c>
+      <c r="F71" s="46" t="inlineStr">
+        <is>
+          <t>20 pcs</t>
+        </is>
+      </c>
+      <c r="G71" s="46" t="inlineStr"/>
+      <c r="H71" s="46" t="inlineStr"/>
+      <c r="I71" s="46" t="inlineStr"/>
+      <c r="J71" s="47" t="inlineStr">
+        <is>
+          <t>??? / no recipe</t>
+        </is>
+      </c>
+      <c r="K71" s="46" t="inlineStr"/>
+      <c r="L71" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M71" s="46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N71" s="46" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O71" s="46" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P71" s="46" t="inlineStr"/>
+      <c r="Q71" s="46" t="inlineStr"/>
+      <c r="R71" s="47" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S71" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T71" s="43" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B72" s="44" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C72" s="44" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D72" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E72" s="45" t="inlineStr">
+        <is>
+          <t>Vegan Chili (→ Wk4 Mon Lunch)</t>
+        </is>
+      </c>
+      <c r="F72" s="44" t="inlineStr">
+        <is>
+          <t>130 lbs</t>
+        </is>
+      </c>
+      <c r="G72" s="44" t="inlineStr"/>
+      <c r="H72" s="44" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I72" s="44" t="inlineStr">
+        <is>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="J72" s="45" t="inlineStr">
+        <is>
+          <t>Stove top</t>
+        </is>
+      </c>
+      <c r="K72" s="44" t="n">
+        <v>240</v>
+      </c>
+      <c r="L72" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M72" s="44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N72" s="44" t="inlineStr">
+        <is>
+          <t>MONDAY</t>
+        </is>
+      </c>
+      <c r="O72" s="44" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P72" s="44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q72" s="44" t="inlineStr"/>
+      <c r="R72" s="45" t="inlineStr">
+        <is>
           <t>Serves: Wk. 4 Monday Lunch</t>
         </is>
       </c>
-      <c r="S70" s="48" t="n">
+      <c r="S72" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="T70" s="43" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="44" t="inlineStr">
+      <c r="T72" s="43" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B71" s="44" t="inlineStr">
+      <c r="B73" s="44" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C71" s="44" t="inlineStr">
+      <c r="C73" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D71" s="44" t="inlineStr">
+      <c r="D73" s="44" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E71" s="45" t="inlineStr">
+      <c r="E73" s="45" t="inlineStr">
         <is>
           <t>Rice (Thu Dinner)</t>
         </is>
       </c>
-      <c r="F71" s="44" t="inlineStr">
+      <c r="F73" s="44" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="G71" s="44" t="inlineStr">
+      <c r="G73" s="44" t="inlineStr">
         <is>
           <t>8 oz</t>
         </is>
       </c>
-      <c r="H71" s="44" t="inlineStr">
+      <c r="H73" s="44" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I71" s="44" t="inlineStr">
+      <c r="I73" s="44" t="inlineStr">
         <is>
           <t>4 hotels</t>
         </is>
       </c>
-      <c r="J71" s="45" t="inlineStr"/>
-      <c r="K71" s="44" t="inlineStr">
+      <c r="J73" s="45" t="inlineStr"/>
+      <c r="K73" s="44" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L71" s="41" t="inlineStr">
+      <c r="L73" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M71" s="44" t="inlineStr">
+      <c r="M73" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N71" s="44" t="inlineStr">
+      <c r="N73" s="44" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="O71" s="44" t="inlineStr">
+      <c r="O73" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P71" s="44" t="inlineStr">
+      <c r="P73" s="44" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q71" s="44" t="inlineStr"/>
-      <c r="R71" s="45" t="inlineStr">
+      <c r="Q73" s="44" t="inlineStr"/>
+      <c r="R73" s="45" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Thursday Dinner</t>
-        </is>
-      </c>
-      <c r="S71" s="42" t="n"/>
-      <c r="T71" s="43" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B72" s="50" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C72" s="50" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D72" s="50" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E72" s="51" t="inlineStr">
-        <is>
-          <t>Reheat Pork Griot (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="F72" s="50" t="inlineStr">
-        <is>
-          <t>40 lbs</t>
-        </is>
-      </c>
-      <c r="G72" s="50" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="H72" s="50" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I72" s="50" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="J72" s="51" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="K72" s="50" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L72" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M72" s="50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N72" s="50" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O72" s="50" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P72" s="50" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q72" s="50" t="inlineStr"/>
-      <c r="R72" s="51" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Thursday Production</t>
-        </is>
-      </c>
-      <c r="S72" s="42" t="n"/>
-      <c r="T72" s="43" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B73" s="50" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="C73" s="50" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D73" s="50" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E73" s="51" t="inlineStr">
-        <is>
-          <t>Reheat Chicken Griot — Halal (Thu Dinner)</t>
-        </is>
-      </c>
-      <c r="F73" s="50" t="inlineStr">
-        <is>
-          <t>32 lbs</t>
-        </is>
-      </c>
-      <c r="G73" s="50" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="H73" s="50" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I73" s="50" t="inlineStr">
-        <is>
-          <t>1u</t>
-        </is>
-      </c>
-      <c r="J73" s="51" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="K73" s="50" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L73" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M73" s="50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N73" s="50" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O73" s="50" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P73" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="50" t="inlineStr"/>
-      <c r="R73" s="51" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Thursday Production</t>
         </is>
       </c>
       <c r="S73" s="42" t="n"/>
       <c r="T73" s="43" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="44" t="inlineStr">
+      <c r="A74" s="50" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B74" s="44" t="inlineStr">
+      <c r="B74" s="50" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C74" s="44" t="inlineStr">
+      <c r="C74" s="50" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D74" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E74" s="45" t="inlineStr">
-        <is>
-          <t>Citrus Tofu (Thu Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="F74" s="44" t="inlineStr">
-        <is>
-          <t>12 pcs</t>
-        </is>
-      </c>
-      <c r="G74" s="44" t="inlineStr"/>
-      <c r="H74" s="44" t="inlineStr"/>
-      <c r="I74" s="44" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="J74" s="45" t="inlineStr">
-        <is>
-          <t>Roast</t>
-        </is>
-      </c>
-      <c r="K74" s="44" t="inlineStr">
-        <is>
-          <t>30</t>
+      <c r="D74" s="50" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E74" s="51" t="inlineStr">
+        <is>
+          <t>Reheat Pork Griot (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="F74" s="50" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="G74" s="50" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="H74" s="50" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I74" s="50" t="inlineStr">
+        <is>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="J74" s="51" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="K74" s="50" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="L74" s="41" t="inlineStr">
@@ -27104,260 +27104,276 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M74" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N74" s="44" t="inlineStr">
+      <c r="M74" s="50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N74" s="50" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="O74" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P74" s="44" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q74" s="44" t="inlineStr"/>
-      <c r="R74" s="45" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
+      <c r="O74" s="50" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P74" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q74" s="50" t="inlineStr"/>
+      <c r="R74" s="51" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Thursday Production</t>
         </is>
       </c>
       <c r="S74" s="42" t="n"/>
       <c r="T74" s="43" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="44" t="inlineStr">
+      <c r="A75" s="50" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B75" s="44" t="inlineStr">
+      <c r="B75" s="50" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C75" s="44" t="inlineStr">
+      <c r="C75" s="50" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D75" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E75" s="45" t="inlineStr">
-        <is>
-          <t>Chakalaka (Thu Dinner side)</t>
-        </is>
-      </c>
-      <c r="F75" s="44" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G75" s="44" t="inlineStr"/>
-      <c r="H75" s="44" t="inlineStr"/>
-      <c r="I75" s="44" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="J75" s="45" t="inlineStr">
-        <is>
-          <t>Cook at LAN; send hot PM</t>
-        </is>
-      </c>
-      <c r="K75" s="44" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L75" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M75" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N75" s="44" t="inlineStr">
+      <c r="D75" s="50" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E75" s="51" t="inlineStr">
+        <is>
+          <t>Reheat Chicken Griot — Halal (Thu Dinner)</t>
+        </is>
+      </c>
+      <c r="F75" s="50" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="G75" s="50" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="H75" s="50" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I75" s="50" t="inlineStr">
+        <is>
+          <t>1u</t>
+        </is>
+      </c>
+      <c r="J75" s="51" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="K75" s="50" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L75" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M75" s="50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N75" s="50" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="O75" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P75" s="44" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q75" s="44" t="inlineStr"/>
-      <c r="R75" s="45" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Thursday Dinner</t>
+      <c r="O75" s="50" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P75" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="50" t="inlineStr"/>
+      <c r="R75" s="51" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Thursday Production</t>
         </is>
       </c>
       <c r="S75" s="42" t="n"/>
       <c r="T75" s="43" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="52" t="inlineStr">
+      <c r="A76" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B76" s="52" t="inlineStr">
+      <c r="B76" s="44" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C76" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D76" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E76" s="53" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F76" s="52" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G76" s="52" t="inlineStr"/>
-      <c r="H76" s="52" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I76" s="52" t="inlineStr"/>
-      <c r="J76" s="53" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K76" s="52" t="inlineStr"/>
+      <c r="C76" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D76" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E76" s="45" t="inlineStr">
+        <is>
+          <t>Citrus Tofu (Thu Dinner — Veg)</t>
+        </is>
+      </c>
+      <c r="F76" s="44" t="inlineStr">
+        <is>
+          <t>12 pcs</t>
+        </is>
+      </c>
+      <c r="G76" s="44" t="inlineStr"/>
+      <c r="H76" s="44" t="inlineStr"/>
+      <c r="I76" s="44" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="J76" s="45" t="inlineStr">
+        <is>
+          <t>Roast</t>
+        </is>
+      </c>
+      <c r="K76" s="44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="L76" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M76" s="52" t="inlineStr"/>
-      <c r="N76" s="52" t="inlineStr"/>
-      <c r="O76" s="52" t="inlineStr"/>
-      <c r="P76" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R76" s="53" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
+      <c r="M76" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N76" s="44" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O76" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P76" s="44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q76" s="44" t="inlineStr"/>
+      <c r="R76" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
         </is>
       </c>
       <c r="S76" s="42" t="n"/>
       <c r="T76" s="43" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="52" t="inlineStr">
+      <c r="A77" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B77" s="52" t="inlineStr">
+      <c r="B77" s="44" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C77" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D77" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E77" s="53" t="inlineStr">
-        <is>
-          <t>HOT Pork/Chicken Griot + Citrus Tofu → Dinner</t>
-        </is>
-      </c>
-      <c r="F77" s="52" t="inlineStr">
+      <c r="C77" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D77" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E77" s="45" t="inlineStr">
+        <is>
+          <t>Chakalaka (Thu Dinner side)</t>
+        </is>
+      </c>
+      <c r="F77" s="44" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G77" s="52" t="inlineStr">
-        <is>
-          <t>12 oz</t>
-        </is>
-      </c>
-      <c r="H77" s="52" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I77" s="52" t="inlineStr">
-        <is>
-          <t>2.5 hotels</t>
-        </is>
-      </c>
-      <c r="J77" s="53" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K77" s="52" t="n"/>
-      <c r="L77" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M77" s="52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N77" s="52" t="inlineStr"/>
-      <c r="O77" s="52" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P77" s="52" t="n">
+      <c r="G77" s="44" t="inlineStr"/>
+      <c r="H77" s="44" t="inlineStr"/>
+      <c r="I77" s="44" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J77" s="45" t="inlineStr">
+        <is>
+          <t>Cook at LAN; send hot PM</t>
+        </is>
+      </c>
+      <c r="K77" s="44" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L77" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M77" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N77" s="44" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O77" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P77" s="44" t="n">
         <v>3</v>
       </c>
-      <c r="Q77" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R77" s="53" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Tue–Thu Production</t>
+      <c r="Q77" s="44" t="inlineStr"/>
+      <c r="R77" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Thursday Dinner</t>
         </is>
       </c>
       <c r="S77" s="42" t="n"/>
@@ -27386,32 +27402,24 @@
       </c>
       <c r="E78" s="53" t="inlineStr">
         <is>
-          <t>HOT Rice → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F78" s="52" t="inlineStr">
         <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
-      <c r="G78" s="52" t="inlineStr">
-        <is>
-          <t>8 oz</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="G78" s="52" t="inlineStr"/>
       <c r="H78" s="52" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I78" s="52" t="inlineStr">
-        <is>
-          <t>4 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I78" s="52" t="inlineStr"/>
       <c r="J78" s="53" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K78" s="52" t="inlineStr"/>
@@ -27420,21 +27428,11 @@
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M78" s="52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="M78" s="52" t="inlineStr"/>
       <c r="N78" s="52" t="inlineStr"/>
-      <c r="O78" s="52" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P78" s="52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="O78" s="52" t="inlineStr"/>
+      <c r="P78" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="Q78" s="52" t="inlineStr">
         <is>
@@ -27443,7 +27441,7 @@
       </c>
       <c r="R78" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk. 2 Tue–Thu Production</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
       <c r="S78" s="42" t="n"/>
@@ -27472,7 +27470,7 @@
       </c>
       <c r="E79" s="53" t="inlineStr">
         <is>
-          <t>HOT Chakalaka → Dinner side</t>
+          <t>HOT Pork/Chicken Griot + Citrus Tofu → Dinner</t>
         </is>
       </c>
       <c r="F79" s="52" t="inlineStr">
@@ -27480,41 +27478,41 @@
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G79" s="52" t="inlineStr"/>
+      <c r="G79" s="52" t="inlineStr">
+        <is>
+          <t>12 oz</t>
+        </is>
+      </c>
       <c r="H79" s="52" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>vac</t>
         </is>
       </c>
       <c r="I79" s="52" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>2.5 hotels</t>
         </is>
       </c>
       <c r="J79" s="53" t="inlineStr">
         <is>
-          <t>LAN → Rex</t>
-        </is>
-      </c>
-      <c r="K79" s="52" t="inlineStr"/>
-      <c r="L79" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K79" s="52" t="n"/>
+      <c r="L79" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M79" s="52" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N79" s="52" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N79" s="52" t="inlineStr"/>
       <c r="O79" s="52" t="inlineStr">
         <is>
-          <t>DINNER</t>
+          <t>PRODUCTION</t>
         </is>
       </c>
       <c r="P79" s="52" t="n">
@@ -27527,7 +27525,7 @@
       </c>
       <c r="R79" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Thursday Dinner (LAN same day)</t>
+          <t>Produced: Wk. 2 Tue–Thu Production</t>
         </is>
       </c>
       <c r="S79" s="42" t="n"/>
@@ -27556,51 +27554,55 @@
       </c>
       <c r="E80" s="53" t="inlineStr">
         <is>
-          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
+          <t>HOT Rice → Dinner</t>
         </is>
       </c>
       <c r="F80" s="52" t="inlineStr">
         <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="G80" s="52" t="inlineStr"/>
+          <t>4 hotels</t>
+        </is>
+      </c>
+      <c r="G80" s="52" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
       <c r="H80" s="52" t="inlineStr">
         <is>
-          <t>bus bin</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="I80" s="52" t="inlineStr">
         <is>
-          <t>2 bins</t>
+          <t>4 hotels</t>
         </is>
       </c>
       <c r="J80" s="53" t="inlineStr">
         <is>
-          <t>LAN → Rex fridge</t>
+          <t>Bloor → Rex</t>
         </is>
       </c>
       <c r="K80" s="52" t="inlineStr"/>
-      <c r="L80" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
+      <c r="L80" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M80" s="52" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N80" s="52" t="inlineStr">
-        <is>
-          <t>THURSDAY</t>
-        </is>
-      </c>
-      <c r="O80" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P80" s="52" t="n">
-        <v>2</v>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N80" s="52" t="inlineStr"/>
+      <c r="O80" s="52" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P80" s="52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="Q80" s="52" t="inlineStr">
         <is>
@@ -27609,157 +27611,175 @@
       </c>
       <c r="R80" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
+          <t>Produced: Wk. 2 Tue–Thu Production</t>
         </is>
       </c>
       <c r="S80" s="42" t="n"/>
       <c r="T80" s="43" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="42" t="inlineStr">
+      <c r="A81" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B81" s="42" t="inlineStr">
+      <c r="B81" s="52" t="inlineStr">
         <is>
           <t>THURSDAY</t>
         </is>
       </c>
-      <c r="C81" s="42" t="inlineStr">
+      <c r="C81" s="52" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="D81" s="42" t="inlineStr">
+      <c r="D81" s="52" t="inlineStr">
         <is>
           <t>SEND PM</t>
         </is>
       </c>
-      <c r="E81" s="43" t="inlineStr">
-        <is>
-          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="F81" s="42" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="G81" s="42" t="n"/>
-      <c r="H81" s="42" t="n"/>
-      <c r="I81" s="42" t="inlineStr">
-        <is>
-          <t>2 bins</t>
-        </is>
-      </c>
-      <c r="J81" s="43" t="inlineStr">
+      <c r="E81" s="53" t="inlineStr">
+        <is>
+          <t>HOT Chakalaka → Dinner side</t>
+        </is>
+      </c>
+      <c r="F81" s="52" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G81" s="52" t="inlineStr"/>
+      <c r="H81" s="52" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I81" s="52" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J81" s="53" t="inlineStr">
         <is>
           <t>LAN → Rex</t>
         </is>
       </c>
-      <c r="K81" s="42" t="n"/>
-      <c r="L81" s="42" t="inlineStr">
+      <c r="K81" s="52" t="inlineStr"/>
+      <c r="L81" s="54" t="inlineStr">
         <is>
           <t>LAN</t>
         </is>
       </c>
-      <c r="M81" s="42" t="inlineStr">
+      <c r="M81" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N81" s="42" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O81" s="42" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P81" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q81" s="42" t="inlineStr">
+      <c r="N81" s="52" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O81" s="52" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P81" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="52" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="R81" s="43" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
+      <c r="R81" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Thursday Dinner (LAN same day)</t>
         </is>
       </c>
       <c r="S81" s="42" t="n"/>
       <c r="T81" s="43" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="42" t="inlineStr">
+      <c r="A82" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B82" s="42" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C82" s="42" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D82" s="42" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="E82" s="43" t="inlineStr">
-        <is>
-          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
-        </is>
-      </c>
-      <c r="F82" s="42" t="n"/>
-      <c r="G82" s="42" t="n"/>
-      <c r="H82" s="42" t="n"/>
-      <c r="I82" s="42" t="n"/>
-      <c r="J82" s="43" t="inlineStr">
-        <is>
-          <t>Cold salad already at Rex</t>
-        </is>
-      </c>
-      <c r="K82" s="42" t="n"/>
-      <c r="L82" s="42" t="inlineStr">
-        <is>
-          <t>Rex</t>
-        </is>
-      </c>
-      <c r="M82" s="42" t="inlineStr">
+      <c r="B82" s="52" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="C82" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D82" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E82" s="53" t="inlineStr">
+        <is>
+          <t>Cold Egg Salad Mix → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="F82" s="52" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="G82" s="52" t="inlineStr"/>
+      <c r="H82" s="52" t="inlineStr">
+        <is>
+          <t>bus bin</t>
+        </is>
+      </c>
+      <c r="I82" s="52" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
+      <c r="J82" s="53" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="K82" s="52" t="inlineStr"/>
+      <c r="L82" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M82" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N82" s="42" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O82" s="42" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P82" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="42" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R82" s="43" t="n"/>
+      <c r="N82" s="52" t="inlineStr">
+        <is>
+          <t>THURSDAY</t>
+        </is>
+      </c>
+      <c r="O82" s="52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P82" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R82" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
+        </is>
+      </c>
       <c r="S82" s="42" t="n"/>
       <c r="T82" s="43" t="n"/>
     </row>
@@ -27771,37 +27791,45 @@
       </c>
       <c r="B83" s="42" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>THURSDAY</t>
         </is>
       </c>
       <c r="C83" s="42" t="inlineStr">
         <is>
-          <t>LUNCH</t>
+          <t>SEND PM</t>
         </is>
       </c>
       <c r="D83" s="42" t="inlineStr">
         <is>
-          <t>NOTE</t>
+          <t>SEND PM</t>
         </is>
       </c>
       <c r="E83" s="43" t="inlineStr">
         <is>
-          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
-        </is>
-      </c>
-      <c r="F83" s="42" t="n"/>
+          <t>Cold Bean Salad → Rex fridge (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="F83" s="42" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
       <c r="G83" s="42" t="n"/>
       <c r="H83" s="42" t="n"/>
-      <c r="I83" s="42" t="n"/>
+      <c r="I83" s="42" t="inlineStr">
+        <is>
+          <t>2 bins</t>
+        </is>
+      </c>
       <c r="J83" s="43" t="inlineStr">
         <is>
-          <t>Cold salad pre-sent; no AM run needed</t>
+          <t>LAN → Rex</t>
         </is>
       </c>
       <c r="K83" s="42" t="n"/>
       <c r="L83" s="42" t="inlineStr">
         <is>
-          <t>Rex</t>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M83" s="42" t="inlineStr">
@@ -27819,172 +27847,150 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P83" s="42" t="n"/>
-      <c r="Q83" s="42" t="n"/>
-      <c r="R83" s="43" t="n"/>
+      <c r="P83" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q83" s="42" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R83" s="43" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Wednesday Production (LAN)</t>
+        </is>
+      </c>
       <c r="S83" s="42" t="n"/>
       <c r="T83" s="43" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="44" t="inlineStr">
+      <c r="A84" s="42" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B84" s="44" t="inlineStr">
+      <c r="B84" s="42" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C84" s="44" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D84" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E84" s="45" t="inlineStr">
-        <is>
-          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
-        </is>
-      </c>
-      <c r="F84" s="44" t="inlineStr">
-        <is>
-          <t>100 lbs</t>
-        </is>
-      </c>
-      <c r="G84" s="44" t="inlineStr"/>
-      <c r="H84" s="44" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I84" s="44" t="inlineStr"/>
-      <c r="J84" s="45" t="inlineStr"/>
-      <c r="K84" s="44" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="L84" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M84" s="44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N84" s="44" t="inlineStr">
-        <is>
-          <t>SUNDAY</t>
-        </is>
-      </c>
-      <c r="O84" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P84" s="44" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-      <c r="Q84" s="44" t="inlineStr"/>
-      <c r="R84" s="45" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Sunday Dinner</t>
-        </is>
-      </c>
-      <c r="S84" s="49" t="n">
-        <v>2</v>
-      </c>
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D84" s="42" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E84" s="43" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad at Rex — sent Thu PM</t>
+        </is>
+      </c>
+      <c r="F84" s="42" t="n"/>
+      <c r="G84" s="42" t="n"/>
+      <c r="H84" s="42" t="n"/>
+      <c r="I84" s="42" t="n"/>
+      <c r="J84" s="43" t="inlineStr">
+        <is>
+          <t>Cold salad already at Rex</t>
+        </is>
+      </c>
+      <c r="K84" s="42" t="n"/>
+      <c r="L84" s="42" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="M84" s="42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N84" s="42" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O84" s="42" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P84" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="42" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R84" s="43" t="n"/>
+      <c r="S84" s="42" t="n"/>
       <c r="T84" s="43" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="44" t="inlineStr">
+      <c r="A85" s="42" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B85" s="44" t="inlineStr">
+      <c r="B85" s="42" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C85" s="44" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D85" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E85" s="45" t="inlineStr">
-        <is>
-          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
-        </is>
-      </c>
-      <c r="F85" s="44" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G85" s="44" t="inlineStr"/>
-      <c r="H85" s="44" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I85" s="44" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="J85" s="45" t="inlineStr"/>
-      <c r="K85" s="44" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="L85" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M85" s="44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N85" s="44" t="inlineStr">
-        <is>
-          <t>WEDNESDAY</t>
-        </is>
-      </c>
-      <c r="O85" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P85" s="44" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q85" s="44" t="inlineStr"/>
-      <c r="R85" s="45" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Wednesday Dinner</t>
-        </is>
-      </c>
-      <c r="S85" s="48" t="n">
-        <v>5</v>
-      </c>
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D85" s="42" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E85" s="43" t="inlineStr">
+        <is>
+          <t>Egg Salad Wrap + Bean Salad (Fri Lunch)</t>
+        </is>
+      </c>
+      <c r="F85" s="42" t="n"/>
+      <c r="G85" s="42" t="n"/>
+      <c r="H85" s="42" t="n"/>
+      <c r="I85" s="42" t="n"/>
+      <c r="J85" s="43" t="inlineStr">
+        <is>
+          <t>Cold salad pre-sent; no AM run needed</t>
+        </is>
+      </c>
+      <c r="K85" s="42" t="n"/>
+      <c r="L85" s="42" t="inlineStr">
+        <is>
+          <t>Rex</t>
+        </is>
+      </c>
+      <c r="M85" s="42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N85" s="42" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O85" s="42" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P85" s="42" t="n"/>
+      <c r="Q85" s="42" t="n"/>
+      <c r="R85" s="43" t="n"/>
+      <c r="S85" s="42" t="n"/>
       <c r="T85" s="43" t="n"/>
     </row>
     <row r="86">
@@ -28000,73 +28006,71 @@
       </c>
       <c r="C86" s="44" t="inlineStr">
         <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D86" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E86" s="45" t="inlineStr">
+        <is>
+          <t>White Chilli Chicken Pasta (→ Wk4 Sun Dinner)</t>
+        </is>
+      </c>
+      <c r="F86" s="44" t="inlineStr">
+        <is>
+          <t>100 lbs</t>
+        </is>
+      </c>
+      <c r="G86" s="44" t="inlineStr"/>
+      <c r="H86" s="44" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I86" s="44" t="inlineStr"/>
+      <c r="J86" s="45" t="inlineStr"/>
+      <c r="K86" s="44" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L86" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M86" s="44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N86" s="44" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O86" s="44" t="inlineStr">
+        <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D86" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E86" s="45" t="inlineStr">
-        <is>
-          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
-        </is>
-      </c>
-      <c r="F86" s="44" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="G86" s="44" t="inlineStr"/>
-      <c r="H86" s="44" t="inlineStr"/>
-      <c r="I86" s="44" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="J86" s="45" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="K86" s="44" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="L86" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M86" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N86" s="44" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O86" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
       <c r="P86" s="44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>???</t>
         </is>
       </c>
       <c r="Q86" s="44" t="inlineStr"/>
       <c r="R86" s="45" t="inlineStr">
         <is>
-          <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-      <c r="S86" s="42" t="n"/>
+          <t>Serves: Wk. 4 Sunday Dinner</t>
+        </is>
+      </c>
+      <c r="S86" s="49" t="n">
+        <v>2</v>
+      </c>
       <c r="T86" s="43" t="n"/>
     </row>
     <row r="87">
@@ -28082,156 +28086,152 @@
       </c>
       <c r="C87" s="44" t="inlineStr">
         <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D87" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E87" s="45" t="inlineStr">
+        <is>
+          <t>Eggplant/Cassava Stew (→ Wk4 Wed Dinner)</t>
+        </is>
+      </c>
+      <c r="F87" s="44" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G87" s="44" t="inlineStr"/>
+      <c r="H87" s="44" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I87" s="44" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="J87" s="45" t="inlineStr"/>
+      <c r="K87" s="44" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L87" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M87" s="44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N87" s="44" t="inlineStr">
+        <is>
+          <t>WEDNESDAY</t>
+        </is>
+      </c>
+      <c r="O87" s="44" t="inlineStr">
+        <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D87" s="44" t="inlineStr">
-        <is>
-          <t>COOK</t>
-        </is>
-      </c>
-      <c r="E87" s="45" t="inlineStr">
-        <is>
-          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
-        </is>
-      </c>
-      <c r="F87" s="44" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="G87" s="44" t="inlineStr"/>
-      <c r="H87" s="44" t="inlineStr"/>
-      <c r="I87" s="44" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J87" s="45" t="inlineStr">
-        <is>
-          <t>Wok/oven</t>
-        </is>
-      </c>
-      <c r="K87" s="44" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L87" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M87" s="44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N87" s="44" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O87" s="44" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P87" s="44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="P87" s="44" t="n">
+        <v>2</v>
       </c>
       <c r="Q87" s="44" t="inlineStr"/>
       <c r="R87" s="45" t="inlineStr">
         <is>
+          <t>Serves: Wk. 4 Wednesday Dinner</t>
+        </is>
+      </c>
+      <c r="S87" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" s="43" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C88" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D88" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E88" s="45" t="inlineStr">
+        <is>
+          <t>Chicken &amp; Mushroom Fried Rice (Fri Dinner)</t>
+        </is>
+      </c>
+      <c r="F88" s="44" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="G88" s="44" t="inlineStr"/>
+      <c r="H88" s="44" t="inlineStr"/>
+      <c r="I88" s="44" t="inlineStr">
+        <is>
+          <t>5 hotels</t>
+        </is>
+      </c>
+      <c r="J88" s="45" t="inlineStr">
+        <is>
+          <t>Wok/oven</t>
+        </is>
+      </c>
+      <c r="K88" s="44" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L88" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M88" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N88" s="44" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O88" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P88" s="44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q88" s="44" t="inlineStr"/>
+      <c r="R88" s="45" t="inlineStr">
+        <is>
           <t>Serves: Wk. 3 Friday Dinner</t>
-        </is>
-      </c>
-      <c r="S87" s="42" t="n"/>
-      <c r="T87" s="43" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B88" s="50" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="C88" s="50" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="D88" s="50" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E88" s="51" t="inlineStr">
-        <is>
-          <t>Heat Spring Rolls (Fri Dinner side)</t>
-        </is>
-      </c>
-      <c r="F88" s="50" t="inlineStr">
-        <is>
-          <t>200 pcs</t>
-        </is>
-      </c>
-      <c r="G88" s="50" t="inlineStr"/>
-      <c r="H88" s="50" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I88" s="50" t="inlineStr">
-        <is>
-          <t>2 hotels</t>
-        </is>
-      </c>
-      <c r="J88" s="51" t="inlineStr">
-        <is>
-          <t>Purchased frozen; heat day-of at Bloor</t>
-        </is>
-      </c>
-      <c r="K88" s="50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="L88" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M88" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N88" s="50" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O88" s="50" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P88" s="50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q88" s="50" t="inlineStr"/>
-      <c r="R88" s="51" t="inlineStr">
-        <is>
-          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
       <c r="S88" s="42" t="n"/>
@@ -28260,33 +28260,29 @@
       </c>
       <c r="E89" s="45" t="inlineStr">
         <is>
-          <t>Bok Choy (Fri Dinner side)</t>
+          <t>Vegan/No-Soy Mushroom Fried Rice (Fri Dinner — Veg)</t>
         </is>
       </c>
       <c r="F89" s="44" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="G89" s="44" t="inlineStr"/>
-      <c r="H89" s="44" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
+      <c r="H89" s="44" t="inlineStr"/>
       <c r="I89" s="44" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>1 hotel</t>
         </is>
       </c>
       <c r="J89" s="45" t="inlineStr">
         <is>
-          <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
+          <t>Wok/oven</t>
         </is>
       </c>
       <c r="K89" s="44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L89" s="41" t="inlineStr">
@@ -28309,8 +28305,10 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P89" s="44" t="n">
-        <v>3</v>
+      <c r="P89" s="44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="Q89" s="44" t="inlineStr"/>
       <c r="R89" s="45" t="inlineStr">
@@ -28322,168 +28320,170 @@
       <c r="T89" s="43" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="52" t="inlineStr">
+      <c r="A90" s="50" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B90" s="52" t="inlineStr">
+      <c r="B90" s="50" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C90" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D90" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E90" s="53" t="inlineStr">
-        <is>
-          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
-        </is>
-      </c>
-      <c r="F90" s="52" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="G90" s="52" t="inlineStr"/>
-      <c r="H90" s="52" t="inlineStr">
+      <c r="C90" s="50" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D90" s="50" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E90" s="51" t="inlineStr">
+        <is>
+          <t>Heat Spring Rolls (Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="F90" s="50" t="inlineStr">
+        <is>
+          <t>200 pcs</t>
+        </is>
+      </c>
+      <c r="G90" s="50" t="inlineStr"/>
+      <c r="H90" s="50" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="I90" s="52" t="inlineStr">
-        <is>
-          <t>5 hotels</t>
-        </is>
-      </c>
-      <c r="J90" s="53" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K90" s="52" t="inlineStr"/>
+      <c r="I90" s="50" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J90" s="51" t="inlineStr">
+        <is>
+          <t>Purchased frozen; heat day-of at Bloor</t>
+        </is>
+      </c>
+      <c r="K90" s="50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="L90" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M90" s="52" t="inlineStr">
+      <c r="M90" s="50" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N90" s="52" t="inlineStr">
+      <c r="N90" s="50" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O90" s="52" t="inlineStr">
+      <c r="O90" s="50" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P90" s="52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Q90" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R90" s="53" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
+      <c r="P90" s="50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q90" s="50" t="inlineStr"/>
+      <c r="R90" s="51" t="inlineStr">
+        <is>
+          <t>Serves: same day (purchased frozen)</t>
         </is>
       </c>
       <c r="S90" s="42" t="n"/>
       <c r="T90" s="43" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="52" t="inlineStr">
+      <c r="A91" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B91" s="52" t="inlineStr">
+      <c r="B91" s="44" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="C91" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D91" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E91" s="53" t="inlineStr">
-        <is>
-          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
-        </is>
-      </c>
-      <c r="F91" s="52" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="G91" s="52" t="inlineStr"/>
-      <c r="H91" s="52" t="inlineStr"/>
-      <c r="I91" s="52" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J91" s="53" t="inlineStr">
-        <is>
-          <t>Bloor → Rex</t>
-        </is>
-      </c>
-      <c r="K91" s="52" t="inlineStr"/>
+      <c r="C91" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D91" s="44" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="E91" s="45" t="inlineStr">
+        <is>
+          <t>Bok Choy (Fri Dinner side)</t>
+        </is>
+      </c>
+      <c r="F91" s="44" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="G91" s="44" t="inlineStr"/>
+      <c r="H91" s="44" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I91" s="44" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="J91" s="45" t="inlineStr">
+        <is>
+          <t>⚠ NO RECIPE / amount unconfirmed — cook day-of at Bloor</t>
+        </is>
+      </c>
+      <c r="K91" s="44" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="L91" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M91" s="52" t="inlineStr">
+      <c r="M91" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N91" s="52" t="inlineStr">
+      <c r="N91" s="44" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O91" s="52" t="inlineStr">
+      <c r="O91" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P91" s="52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q91" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R91" s="53" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
+      <c r="P91" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="44" t="inlineStr"/>
+      <c r="R91" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Friday Dinner</t>
         </is>
       </c>
       <c r="S91" s="42" t="n"/>
@@ -28512,19 +28512,23 @@
       </c>
       <c r="E92" s="53" t="inlineStr">
         <is>
-          <t>HOT Spring Rolls → Dinner side</t>
+          <t>HOT Chicken &amp; Mushroom Fried Rice → Dinner</t>
         </is>
       </c>
       <c r="F92" s="52" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="G92" s="52" t="inlineStr"/>
-      <c r="H92" s="52" t="inlineStr"/>
+      <c r="H92" s="52" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="I92" s="52" t="inlineStr">
         <is>
-          <t>2 hotels</t>
+          <t>5 hotels</t>
         </is>
       </c>
       <c r="J92" s="53" t="inlineStr">
@@ -28555,7 +28559,7 @@
       </c>
       <c r="P92" s="52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q92" s="52" t="inlineStr">
@@ -28572,431 +28576,425 @@
       <c r="T92" s="43" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="39" t="inlineStr">
+      <c r="A93" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B93" s="39" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C93" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D93" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E93" s="40" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Beef → Lunch</t>
-        </is>
-      </c>
-      <c r="F93" s="39" t="inlineStr">
-        <is>
-          <t>80 lbs</t>
-        </is>
-      </c>
-      <c r="G93" s="39" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
-      <c r="H93" s="39" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I93" s="39" t="inlineStr">
-        <is>
-          <t>2u</t>
-        </is>
-      </c>
-      <c r="J93" s="40" t="inlineStr">
+      <c r="B93" s="52" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C93" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D93" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E93" s="53" t="inlineStr">
+        <is>
+          <t>HOT Vegan/No-Soy Mushroom Fried Rice → Dinner (Veg)</t>
+        </is>
+      </c>
+      <c r="F93" s="52" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="G93" s="52" t="inlineStr"/>
+      <c r="H93" s="52" t="inlineStr"/>
+      <c r="I93" s="52" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J93" s="53" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K93" s="39" t="inlineStr"/>
+      <c r="K93" s="52" t="inlineStr"/>
       <c r="L93" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M93" s="39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N93" s="39" t="inlineStr">
+      <c r="M93" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N93" s="52" t="inlineStr">
         <is>
           <t>FRIDAY</t>
         </is>
       </c>
-      <c r="O93" s="39" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P93" s="58" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q93" s="39" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R93" s="40" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Production</t>
+      <c r="O93" s="52" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P93" s="52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q93" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R93" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
         </is>
       </c>
       <c r="S93" s="42" t="n"/>
       <c r="T93" s="43" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="39" t="inlineStr">
+      <c r="A94" s="52" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B94" s="39" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C94" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="D94" s="39" t="inlineStr">
-        <is>
-          <t>SEND AM</t>
-        </is>
-      </c>
-      <c r="E94" s="40" t="inlineStr">
-        <is>
-          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
-        </is>
-      </c>
-      <c r="F94" s="39" t="inlineStr">
-        <is>
-          <t>12 lbs</t>
-        </is>
-      </c>
-      <c r="G94" s="39" t="inlineStr">
-        <is>
-          <t>4 oz</t>
-        </is>
-      </c>
-      <c r="H94" s="39" t="inlineStr">
-        <is>
-          <t>vac</t>
-        </is>
-      </c>
-      <c r="I94" s="39" t="inlineStr">
-        <is>
-          <t>0.5u</t>
-        </is>
-      </c>
-      <c r="J94" s="40" t="inlineStr">
+      <c r="B94" s="52" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="C94" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D94" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E94" s="53" t="inlineStr">
+        <is>
+          <t>HOT Spring Rolls → Dinner side</t>
+        </is>
+      </c>
+      <c r="F94" s="52" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="G94" s="52" t="inlineStr"/>
+      <c r="H94" s="52" t="inlineStr"/>
+      <c r="I94" s="52" t="inlineStr">
+        <is>
+          <t>2 hotels</t>
+        </is>
+      </c>
+      <c r="J94" s="53" t="inlineStr">
         <is>
           <t>Bloor → Rex</t>
         </is>
       </c>
-      <c r="K94" s="39" t="inlineStr"/>
+      <c r="K94" s="52" t="inlineStr"/>
       <c r="L94" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M94" s="39" t="inlineStr">
+      <c r="M94" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N94" s="52" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O94" s="52" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P94" s="52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N94" s="39" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O94" s="39" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P94" s="58" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q94" s="39" t="inlineStr">
-        <is>
-          <t>AM</t>
-        </is>
-      </c>
-      <c r="R94" s="40" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 2 Friday Production</t>
+      <c r="Q94" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R94" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Friday Dinner (same day)</t>
         </is>
       </c>
       <c r="S94" s="42" t="n"/>
       <c r="T94" s="43" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="50" t="inlineStr">
+      <c r="A95" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B95" s="50" t="inlineStr">
+      <c r="B95" s="39" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C95" s="50" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="D95" s="50" t="inlineStr">
-        <is>
-          <t>HEAT</t>
-        </is>
-      </c>
-      <c r="E95" s="51" t="inlineStr">
-        <is>
-          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
-        </is>
-      </c>
-      <c r="F95" s="50" t="inlineStr">
-        <is>
-          <t>92 lbs (80+12)</t>
-        </is>
-      </c>
-      <c r="G95" s="50" t="inlineStr">
+      <c r="C95" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D95" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Beef → Lunch</t>
+        </is>
+      </c>
+      <c r="F95" s="39" t="inlineStr">
+        <is>
+          <t>80 lbs</t>
+        </is>
+      </c>
+      <c r="G95" s="39" t="inlineStr">
         <is>
           <t>6 oz</t>
         </is>
       </c>
-      <c r="H95" s="50" t="inlineStr">
+      <c r="H95" s="39" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I95" s="50" t="inlineStr"/>
-      <c r="J95" s="51" t="inlineStr">
-        <is>
-          <t>Reheat bagged</t>
-        </is>
-      </c>
-      <c r="K95" s="50" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I95" s="39" t="inlineStr">
+        <is>
+          <t>2u</t>
+        </is>
+      </c>
+      <c r="J95" s="40" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K95" s="39" t="inlineStr"/>
       <c r="L95" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M95" s="50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N95" s="50" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O95" s="50" t="inlineStr">
-        <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P95" s="50" t="inlineStr"/>
-      <c r="Q95" s="50" t="inlineStr"/>
-      <c r="R95" s="51" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Sunday Production</t>
+      <c r="M95" s="39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N95" s="39" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O95" s="39" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P95" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q95" s="39" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R95" s="40" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Friday Production</t>
         </is>
       </c>
       <c r="S95" s="42" t="n"/>
       <c r="T95" s="43" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="46" t="inlineStr">
+      <c r="A96" s="39" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B96" s="46" t="inlineStr">
+      <c r="B96" s="39" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C96" s="46" t="inlineStr">
+      <c r="C96" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="D96" s="39" t="inlineStr">
+        <is>
+          <t>SEND AM</t>
+        </is>
+      </c>
+      <c r="E96" s="40" t="inlineStr">
+        <is>
+          <t>HOT CONC Salad Vegan → Lunch (Veg)</t>
+        </is>
+      </c>
+      <c r="F96" s="39" t="inlineStr">
+        <is>
+          <t>12 lbs</t>
+        </is>
+      </c>
+      <c r="G96" s="39" t="inlineStr">
+        <is>
+          <t>4 oz</t>
+        </is>
+      </c>
+      <c r="H96" s="39" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I96" s="39" t="inlineStr">
+        <is>
+          <t>0.5u</t>
+        </is>
+      </c>
+      <c r="J96" s="40" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K96" s="39" t="inlineStr"/>
+      <c r="L96" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M96" s="39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N96" s="39" t="inlineStr">
+        <is>
+          <t>FRIDAY</t>
+        </is>
+      </c>
+      <c r="O96" s="39" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D96" s="46" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E96" s="47" t="inlineStr">
-        <is>
-          <t>Cut/Season Tandoori Pork</t>
-        </is>
-      </c>
-      <c r="F96" s="46" t="inlineStr">
-        <is>
-          <t>1 cs</t>
-        </is>
-      </c>
-      <c r="G96" s="46" t="inlineStr"/>
-      <c r="H96" s="46" t="inlineStr">
-        <is>
-          <t>hotels</t>
-        </is>
-      </c>
-      <c r="I96" s="46" t="inlineStr">
-        <is>
-          <t>1.5u</t>
-        </is>
-      </c>
-      <c r="J96" s="47" t="inlineStr">
-        <is>
-          <t>Season w/Vindaloo Dry Spice Mix</t>
-        </is>
-      </c>
-      <c r="K96" s="46" t="inlineStr">
+      <c r="P96" s="58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q96" s="39" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="R96" s="40" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 2 Friday Production</t>
+        </is>
+      </c>
+      <c r="S96" s="42" t="n"/>
+      <c r="T96" s="43" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B97" s="50" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C97" s="50" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="D97" s="50" t="inlineStr">
+        <is>
+          <t>HEAT</t>
+        </is>
+      </c>
+      <c r="E97" s="51" t="inlineStr">
+        <is>
+          <t>Reheat CONC Salad Beef + Vegan (Sat Lunch)</t>
+        </is>
+      </c>
+      <c r="F97" s="50" t="inlineStr">
+        <is>
+          <t>92 lbs (80+12)</t>
+        </is>
+      </c>
+      <c r="G97" s="50" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="H97" s="50" t="inlineStr">
+        <is>
+          <t>vac</t>
+        </is>
+      </c>
+      <c r="I97" s="50" t="inlineStr"/>
+      <c r="J97" s="51" t="inlineStr">
+        <is>
+          <t>Reheat bagged</t>
+        </is>
+      </c>
+      <c r="K97" s="50" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L96" s="41" t="inlineStr">
+      <c r="L97" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M96" s="46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N96" s="46" t="inlineStr">
-        <is>
-          <t>FRIDAY</t>
-        </is>
-      </c>
-      <c r="O96" s="46" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P96" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q96" s="46" t="inlineStr"/>
-      <c r="R96" s="47" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 4 Friday Dinner</t>
-        </is>
-      </c>
-      <c r="S96" s="48" t="n">
-        <v>6</v>
-      </c>
-      <c r="T96" s="43" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="46" t="inlineStr">
+      <c r="M97" s="50" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B97" s="46" t="inlineStr">
+      <c r="N97" s="50" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C97" s="46" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="D97" s="46" t="inlineStr">
-        <is>
-          <t>PREP</t>
-        </is>
-      </c>
-      <c r="E97" s="47" t="inlineStr">
-        <is>
-          <t>Tandoori Marinade</t>
-        </is>
-      </c>
-      <c r="F97" s="46" t="inlineStr">
-        <is>
-          <t>recipe</t>
-        </is>
-      </c>
-      <c r="G97" s="46" t="inlineStr"/>
-      <c r="H97" s="46" t="inlineStr">
-        <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I97" s="46" t="inlineStr">
-        <is>
-          <t>1 hotel</t>
-        </is>
-      </c>
-      <c r="J97" s="47" t="inlineStr"/>
-      <c r="K97" s="46" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="L97" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M97" s="46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N97" s="46" t="inlineStr">
-        <is>
-          <t>MONDAY</t>
-        </is>
-      </c>
-      <c r="O97" s="46" t="inlineStr">
-        <is>
-          <t>PRODUCTION</t>
-        </is>
-      </c>
-      <c r="P97" s="46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q97" s="46" t="inlineStr"/>
-      <c r="R97" s="47" t="inlineStr">
-        <is>
-          <t>Serves: Tandoori Production Wk. 4 Monday</t>
-        </is>
-      </c>
-      <c r="S97" s="49" t="n">
-        <v>2</v>
-      </c>
+      <c r="O97" s="50" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P97" s="50" t="inlineStr"/>
+      <c r="Q97" s="50" t="inlineStr"/>
+      <c r="R97" s="51" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Sunday Production</t>
+        </is>
+      </c>
+      <c r="S97" s="42" t="n"/>
       <c r="T97" s="43" t="n"/>
     </row>
     <row r="98">
@@ -29022,29 +29020,33 @@
       </c>
       <c r="E98" s="47" t="inlineStr">
         <is>
-          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
+          <t>Cut/Season Tandoori Pork</t>
         </is>
       </c>
       <c r="F98" s="46" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>1 cs</t>
         </is>
       </c>
       <c r="G98" s="46" t="inlineStr"/>
       <c r="H98" s="46" t="inlineStr">
         <is>
-          <t>bins</t>
+          <t>hotels</t>
         </is>
       </c>
       <c r="I98" s="46" t="inlineStr">
         <is>
-          <t>3 bins (6u)</t>
-        </is>
-      </c>
-      <c r="J98" s="47" t="inlineStr"/>
+          <t>1.5u</t>
+        </is>
+      </c>
+      <c r="J98" s="47" t="inlineStr">
+        <is>
+          <t>Season w/Vindaloo Dry Spice Mix</t>
+        </is>
+      </c>
       <c r="K98" s="46" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L98" s="41" t="inlineStr">
@@ -29059,7 +29061,7 @@
       </c>
       <c r="N98" s="46" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="O98" s="46" t="inlineStr">
@@ -29067,19 +29069,17 @@
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P98" s="46" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="P98" s="46" t="n">
+        <v>3</v>
       </c>
       <c r="Q98" s="46" t="inlineStr"/>
       <c r="R98" s="47" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
+          <t>Serves: Wk. 4 Friday Dinner</t>
         </is>
       </c>
       <c r="S98" s="48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T98" s="43" t="n"/>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="B99" s="46" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="C99" s="46" t="inlineStr">
@@ -29106,7 +29106,7 @@
       </c>
       <c r="E99" s="47" t="inlineStr">
         <is>
-          <t>Massaman Curry Paste</t>
+          <t>Tandoori Marinade</t>
         </is>
       </c>
       <c r="F99" s="46" t="inlineStr">
@@ -29117,19 +29117,15 @@
       <c r="G99" s="46" t="inlineStr"/>
       <c r="H99" s="46" t="inlineStr">
         <is>
-          <t>cambro</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="I99" s="46" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J99" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
-        </is>
-      </c>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J99" s="47" t="inlineStr"/>
       <c r="K99" s="46" t="inlineStr">
         <is>
           <t>60</t>
@@ -29147,25 +29143,27 @@
       </c>
       <c r="N99" s="46" t="inlineStr">
         <is>
-          <t>TUESDAY</t>
+          <t>MONDAY</t>
         </is>
       </c>
       <c r="O99" s="46" t="inlineStr">
         <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P99" s="46" t="n">
-        <v>0.5</v>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="P99" s="46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="Q99" s="46" t="inlineStr"/>
       <c r="R99" s="47" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Tuesday Dinner</t>
-        </is>
-      </c>
-      <c r="S99" s="48" t="n">
-        <v>4</v>
+          <t>Serves: Tandoori Production Wk. 4 Monday</t>
+        </is>
+      </c>
+      <c r="S99" s="49" t="n">
+        <v>2</v>
       </c>
       <c r="T99" s="43" t="n"/>
     </row>
@@ -29177,7 +29175,7 @@
       </c>
       <c r="B100" s="46" t="inlineStr">
         <is>
-          <t>FRIDAY</t>
+          <t>SATURDAY</t>
         </is>
       </c>
       <c r="C100" s="46" t="inlineStr">
@@ -29192,29 +29190,29 @@
       </c>
       <c r="E100" s="47" t="inlineStr">
         <is>
-          <t>Portobello Cheese Melt prep (→ Wk4 Sun Lunch — Veg)</t>
+          <t>Trim/Season BBQ Chicken Legs (→ Wk 4 Tuesday Dinner)</t>
         </is>
       </c>
       <c r="F100" s="46" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>155</t>
         </is>
       </c>
       <c r="G100" s="46" t="inlineStr"/>
       <c r="H100" s="46" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I100" s="46" t="inlineStr"/>
-      <c r="J100" s="47" t="inlineStr">
-        <is>
-          <t>Prep/slice portobello; hold chilled; cook day-of</t>
-        </is>
-      </c>
+          <t>bins</t>
+        </is>
+      </c>
+      <c r="I100" s="46" t="inlineStr">
+        <is>
+          <t>3 bins (6u)</t>
+        </is>
+      </c>
+      <c r="J100" s="47" t="inlineStr"/>
       <c r="K100" s="46" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>90</t>
         </is>
       </c>
       <c r="L100" s="41" t="inlineStr">
@@ -29229,25 +29227,27 @@
       </c>
       <c r="N100" s="46" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="O100" s="46" t="inlineStr">
         <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P100" s="46" t="n">
-        <v>1</v>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P100" s="46" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
       </c>
       <c r="Q100" s="46" t="inlineStr"/>
       <c r="R100" s="47" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
-        </is>
-      </c>
-      <c r="S100" s="49" t="n">
-        <v>2</v>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S100" s="48" t="n">
+        <v>3</v>
       </c>
       <c r="T100" s="43" t="n"/>
     </row>
@@ -29259,7 +29259,7 @@
       </c>
       <c r="B101" s="46" t="inlineStr">
         <is>
-          <t>SATURDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C101" s="46" t="inlineStr">
@@ -29274,38 +29274,38 @@
       </c>
       <c r="E101" s="47" t="inlineStr">
         <is>
-          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
+          <t>Massaman Curry Paste</t>
         </is>
       </c>
       <c r="F101" s="46" t="inlineStr">
         <is>
-          <t>3 bins + 1 bag</t>
+          <t>recipe</t>
         </is>
       </c>
       <c r="G101" s="46" t="inlineStr"/>
       <c r="H101" s="46" t="inlineStr">
         <is>
-          <t>bus bin/bag</t>
+          <t>cambro</t>
         </is>
       </c>
       <c r="I101" s="46" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J101" s="47" t="inlineStr">
         <is>
-          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
+          <t xml:space="preserve">MOVED from Sat → Fri. Stores overnight in cambro. </t>
         </is>
       </c>
       <c r="K101" s="46" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L101" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L101" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M101" s="46" t="inlineStr">
@@ -29315,27 +29315,25 @@
       </c>
       <c r="N101" s="46" t="inlineStr">
         <is>
-          <t>SUNDAY</t>
+          <t>TUESDAY</t>
         </is>
       </c>
       <c r="O101" s="46" t="inlineStr">
         <is>
-          <t>LUNCH</t>
-        </is>
-      </c>
-      <c r="P101" s="46" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P101" s="46" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q101" s="46" t="inlineStr"/>
       <c r="R101" s="47" t="inlineStr">
         <is>
-          <t>Serves: Wk. 4 Sunday Lunch</t>
-        </is>
-      </c>
-      <c r="S101" s="49" t="n">
-        <v>1</v>
+          <t>Serves: Wk. 4 Tuesday Dinner</t>
+        </is>
+      </c>
+      <c r="S101" s="48" t="n">
+        <v>4</v>
       </c>
       <c r="T101" s="43" t="n"/>
     </row>
@@ -29347,7 +29345,7 @@
       </c>
       <c r="B102" s="46" t="inlineStr">
         <is>
-          <t>SATURDAY</t>
+          <t>FRIDAY</t>
         </is>
       </c>
       <c r="C102" s="46" t="inlineStr">
@@ -29362,30 +29360,34 @@
       </c>
       <c r="E102" s="47" t="inlineStr">
         <is>
-          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+          <t>Portobello Cheese Melt prep (→ Wk4 Sun Lunch — Veg)</t>
         </is>
       </c>
       <c r="F102" s="46" t="inlineStr">
         <is>
-          <t>3 hotels</t>
+          <t>???</t>
         </is>
       </c>
       <c r="G102" s="46" t="inlineStr"/>
-      <c r="H102" s="46" t="inlineStr"/>
+      <c r="H102" s="46" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
       <c r="I102" s="46" t="inlineStr"/>
       <c r="J102" s="47" t="inlineStr">
         <is>
-          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+          <t>Prep/slice portobello; hold chilled; cook day-of</t>
         </is>
       </c>
       <c r="K102" s="46" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="L102" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="L102" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
         </is>
       </c>
       <c r="M102" s="46" t="inlineStr">
@@ -29403,10 +29405,8 @@
           <t>LUNCH</t>
         </is>
       </c>
-      <c r="P102" s="46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="P102" s="46" t="n">
+        <v>1</v>
       </c>
       <c r="Q102" s="46" t="inlineStr"/>
       <c r="R102" s="47" t="inlineStr">
@@ -29415,7 +29415,7 @@
         </is>
       </c>
       <c r="S102" s="49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T102" s="43" t="n"/>
     </row>
@@ -29442,38 +29442,38 @@
       </c>
       <c r="E103" s="47" t="inlineStr">
         <is>
-          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+          <t>Prep Salad Greens / Lettuce / Tomato (→ Sun Lunch)</t>
         </is>
       </c>
       <c r="F103" s="46" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>3 bins + 1 bag</t>
         </is>
       </c>
       <c r="G103" s="46" t="inlineStr"/>
       <c r="H103" s="46" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>bus bin/bag</t>
         </is>
       </c>
       <c r="I103" s="46" t="inlineStr">
         <is>
-          <t>1 hotel</t>
+          <t>4 items</t>
         </is>
       </c>
       <c r="J103" s="47" t="inlineStr">
         <is>
-          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+          <t>Prep at LAN AM; send PM. May prep Fri if needed.</t>
         </is>
       </c>
       <c r="K103" s="46" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="L103" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L103" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
         </is>
       </c>
       <c r="M103" s="46" t="inlineStr">
@@ -29493,7 +29493,7 @@
       </c>
       <c r="P103" s="46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Q103" s="46" t="inlineStr"/>
@@ -29508,412 +29508,406 @@
       <c r="T103" s="43" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="44" t="inlineStr">
+      <c r="A104" s="46" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B104" s="44" t="inlineStr">
+      <c r="B104" s="46" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C104" s="44" t="inlineStr">
+      <c r="C104" s="46" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="D104" s="44" t="inlineStr">
+      <c r="D104" s="46" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E104" s="47" t="inlineStr">
+        <is>
+          <t>Prep Roasted Peppers &amp; Onions (→ Wk4 Sun Lunch)</t>
+        </is>
+      </c>
+      <c r="F104" s="46" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G104" s="46" t="inlineStr"/>
+      <c r="H104" s="46" t="inlineStr"/>
+      <c r="I104" s="46" t="inlineStr"/>
+      <c r="J104" s="47" t="inlineStr">
+        <is>
+          <t>Roast at LAN Sat; hold chilled; send hot Sun AM</t>
+        </is>
+      </c>
+      <c r="K104" s="46" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L104" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M104" s="46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N104" s="46" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O104" s="46" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P104" s="46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q104" s="46" t="inlineStr"/>
+      <c r="R104" s="47" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S104" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" s="43" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B105" s="46" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C105" s="46" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D105" s="46" t="inlineStr">
+        <is>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="E105" s="47" t="inlineStr">
+        <is>
+          <t>Prep Roasted Veg (→ Sun Lunch — Veg)</t>
+        </is>
+      </c>
+      <c r="F105" s="46" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="G105" s="46" t="inlineStr"/>
+      <c r="H105" s="46" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I105" s="46" t="inlineStr">
+        <is>
+          <t>1 hotel</t>
+        </is>
+      </c>
+      <c r="J105" s="47" t="inlineStr">
+        <is>
+          <t>Slice/season at Bloor Sat; roast Sun AM. RECIPE NEEDED.</t>
+        </is>
+      </c>
+      <c r="K105" s="46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L105" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M105" s="46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N105" s="46" t="inlineStr">
+        <is>
+          <t>SUNDAY</t>
+        </is>
+      </c>
+      <c r="O105" s="46" t="inlineStr">
+        <is>
+          <t>LUNCH</t>
+        </is>
+      </c>
+      <c r="P105" s="46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q105" s="46" t="inlineStr"/>
+      <c r="R105" s="47" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 4 Sunday Lunch</t>
+        </is>
+      </c>
+      <c r="S105" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" s="43" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B106" s="44" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C106" s="44" t="inlineStr">
+        <is>
+          <t>PRODUCTION</t>
+        </is>
+      </c>
+      <c r="D106" s="44" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E104" s="45" t="inlineStr">
+      <c r="E106" s="45" t="inlineStr">
         <is>
           <t>Beef Massaman Curry (Sat Wk 4. Dinner)</t>
         </is>
       </c>
-      <c r="F104" s="44" t="inlineStr">
+      <c r="F106" s="44" t="inlineStr">
         <is>
           <t>110lbs</t>
         </is>
       </c>
-      <c r="G104" s="44" t="inlineStr">
+      <c r="G106" s="44" t="inlineStr">
         <is>
           <t>12 oz</t>
         </is>
       </c>
-      <c r="H104" s="44" t="inlineStr">
+      <c r="H106" s="44" t="inlineStr">
         <is>
           <t>vac</t>
         </is>
       </c>
-      <c r="I104" s="44" t="inlineStr">
+      <c r="I106" s="44" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J104" s="45" t="inlineStr">
+      <c r="J106" s="45" t="inlineStr">
         <is>
           <t>Braised Beef (Combi) 2+ hours; Stove Top</t>
         </is>
       </c>
-      <c r="K104" s="44" t="inlineStr">
+      <c r="K106" s="44" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="L104" s="41" t="inlineStr">
+      <c r="L106" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M104" s="44" t="inlineStr">
+      <c r="M106" s="44" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N104" s="44" t="inlineStr">
+      <c r="N106" s="44" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O104" s="44" t="inlineStr">
+      <c r="O106" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P104" s="44" t="inlineStr">
+      <c r="P106" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q104" s="44" t="inlineStr"/>
-      <c r="R104" s="45" t="inlineStr">
+      <c r="Q106" s="44" t="inlineStr"/>
+      <c r="R106" s="45" t="inlineStr">
         <is>
           <t>Serves: Wk. 4 Saturday Dinner</t>
         </is>
       </c>
-      <c r="S104" s="48" t="n">
+      <c r="S106" s="48" t="n">
         <v>7</v>
       </c>
-      <c r="T104" s="43" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="44" t="inlineStr">
+      <c r="T106" s="43" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" s="44" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C107" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="D107" s="44" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="E107" s="45" t="inlineStr">
+        <is>
+          <t>Pepperoni + Veg Pizza (Sat Dinner — vendor pickup)</t>
+        </is>
+      </c>
+      <c r="F107" s="44" t="n"/>
+      <c r="G107" s="44" t="n"/>
+      <c r="H107" s="44" t="n"/>
+      <c r="I107" s="44" t="n"/>
+      <c r="J107" s="45" t="inlineStr">
+        <is>
+          <t>Picked up from vendor on PM van run</t>
+        </is>
+      </c>
+      <c r="K107" s="44" t="n"/>
+      <c r="L107" s="41" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="M107" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="N107" s="44" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O107" s="44" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P107" s="44" t="n"/>
+      <c r="Q107" s="44" t="n"/>
+      <c r="R107" s="45" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Saturday Dinner</t>
+        </is>
+      </c>
+      <c r="S107" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="43" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B105" s="44" t="inlineStr">
+      <c r="B108" s="44" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="C105" s="44" t="inlineStr">
+      <c r="C108" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="D105" s="44" t="inlineStr">
+      <c r="D108" s="44" t="inlineStr">
         <is>
           <t>COOK</t>
         </is>
       </c>
-      <c r="E105" s="45" t="inlineStr">
+      <c r="E108" s="45" t="inlineStr">
         <is>
           <t>Potato Wedges (Sat Dinner side)</t>
         </is>
       </c>
-      <c r="F105" s="44" t="inlineStr">
+      <c r="F108" s="44" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="G105" s="44" t="inlineStr"/>
-      <c r="H105" s="44" t="inlineStr"/>
-      <c r="I105" s="44" t="inlineStr">
+      <c r="G108" s="44" t="inlineStr"/>
+      <c r="H108" s="44" t="inlineStr"/>
+      <c r="I108" s="44" t="inlineStr">
         <is>
           <t>3 hotels</t>
         </is>
       </c>
-      <c r="J105" s="45" t="inlineStr">
+      <c r="J108" s="45" t="inlineStr">
         <is>
           <t>Purchased frozen; oven</t>
         </is>
       </c>
-      <c r="K105" s="44" t="inlineStr">
+      <c r="K108" s="44" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="L105" s="41" t="inlineStr">
+      <c r="L108" s="41" t="inlineStr">
         <is>
           <t>Bloor</t>
         </is>
       </c>
-      <c r="M105" s="44" t="inlineStr">
+      <c r="M108" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N105" s="44" t="inlineStr">
+      <c r="N108" s="44" t="inlineStr">
         <is>
           <t>SATURDAY</t>
         </is>
       </c>
-      <c r="O105" s="44" t="inlineStr">
+      <c r="O108" s="44" t="inlineStr">
         <is>
           <t>DINNER</t>
         </is>
       </c>
-      <c r="P105" s="44" t="inlineStr">
+      <c r="P108" s="44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q105" s="44" t="inlineStr"/>
-      <c r="R105" s="45" t="inlineStr">
+      <c r="Q108" s="44" t="inlineStr"/>
+      <c r="R108" s="45" t="inlineStr">
         <is>
           <t>Serves: Wk. 3 Saturday Dinner</t>
-        </is>
-      </c>
-      <c r="S105" s="42" t="n"/>
-      <c r="T105" s="43" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B106" s="52" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C106" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D106" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E106" s="53" t="inlineStr">
-        <is>
-          <t>Pick up Baked Rolls at GC</t>
-        </is>
-      </c>
-      <c r="F106" s="52" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G106" s="52" t="inlineStr"/>
-      <c r="H106" s="52" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="I106" s="52" t="inlineStr"/>
-      <c r="J106" s="53" t="inlineStr">
-        <is>
-          <t>GC → Rex</t>
-        </is>
-      </c>
-      <c r="K106" s="52" t="inlineStr"/>
-      <c r="L106" s="55" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="M106" s="52" t="inlineStr"/>
-      <c r="N106" s="52" t="inlineStr"/>
-      <c r="O106" s="52" t="inlineStr"/>
-      <c r="P106" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R106" s="53" t="inlineStr">
-        <is>
-          <t>N/A — logistics</t>
-        </is>
-      </c>
-      <c r="S106" s="42" t="n"/>
-      <c r="T106" s="43" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B107" s="52" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C107" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D107" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E107" s="53" t="inlineStr">
-        <is>
-          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
-        </is>
-      </c>
-      <c r="F107" s="52" t="inlineStr">
-        <is>
-          <t>pickup</t>
-        </is>
-      </c>
-      <c r="G107" s="52" t="inlineStr"/>
-      <c r="H107" s="52" t="inlineStr">
-        <is>
-          <t>boxes</t>
-        </is>
-      </c>
-      <c r="I107" s="52" t="inlineStr">
-        <is>
-          <t>order</t>
-        </is>
-      </c>
-      <c r="J107" s="53" t="inlineStr">
-        <is>
-          <t>Vendor → Rex | Driver collects ordered pizza</t>
-        </is>
-      </c>
-      <c r="K107" s="52" t="inlineStr"/>
-      <c r="L107" s="57" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="M107" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N107" s="52" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O107" s="52" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P107" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R107" s="53" t="inlineStr">
-        <is>
-          <t>Serves: Wk. 3 Saturday Dinner</t>
-        </is>
-      </c>
-      <c r="S107" s="42" t="n"/>
-      <c r="T107" s="43" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B108" s="52" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="C108" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="D108" s="52" t="inlineStr">
-        <is>
-          <t>SEND PM</t>
-        </is>
-      </c>
-      <c r="E108" s="53" t="inlineStr">
-        <is>
-          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
-        </is>
-      </c>
-      <c r="F108" s="52" t="inlineStr">
-        <is>
-          <t>3 bins + 1 bag</t>
-        </is>
-      </c>
-      <c r="G108" s="52" t="inlineStr"/>
-      <c r="H108" s="52" t="inlineStr">
-        <is>
-          <t>bus bin/bag</t>
-        </is>
-      </c>
-      <c r="I108" s="52" t="inlineStr">
-        <is>
-          <t>4 items</t>
-        </is>
-      </c>
-      <c r="J108" s="53" t="inlineStr">
-        <is>
-          <t>LAN → Rex fridge</t>
-        </is>
-      </c>
-      <c r="K108" s="52" t="inlineStr"/>
-      <c r="L108" s="54" t="inlineStr">
-        <is>
-          <t>LAN</t>
-        </is>
-      </c>
-      <c r="M108" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N108" s="52" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O108" s="52" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P108" s="52" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="Q108" s="52" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="R108" s="53" t="inlineStr">
-        <is>
-          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
         </is>
       </c>
       <c r="S108" s="42" t="n"/>
@@ -29942,59 +29936,37 @@
       </c>
       <c r="E109" s="53" t="inlineStr">
         <is>
-          <t>HOT Potato Wedges → Dinner</t>
+          <t>Pick up Baked Rolls at GC</t>
         </is>
       </c>
       <c r="F109" s="52" t="inlineStr">
         <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
-      <c r="G109" s="52" t="inlineStr">
-        <is>
-          <t>6 oz</t>
-        </is>
-      </c>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="G109" s="52" t="inlineStr"/>
       <c r="H109" s="52" t="inlineStr">
         <is>
-          <t>hotel</t>
-        </is>
-      </c>
-      <c r="I109" s="52" t="inlineStr">
-        <is>
-          <t>3 hotels</t>
-        </is>
-      </c>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="I109" s="52" t="inlineStr"/>
       <c r="J109" s="53" t="inlineStr">
         <is>
-          <t>Bloor → Rex</t>
+          <t>GC → Rex</t>
         </is>
       </c>
       <c r="K109" s="52" t="inlineStr"/>
-      <c r="L109" s="41" t="inlineStr">
-        <is>
-          <t>Bloor</t>
-        </is>
-      </c>
-      <c r="M109" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N109" s="52" t="inlineStr">
-        <is>
-          <t>SATURDAY</t>
-        </is>
-      </c>
-      <c r="O109" s="52" t="inlineStr">
-        <is>
-          <t>DINNER</t>
-        </is>
-      </c>
-      <c r="P109" s="52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="L109" s="55" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="M109" s="52" t="inlineStr"/>
+      <c r="N109" s="52" t="inlineStr"/>
+      <c r="O109" s="52" t="inlineStr"/>
+      <c r="P109" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="Q109" s="52" t="inlineStr">
         <is>
@@ -30003,11 +29975,271 @@
       </c>
       <c r="R109" s="53" t="inlineStr">
         <is>
-          <t>Produced: Wk. 3 Saturday Dinner (same day)</t>
+          <t>N/A — logistics</t>
         </is>
       </c>
       <c r="S109" s="42" t="n"/>
       <c r="T109" s="43" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B110" s="52" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C110" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D110" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E110" s="53" t="inlineStr">
+        <is>
+          <t>Pick up Pepperoni + Veg Pizza at vendor</t>
+        </is>
+      </c>
+      <c r="F110" s="52" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="G110" s="52" t="inlineStr"/>
+      <c r="H110" s="52" t="inlineStr">
+        <is>
+          <t>boxes</t>
+        </is>
+      </c>
+      <c r="I110" s="52" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="J110" s="53" t="inlineStr">
+        <is>
+          <t>Vendor → Rex | Driver collects ordered pizza</t>
+        </is>
+      </c>
+      <c r="K110" s="52" t="inlineStr"/>
+      <c r="L110" s="57" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="M110" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N110" s="52" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O110" s="52" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P110" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R110" s="53" t="inlineStr">
+        <is>
+          <t>Serves: Wk. 3 Saturday Dinner</t>
+        </is>
+      </c>
+      <c r="S110" s="42" t="n"/>
+      <c r="T110" s="43" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B111" s="52" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C111" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D111" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E111" s="53" t="inlineStr">
+        <is>
+          <t>Cold Greens + Lettuce/Tomato → Sun Lunch</t>
+        </is>
+      </c>
+      <c r="F111" s="52" t="inlineStr">
+        <is>
+          <t>3 bins + 1 bag</t>
+        </is>
+      </c>
+      <c r="G111" s="52" t="inlineStr"/>
+      <c r="H111" s="52" t="inlineStr">
+        <is>
+          <t>bus bin/bag</t>
+        </is>
+      </c>
+      <c r="I111" s="52" t="inlineStr">
+        <is>
+          <t>4 items</t>
+        </is>
+      </c>
+      <c r="J111" s="53" t="inlineStr">
+        <is>
+          <t>LAN → Rex fridge</t>
+        </is>
+      </c>
+      <c r="K111" s="52" t="inlineStr"/>
+      <c r="L111" s="54" t="inlineStr">
+        <is>
+          <t>LAN</t>
+        </is>
+      </c>
+      <c r="M111" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N111" s="52" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O111" s="52" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P111" s="52" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Q111" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R111" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Dinner (LAN same day)</t>
+        </is>
+      </c>
+      <c r="S111" s="42" t="n"/>
+      <c r="T111" s="43" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B112" s="52" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="C112" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="D112" s="52" t="inlineStr">
+        <is>
+          <t>SEND PM</t>
+        </is>
+      </c>
+      <c r="E112" s="53" t="inlineStr">
+        <is>
+          <t>HOT Potato Wedges → Dinner</t>
+        </is>
+      </c>
+      <c r="F112" s="52" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="G112" s="52" t="inlineStr">
+        <is>
+          <t>6 oz</t>
+        </is>
+      </c>
+      <c r="H112" s="52" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="I112" s="52" t="inlineStr">
+        <is>
+          <t>3 hotels</t>
+        </is>
+      </c>
+      <c r="J112" s="53" t="inlineStr">
+        <is>
+          <t>Bloor → Rex</t>
+        </is>
+      </c>
+      <c r="K112" s="52" t="inlineStr"/>
+      <c r="L112" s="41" t="inlineStr">
+        <is>
+          <t>Bloor</t>
+        </is>
+      </c>
+      <c r="M112" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N112" s="52" t="inlineStr">
+        <is>
+          <t>SATURDAY</t>
+        </is>
+      </c>
+      <c r="O112" s="52" t="inlineStr">
+        <is>
+          <t>DINNER</t>
+        </is>
+      </c>
+      <c r="P112" s="52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q112" s="52" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="R112" s="53" t="inlineStr">
+        <is>
+          <t>Produced: Wk. 3 Saturday Dinner (same day)</t>
+        </is>
+      </c>
+      <c r="S112" s="42" t="n"/>
+      <c r="T112" s="43" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R106"/>
